--- a/Excel/一方通行/斩业星熊.xlsx
+++ b/Excel/一方通行/斩业星熊.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\一方通行\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7A0FB55-B2BE-4159-B715-4173B6713308}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF7D36AA-0C5C-4286-8A26-AA011B6CCA3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -53,6 +53,7 @@
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>PC:</t>
@@ -61,6 +62,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -86,6 +88,7 @@
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>PC:</t>
@@ -94,6 +97,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -101,13 +105,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="AZ1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000002000000}">
+    <comment ref="BB1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000002000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>PC:</t>
@@ -116,6 +121,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -126,13 +132,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="BP1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000003000000}">
+    <comment ref="BR1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000003000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Admin:</t>
@@ -141,6 +148,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -148,13 +156,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="CR1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000004000000}">
+    <comment ref="CT1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000004000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Admin:</t>
@@ -163,6 +172,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -188,6 +198,7 @@
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Admin:</t>
@@ -196,6 +207,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -211,6 +223,7 @@
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Admin:
@@ -220,6 +233,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -236,6 +250,7 @@
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Admin:</t>
@@ -244,6 +259,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -261,6 +277,7 @@
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Admin:</t>
@@ -269,6 +286,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -281,7 +299,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="900" uniqueCount="535">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="906" uniqueCount="540">
   <si>
     <t>Id</t>
   </si>
@@ -1897,6 +1915,26 @@
   </si>
   <si>
     <t>斩熊3二攻击,星熊锁血,星熊分摊对其他,星熊分摊对自身,斩熊撤退,斩熊3结束动作</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>优先Buff</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>自定义优先级</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>OrderBuff</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>OrderExpression</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
@@ -1916,18 +1954,21 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFFC000"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1935,6 +1976,7 @@
       <sz val="11"/>
       <color rgb="FF00B0F0"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1942,12 +1984,14 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1955,16 +1999,19 @@
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -2014,7 +2061,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2050,6 +2097,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -5868,7 +5918,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:DH737"/>
+  <dimension ref="A1:DJ737"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.08203125" customWidth="1"/>
@@ -5908,54 +5958,54 @@
     <col min="38" max="39" width="8.33203125" customWidth="1"/>
     <col min="40" max="40" width="15" customWidth="1"/>
     <col min="41" max="41" width="13.25" customWidth="1"/>
-    <col min="42" max="43" width="11.83203125" customWidth="1"/>
-    <col min="44" max="44" width="18.4140625" customWidth="1"/>
-    <col min="45" max="45" width="12.25" customWidth="1"/>
-    <col min="46" max="46" width="11.9140625" customWidth="1"/>
-    <col min="47" max="47" width="19.58203125" customWidth="1"/>
-    <col min="48" max="48" width="12.6640625" customWidth="1"/>
-    <col min="50" max="50" width="7" customWidth="1"/>
-    <col min="51" max="51" width="11.75" customWidth="1"/>
-    <col min="52" max="52" width="19.75" customWidth="1"/>
-    <col min="53" max="53" width="5.08203125" customWidth="1"/>
-    <col min="54" max="54" width="8.5" customWidth="1"/>
-    <col min="55" max="55" width="13.5" customWidth="1"/>
-    <col min="56" max="56" width="14.6640625" customWidth="1"/>
-    <col min="57" max="57" width="10.1640625" customWidth="1"/>
-    <col min="58" max="58" width="8.25" customWidth="1"/>
-    <col min="59" max="65" width="8.33203125" customWidth="1"/>
-    <col min="66" max="68" width="11.25" customWidth="1"/>
-    <col min="69" max="69" width="6.58203125" customWidth="1"/>
-    <col min="70" max="71" width="8" customWidth="1"/>
-    <col min="72" max="72" width="7.33203125" style="5" customWidth="1"/>
-    <col min="73" max="74" width="8.5" style="5" customWidth="1"/>
-    <col min="75" max="76" width="7.83203125" style="5" customWidth="1"/>
-    <col min="77" max="77" width="22.1640625" style="5" customWidth="1"/>
-    <col min="78" max="78" width="13.5" customWidth="1"/>
-    <col min="79" max="79" width="21.1640625" customWidth="1"/>
-    <col min="80" max="80" width="15.75" customWidth="1"/>
-    <col min="81" max="81" width="15.58203125" customWidth="1"/>
-    <col min="82" max="82" width="12.83203125" customWidth="1"/>
-    <col min="83" max="83" width="16.1640625" customWidth="1"/>
-    <col min="85" max="85" width="16" customWidth="1"/>
-    <col min="86" max="87" width="12.83203125" customWidth="1"/>
-    <col min="88" max="88" width="23.58203125" customWidth="1"/>
-    <col min="89" max="89" width="12.83203125" customWidth="1"/>
-    <col min="90" max="90" width="17.08203125" customWidth="1"/>
-    <col min="91" max="91" width="9.5"/>
-    <col min="97" max="97" width="14" customWidth="1"/>
-    <col min="98" max="98" width="8" customWidth="1"/>
-    <col min="100" max="100" width="11.08203125" customWidth="1"/>
-    <col min="101" max="101" width="13.75" customWidth="1"/>
-    <col min="102" max="102" width="9.5"/>
-    <col min="105" max="106" width="9.5"/>
-    <col min="108" max="108" width="15.5" customWidth="1"/>
-    <col min="110" max="111" width="9.5"/>
-    <col min="112" max="112" width="9" hidden="1" customWidth="1"/>
-    <col min="117" max="117" width="9.5"/>
+    <col min="42" max="45" width="11.83203125" customWidth="1"/>
+    <col min="46" max="46" width="18.4140625" customWidth="1"/>
+    <col min="47" max="47" width="12.25" customWidth="1"/>
+    <col min="48" max="48" width="11.9140625" customWidth="1"/>
+    <col min="49" max="49" width="19.58203125" customWidth="1"/>
+    <col min="50" max="50" width="12.6640625" customWidth="1"/>
+    <col min="52" max="52" width="7" customWidth="1"/>
+    <col min="53" max="53" width="11.75" customWidth="1"/>
+    <col min="54" max="54" width="19.75" customWidth="1"/>
+    <col min="55" max="55" width="5.08203125" customWidth="1"/>
+    <col min="56" max="56" width="8.5" customWidth="1"/>
+    <col min="57" max="57" width="13.5" customWidth="1"/>
+    <col min="58" max="58" width="14.6640625" customWidth="1"/>
+    <col min="59" max="59" width="10.1640625" customWidth="1"/>
+    <col min="60" max="60" width="8.25" customWidth="1"/>
+    <col min="61" max="67" width="8.33203125" customWidth="1"/>
+    <col min="68" max="70" width="11.25" customWidth="1"/>
+    <col min="71" max="71" width="6.58203125" customWidth="1"/>
+    <col min="72" max="73" width="8" customWidth="1"/>
+    <col min="74" max="74" width="7.33203125" style="5" customWidth="1"/>
+    <col min="75" max="76" width="8.5" style="5" customWidth="1"/>
+    <col min="77" max="78" width="7.83203125" style="5" customWidth="1"/>
+    <col min="79" max="79" width="22.1640625" style="5" customWidth="1"/>
+    <col min="80" max="80" width="13.5" customWidth="1"/>
+    <col min="81" max="81" width="21.1640625" customWidth="1"/>
+    <col min="82" max="82" width="15.75" customWidth="1"/>
+    <col min="83" max="83" width="15.58203125" customWidth="1"/>
+    <col min="84" max="84" width="12.83203125" customWidth="1"/>
+    <col min="85" max="85" width="16.1640625" customWidth="1"/>
+    <col min="87" max="87" width="16" customWidth="1"/>
+    <col min="88" max="89" width="12.83203125" customWidth="1"/>
+    <col min="90" max="90" width="23.58203125" customWidth="1"/>
+    <col min="91" max="91" width="12.83203125" customWidth="1"/>
+    <col min="92" max="92" width="17.08203125" customWidth="1"/>
+    <col min="93" max="93" width="9.5"/>
+    <col min="99" max="99" width="14" customWidth="1"/>
+    <col min="100" max="100" width="8" customWidth="1"/>
+    <col min="102" max="102" width="11.08203125" customWidth="1"/>
+    <col min="103" max="103" width="13.75" customWidth="1"/>
+    <col min="104" max="104" width="9.5"/>
+    <col min="107" max="108" width="9.5"/>
+    <col min="110" max="110" width="15.5" customWidth="1"/>
+    <col min="112" max="113" width="9.5"/>
+    <col min="114" max="114" width="9" hidden="1" customWidth="1"/>
+    <col min="119" max="119" width="9.5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:111" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:113" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>141</v>
       </c>
@@ -6079,209 +6129,215 @@
       <c r="AQ1" t="s">
         <v>180</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AR1" s="13" t="s">
+        <v>535</v>
+      </c>
+      <c r="AS1" s="13" t="s">
+        <v>536</v>
+      </c>
+      <c r="AT1" t="s">
         <v>181</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AU1" t="s">
         <v>182</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AV1" t="s">
         <v>183</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AW1" t="s">
         <v>184</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AX1" t="s">
         <v>185</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AY1" t="s">
         <v>186</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AZ1" t="s">
         <v>187</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="BA1" t="s">
         <v>188</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="BB1" t="s">
         <v>189</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BC1" t="s">
         <v>190</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="BD1" t="s">
         <v>191</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BE1" t="s">
         <v>192</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BF1" t="s">
         <v>193</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BG1" t="s">
         <v>194</v>
-      </c>
-      <c r="BF1" t="s">
-        <v>195</v>
       </c>
       <c r="BH1" t="s">
         <v>195</v>
       </c>
-      <c r="BI1" t="s">
+      <c r="BJ1" t="s">
+        <v>195</v>
+      </c>
+      <c r="BK1" t="s">
         <v>196</v>
       </c>
-      <c r="BJ1" t="s">
+      <c r="BL1" t="s">
         <v>197</v>
       </c>
-      <c r="BK1" t="s">
+      <c r="BM1" t="s">
         <v>198</v>
       </c>
-      <c r="BL1" t="s">
+      <c r="BN1" t="s">
         <v>199</v>
       </c>
-      <c r="BM1" t="s">
+      <c r="BO1" t="s">
         <v>200</v>
       </c>
-      <c r="BN1" t="s">
+      <c r="BP1" t="s">
         <v>201</v>
       </c>
-      <c r="BO1" t="s">
+      <c r="BQ1" t="s">
         <v>202</v>
       </c>
-      <c r="BP1" t="s">
+      <c r="BR1" t="s">
         <v>203</v>
       </c>
-      <c r="BQ1" t="s">
+      <c r="BS1" t="s">
         <v>204</v>
       </c>
-      <c r="BR1" t="s">
+      <c r="BT1" t="s">
         <v>205</v>
       </c>
-      <c r="BS1" t="s">
+      <c r="BU1" t="s">
         <v>206</v>
       </c>
-      <c r="BT1" s="5" t="s">
+      <c r="BV1" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="BU1" s="5" t="s">
+      <c r="BW1" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="BV1" s="5" t="s">
+      <c r="BX1" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="BW1" s="5" t="s">
+      <c r="BY1" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="BX1" s="5" t="s">
+      <c r="BZ1" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="BY1" s="5" t="s">
+      <c r="CA1" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="BZ1" t="s">
+      <c r="CB1" t="s">
         <v>213</v>
       </c>
-      <c r="CA1" s="5" t="s">
+      <c r="CC1" s="5" t="s">
         <v>214</v>
       </c>
-      <c r="CB1" t="s">
+      <c r="CD1" t="s">
         <v>215</v>
       </c>
-      <c r="CC1" t="s">
+      <c r="CE1" t="s">
         <v>216</v>
       </c>
-      <c r="CD1" t="s">
+      <c r="CF1" t="s">
         <v>217</v>
       </c>
-      <c r="CE1" t="s">
+      <c r="CG1" t="s">
         <v>218</v>
       </c>
-      <c r="CF1" t="s">
+      <c r="CH1" t="s">
         <v>219</v>
       </c>
-      <c r="CG1" t="s">
+      <c r="CI1" t="s">
         <v>220</v>
       </c>
-      <c r="CH1" t="s">
+      <c r="CJ1" t="s">
         <v>221</v>
       </c>
-      <c r="CI1" t="s">
+      <c r="CK1" t="s">
         <v>222</v>
       </c>
-      <c r="CJ1" t="s">
+      <c r="CL1" t="s">
         <v>223</v>
       </c>
-      <c r="CK1" t="s">
+      <c r="CM1" t="s">
         <v>224</v>
       </c>
-      <c r="CL1" t="s">
+      <c r="CN1" t="s">
         <v>225</v>
       </c>
-      <c r="CM1" t="s">
+      <c r="CO1" t="s">
         <v>226</v>
       </c>
-      <c r="CN1" t="s">
+      <c r="CP1" t="s">
         <v>227</v>
       </c>
-      <c r="CO1" t="s">
+      <c r="CQ1" t="s">
         <v>228</v>
       </c>
-      <c r="CP1" t="s">
+      <c r="CR1" t="s">
         <v>205</v>
       </c>
-      <c r="CQ1" t="s">
+      <c r="CS1" t="s">
         <v>229</v>
       </c>
-      <c r="CR1" t="s">
+      <c r="CT1" t="s">
         <v>230</v>
       </c>
-      <c r="CS1" t="s">
+      <c r="CU1" t="s">
         <v>231</v>
       </c>
-      <c r="CT1" t="s">
+      <c r="CV1" t="s">
         <v>232</v>
       </c>
-      <c r="CU1" t="s">
+      <c r="CW1" t="s">
         <v>233</v>
-      </c>
-      <c r="CV1" t="s">
-        <v>234</v>
-      </c>
-      <c r="CW1" t="s">
-        <v>235</v>
       </c>
       <c r="CX1" t="s">
         <v>234</v>
       </c>
       <c r="CY1" t="s">
+        <v>235</v>
+      </c>
+      <c r="CZ1" t="s">
+        <v>234</v>
+      </c>
+      <c r="DA1" t="s">
         <v>236</v>
       </c>
-      <c r="CZ1" t="s">
+      <c r="DB1" t="s">
         <v>237</v>
       </c>
-      <c r="DA1" t="s">
+      <c r="DC1" t="s">
         <v>238</v>
       </c>
-      <c r="DB1" t="s">
+      <c r="DD1" t="s">
         <v>239</v>
       </c>
-      <c r="DC1" t="s">
+      <c r="DE1" t="s">
         <v>240</v>
       </c>
-      <c r="DD1" t="s">
+      <c r="DF1" t="s">
         <v>241</v>
       </c>
-      <c r="DE1" t="s">
+      <c r="DG1" t="s">
         <v>242</v>
       </c>
-      <c r="DF1" t="s">
+      <c r="DH1" t="s">
         <v>243</v>
       </c>
-      <c r="DG1" t="s">
+      <c r="DI1" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="2" spans="1:111" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -6408,212 +6464,218 @@
       <c r="AQ2" t="s">
         <v>282</v>
       </c>
-      <c r="AR2" t="s">
+      <c r="AR2" s="13" t="s">
+        <v>537</v>
+      </c>
+      <c r="AS2" s="13" t="s">
+        <v>538</v>
+      </c>
+      <c r="AT2" t="s">
         <v>283</v>
       </c>
-      <c r="AS2" t="s">
+      <c r="AU2" t="s">
         <v>284</v>
       </c>
-      <c r="AT2" t="s">
+      <c r="AV2" t="s">
         <v>285</v>
       </c>
-      <c r="AU2" t="s">
+      <c r="AW2" t="s">
         <v>286</v>
       </c>
-      <c r="AV2" t="s">
+      <c r="AX2" t="s">
         <v>287</v>
       </c>
-      <c r="AW2" t="s">
+      <c r="AY2" t="s">
         <v>288</v>
       </c>
-      <c r="AX2" t="s">
+      <c r="AZ2" t="s">
         <v>289</v>
       </c>
-      <c r="AY2" t="s">
+      <c r="BA2" t="s">
         <v>290</v>
       </c>
-      <c r="AZ2" t="s">
+      <c r="BB2" t="s">
         <v>291</v>
       </c>
-      <c r="BA2" t="s">
+      <c r="BC2" t="s">
         <v>292</v>
       </c>
-      <c r="BB2" t="s">
+      <c r="BD2" t="s">
         <v>293</v>
       </c>
-      <c r="BC2" t="s">
+      <c r="BE2" t="s">
         <v>294</v>
       </c>
-      <c r="BD2" t="s">
+      <c r="BF2" t="s">
         <v>295</v>
       </c>
-      <c r="BE2" t="s">
+      <c r="BG2" t="s">
         <v>296</v>
       </c>
-      <c r="BF2" t="s">
+      <c r="BH2" t="s">
         <v>297</v>
       </c>
-      <c r="BG2" t="s">
+      <c r="BI2" t="s">
         <v>298</v>
       </c>
-      <c r="BH2" t="s">
+      <c r="BJ2" t="s">
         <v>299</v>
       </c>
-      <c r="BI2" t="s">
+      <c r="BK2" t="s">
         <v>300</v>
       </c>
-      <c r="BJ2" t="s">
+      <c r="BL2" t="s">
         <v>301</v>
       </c>
-      <c r="BK2" t="s">
+      <c r="BM2" t="s">
         <v>302</v>
       </c>
-      <c r="BL2" t="s">
+      <c r="BN2" t="s">
         <v>303</v>
       </c>
-      <c r="BM2" t="s">
+      <c r="BO2" t="s">
         <v>79</v>
       </c>
-      <c r="BN2" t="s">
+      <c r="BP2" t="s">
         <v>304</v>
       </c>
-      <c r="BO2" t="s">
+      <c r="BQ2" t="s">
         <v>305</v>
       </c>
-      <c r="BP2" t="s">
+      <c r="BR2" t="s">
         <v>306</v>
       </c>
-      <c r="BQ2" t="s">
+      <c r="BS2" t="s">
         <v>307</v>
       </c>
-      <c r="BR2" t="s">
+      <c r="BT2" t="s">
         <v>308</v>
       </c>
-      <c r="BS2" t="s">
+      <c r="BU2" t="s">
         <v>95</v>
       </c>
-      <c r="BT2" s="5" t="s">
+      <c r="BV2" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="BU2" s="5" t="s">
+      <c r="BW2" s="5" t="s">
         <v>310</v>
       </c>
-      <c r="BV2" s="5" t="s">
+      <c r="BX2" s="5" t="s">
         <v>311</v>
       </c>
-      <c r="BW2" s="5" t="s">
+      <c r="BY2" s="5" t="s">
         <v>312</v>
       </c>
-      <c r="BX2" s="5" t="s">
+      <c r="BZ2" s="5" t="s">
         <v>313</v>
       </c>
-      <c r="BY2" s="5" t="s">
+      <c r="CA2" s="5" t="s">
         <v>314</v>
       </c>
-      <c r="BZ2" t="s">
+      <c r="CB2" t="s">
         <v>315</v>
       </c>
-      <c r="CA2" t="s">
+      <c r="CC2" t="s">
         <v>316</v>
       </c>
-      <c r="CB2" t="s">
+      <c r="CD2" t="s">
         <v>317</v>
       </c>
-      <c r="CC2" t="s">
+      <c r="CE2" t="s">
         <v>318</v>
       </c>
-      <c r="CD2" t="s">
+      <c r="CF2" t="s">
         <v>319</v>
       </c>
-      <c r="CE2" t="s">
+      <c r="CG2" t="s">
         <v>320</v>
       </c>
-      <c r="CF2" t="s">
+      <c r="CH2" t="s">
         <v>321</v>
       </c>
-      <c r="CG2" t="s">
+      <c r="CI2" t="s">
         <v>322</v>
       </c>
-      <c r="CH2" t="s">
+      <c r="CJ2" t="s">
         <v>323</v>
       </c>
-      <c r="CI2" t="s">
+      <c r="CK2" t="s">
         <v>324</v>
       </c>
-      <c r="CJ2" t="s">
+      <c r="CL2" t="s">
         <v>325</v>
       </c>
-      <c r="CK2" t="s">
+      <c r="CM2" t="s">
         <v>326</v>
       </c>
-      <c r="CL2" t="s">
+      <c r="CN2" t="s">
         <v>327</v>
       </c>
-      <c r="CM2" t="s">
+      <c r="CO2" t="s">
         <v>328</v>
       </c>
-      <c r="CN2" t="s">
+      <c r="CP2" t="s">
         <v>329</v>
       </c>
-      <c r="CO2" t="s">
+      <c r="CQ2" t="s">
         <v>330</v>
       </c>
-      <c r="CP2" t="s">
+      <c r="CR2" t="s">
         <v>331</v>
       </c>
-      <c r="CQ2" t="s">
+      <c r="CS2" t="s">
         <v>332</v>
       </c>
-      <c r="CR2" t="s">
+      <c r="CT2" t="s">
         <v>333</v>
       </c>
-      <c r="CS2" t="s">
+      <c r="CU2" t="s">
         <v>334</v>
       </c>
-      <c r="CT2" t="s">
+      <c r="CV2" t="s">
         <v>335</v>
       </c>
-      <c r="CU2" t="s">
+      <c r="CW2" t="s">
         <v>336</v>
       </c>
-      <c r="CV2" t="s">
+      <c r="CX2" t="s">
         <v>337</v>
       </c>
-      <c r="CW2" t="s">
+      <c r="CY2" t="s">
         <v>338</v>
       </c>
-      <c r="CX2" t="s">
+      <c r="CZ2" t="s">
         <v>339</v>
       </c>
-      <c r="CY2" t="s">
+      <c r="DA2" t="s">
         <v>340</v>
       </c>
-      <c r="CZ2" t="s">
+      <c r="DB2" t="s">
         <v>341</v>
       </c>
-      <c r="DA2" t="s">
+      <c r="DC2" t="s">
         <v>342</v>
       </c>
-      <c r="DB2" t="s">
+      <c r="DD2" t="s">
         <v>343</v>
       </c>
-      <c r="DC2" t="s">
+      <c r="DE2" t="s">
         <v>344</v>
       </c>
-      <c r="DD2" t="s">
+      <c r="DF2" t="s">
         <v>345</v>
       </c>
-      <c r="DE2" t="s">
+      <c r="DG2" t="s">
         <v>346</v>
       </c>
-      <c r="DF2" t="s">
+      <c r="DH2" t="s">
         <v>347</v>
       </c>
-      <c r="DG2" t="s">
+      <c r="DI2" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="3" spans="1:111" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -6740,182 +6802,182 @@
       <c r="AQ3" t="s">
         <v>2</v>
       </c>
-      <c r="AR3" t="s">
+      <c r="AR3" s="13" t="s">
+        <v>539</v>
+      </c>
+      <c r="AS3" s="13" t="s">
+        <v>539</v>
+      </c>
+      <c r="AT3" t="s">
         <v>355</v>
-      </c>
-      <c r="AS3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AT3" t="s">
-        <v>117</v>
       </c>
       <c r="AU3" t="s">
         <v>116</v>
       </c>
       <c r="AV3" t="s">
-        <v>356</v>
+        <v>117</v>
       </c>
       <c r="AW3" t="s">
         <v>116</v>
       </c>
       <c r="AX3" t="s">
-        <v>117</v>
+        <v>356</v>
       </c>
       <c r="AY3" t="s">
         <v>116</v>
       </c>
       <c r="AZ3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="BA3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="BB3" t="s">
         <v>118</v>
       </c>
       <c r="BC3" t="s">
+        <v>117</v>
+      </c>
+      <c r="BD3" t="s">
         <v>118</v>
       </c>
-      <c r="BD3" t="s">
+      <c r="BE3" t="s">
+        <v>118</v>
+      </c>
+      <c r="BF3" t="s">
         <v>117</v>
-      </c>
-      <c r="BE3" t="s">
-        <v>116</v>
-      </c>
-      <c r="BF3" t="s">
-        <v>355</v>
       </c>
       <c r="BG3" t="s">
         <v>116</v>
       </c>
       <c r="BH3" t="s">
-        <v>117</v>
+        <v>355</v>
       </c>
       <c r="BI3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="BJ3" t="s">
         <v>117</v>
       </c>
       <c r="BK3" t="s">
+        <v>117</v>
+      </c>
+      <c r="BL3" t="s">
+        <v>117</v>
+      </c>
+      <c r="BM3" t="s">
         <v>118</v>
       </c>
-      <c r="BL3" t="s">
+      <c r="BN3" t="s">
         <v>118</v>
       </c>
-      <c r="BM3" t="s">
+      <c r="BO3" t="s">
         <v>119</v>
       </c>
-      <c r="BN3" t="s">
+      <c r="BP3" t="s">
         <v>119</v>
       </c>
-      <c r="BO3" t="s">
+      <c r="BQ3" t="s">
         <v>357</v>
       </c>
-      <c r="BP3" t="s">
+      <c r="BR3" t="s">
         <v>358</v>
       </c>
-      <c r="BQ3" t="s">
+      <c r="BS3" t="s">
         <v>117</v>
       </c>
-      <c r="BR3" t="s">
+      <c r="BT3" t="s">
         <v>117</v>
       </c>
-      <c r="BS3" t="s">
+      <c r="BU3" t="s">
         <v>116</v>
       </c>
-      <c r="BT3" s="5" t="s">
+      <c r="BV3" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="BU3" s="5" t="s">
+      <c r="BW3" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="BV3" s="5" t="s">
+      <c r="BX3" s="5" t="s">
         <v>118</v>
-      </c>
-      <c r="BW3" s="5" t="s">
-        <v>359</v>
-      </c>
-      <c r="BX3" s="5" t="s">
-        <v>116</v>
       </c>
       <c r="BY3" s="5" t="s">
         <v>359</v>
       </c>
-      <c r="BZ3" t="s">
-        <v>124</v>
-      </c>
-      <c r="CA3" t="s">
-        <v>360</v>
+      <c r="BZ3" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="CA3" s="5" t="s">
+        <v>359</v>
       </c>
       <c r="CB3" t="s">
         <v>124</v>
       </c>
       <c r="CC3" t="s">
-        <v>124</v>
+        <v>360</v>
       </c>
       <c r="CD3" t="s">
         <v>124</v>
       </c>
       <c r="CE3" t="s">
+        <v>124</v>
+      </c>
+      <c r="CF3" t="s">
+        <v>124</v>
+      </c>
+      <c r="CG3" t="s">
         <v>361</v>
       </c>
-      <c r="CF3" t="s">
+      <c r="CH3" t="s">
         <v>362</v>
       </c>
-      <c r="CG3" t="s">
+      <c r="CI3" t="s">
         <v>2</v>
       </c>
-      <c r="CH3" t="s">
+      <c r="CJ3" t="s">
         <v>363</v>
       </c>
-      <c r="CI3" t="s">
+      <c r="CK3" t="s">
         <v>363</v>
       </c>
-      <c r="CJ3" t="s">
+      <c r="CL3" t="s">
         <v>125</v>
       </c>
-      <c r="CK3" t="s">
+      <c r="CM3" t="s">
         <v>120</v>
       </c>
-      <c r="CL3" t="s">
+      <c r="CN3" t="s">
         <v>120</v>
-      </c>
-      <c r="CM3" t="s">
-        <v>123</v>
-      </c>
-      <c r="CN3" t="s">
-        <v>123</v>
       </c>
       <c r="CO3" t="s">
         <v>123</v>
       </c>
       <c r="CP3" t="s">
-        <v>360</v>
+        <v>123</v>
       </c>
       <c r="CQ3" t="s">
         <v>123</v>
       </c>
       <c r="CR3" t="s">
+        <v>360</v>
+      </c>
+      <c r="CS3" t="s">
+        <v>123</v>
+      </c>
+      <c r="CT3" t="s">
         <v>116</v>
       </c>
-      <c r="CS3" t="s">
+      <c r="CU3" t="s">
         <v>125</v>
       </c>
-      <c r="CT3" t="s">
+      <c r="CV3" t="s">
         <v>364</v>
       </c>
-      <c r="CU3" t="s">
+      <c r="CW3" t="s">
         <v>365</v>
       </c>
-      <c r="CV3" t="s">
+      <c r="CX3" t="s">
         <v>365</v>
-      </c>
-      <c r="CW3" t="s">
-        <v>364</v>
-      </c>
-      <c r="CX3" t="s">
-        <v>364</v>
       </c>
       <c r="CY3" t="s">
         <v>364</v>
@@ -6927,10 +6989,10 @@
         <v>364</v>
       </c>
       <c r="DB3" t="s">
-        <v>116</v>
+        <v>364</v>
       </c>
       <c r="DC3" t="s">
-        <v>116</v>
+        <v>364</v>
       </c>
       <c r="DD3" t="s">
         <v>116</v>
@@ -6944,13 +7006,19 @@
       <c r="DG3" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="4" spans="1:111" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="DH3" t="s">
+        <v>116</v>
+      </c>
+      <c r="DI3" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="4" spans="1:113" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="5" spans="1:111" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>367</v>
       </c>
@@ -6971,29 +7039,29 @@
       <c r="AO5" t="s">
         <v>368</v>
       </c>
-      <c r="AR5" t="s">
+      <c r="AT5" t="s">
         <v>369</v>
       </c>
-      <c r="AV5" t="s">
+      <c r="AX5" t="s">
         <v>370</v>
       </c>
-      <c r="AX5">
-        <v>1</v>
-      </c>
-      <c r="BB5">
-        <v>1</v>
-      </c>
-      <c r="BZ5" t="s">
+      <c r="AZ5">
+        <v>1</v>
+      </c>
+      <c r="BD5">
+        <v>1</v>
+      </c>
+      <c r="CB5" t="s">
         <v>57</v>
       </c>
-      <c r="CE5" t="s">
+      <c r="CG5" t="s">
         <v>371</v>
       </c>
-      <c r="CW5" t="s">
+      <c r="CY5" t="s">
         <v>372</v>
       </c>
     </row>
-    <row r="6" spans="1:111" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>373</v>
       </c>
@@ -7016,23 +7084,23 @@
       <c r="AG6" t="s">
         <v>375</v>
       </c>
-      <c r="BB6">
-        <v>1</v>
-      </c>
-      <c r="BM6" t="s">
+      <c r="BD6">
+        <v>1</v>
+      </c>
+      <c r="BO6" t="s">
         <v>376</v>
       </c>
-      <c r="BQ6">
+      <c r="BS6">
         <v>0.1</v>
       </c>
-      <c r="CL6" t="s">
+      <c r="CN6" t="s">
         <v>377</v>
       </c>
-      <c r="CP6">
+      <c r="CR6">
         <v>0.2</v>
       </c>
     </row>
-    <row r="7" spans="1:111" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>378</v>
       </c>
@@ -7061,17 +7129,17 @@
       <c r="AG7" t="s">
         <v>375</v>
       </c>
-      <c r="BB7">
-        <v>1</v>
-      </c>
-      <c r="CL7" s="2" t="s">
+      <c r="BD7">
+        <v>1</v>
+      </c>
+      <c r="CN7" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="CP7">
+      <c r="CR7">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:111" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>382</v>
       </c>
@@ -7100,35 +7168,35 @@
       <c r="AG8" t="s">
         <v>375</v>
       </c>
-      <c r="AV8" t="s">
+      <c r="AX8" t="s">
         <v>384</v>
       </c>
-      <c r="AW8" s="4">
-        <v>1</v>
-      </c>
-      <c r="AX8">
+      <c r="AY8" s="4">
+        <v>1</v>
+      </c>
+      <c r="AZ8">
         <v>1.67E-2</v>
       </c>
-      <c r="AY8">
-        <v>1</v>
-      </c>
-      <c r="AZ8">
+      <c r="BA8">
         <v>1</v>
       </c>
       <c r="BB8">
         <v>1</v>
       </c>
-      <c r="BQ8">
+      <c r="BD8">
+        <v>1</v>
+      </c>
+      <c r="BS8">
         <v>0.1</v>
       </c>
-      <c r="CL8" s="2" t="s">
+      <c r="CN8" s="2" t="s">
         <v>385</v>
       </c>
-      <c r="CP8">
+      <c r="CR8">
         <v>0.2</v>
       </c>
     </row>
-    <row r="9" spans="1:111" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>386</v>
       </c>
@@ -7151,26 +7219,26 @@
       <c r="AG9" t="s">
         <v>375</v>
       </c>
-      <c r="BB9">
-        <v>1</v>
-      </c>
-      <c r="BM9" t="s">
+      <c r="BD9">
+        <v>1</v>
+      </c>
+      <c r="BO9" t="s">
         <v>387</v>
       </c>
-      <c r="BQ9">
+      <c r="BS9">
         <v>0.1</v>
       </c>
-      <c r="CL9" t="s">
+      <c r="CN9" t="s">
         <v>388</v>
       </c>
-      <c r="CM9" t="s">
+      <c r="CO9" t="s">
         <v>389</v>
       </c>
-      <c r="CP9">
+      <c r="CR9">
         <v>0.2</v>
       </c>
     </row>
-    <row r="10" spans="1:111" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>390</v>
       </c>
@@ -7193,23 +7261,23 @@
       <c r="AG10" t="s">
         <v>375</v>
       </c>
-      <c r="BB10">
-        <v>1</v>
-      </c>
-      <c r="BQ10">
+      <c r="BD10">
+        <v>1</v>
+      </c>
+      <c r="BS10">
         <v>0.1</v>
       </c>
-      <c r="CL10" t="s">
+      <c r="CN10" t="s">
         <v>388</v>
       </c>
-      <c r="CM10" t="s">
+      <c r="CO10" t="s">
         <v>389</v>
       </c>
-      <c r="CP10">
+      <c r="CR10">
         <v>0.2</v>
       </c>
     </row>
-    <row r="11" spans="1:111" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>391</v>
       </c>
@@ -7232,23 +7300,23 @@
       <c r="AG11" t="s">
         <v>375</v>
       </c>
-      <c r="BB11">
-        <v>1</v>
-      </c>
-      <c r="BQ11">
+      <c r="BD11">
+        <v>1</v>
+      </c>
+      <c r="BS11">
         <v>0.1</v>
       </c>
-      <c r="CL11" t="s">
+      <c r="CN11" t="s">
         <v>388</v>
       </c>
-      <c r="CM11" t="s">
+      <c r="CO11" t="s">
         <v>389</v>
       </c>
-      <c r="CP11">
+      <c r="CR11">
         <v>0.2</v>
       </c>
     </row>
-    <row r="12" spans="1:111" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>392</v>
       </c>
@@ -7271,23 +7339,23 @@
       <c r="AG12" t="s">
         <v>375</v>
       </c>
-      <c r="BB12">
-        <v>1</v>
-      </c>
-      <c r="BQ12">
+      <c r="BD12">
+        <v>1</v>
+      </c>
+      <c r="BS12">
         <v>0.1</v>
       </c>
-      <c r="CL12" t="s">
+      <c r="CN12" t="s">
         <v>388</v>
       </c>
-      <c r="CM12" t="s">
+      <c r="CO12" t="s">
         <v>389</v>
       </c>
-      <c r="CP12">
+      <c r="CR12">
         <v>0.2</v>
       </c>
     </row>
-    <row r="13" spans="1:111" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>393</v>
       </c>
@@ -7310,29 +7378,29 @@
       <c r="AG13" t="s">
         <v>375</v>
       </c>
-      <c r="BB13">
-        <v>1</v>
-      </c>
-      <c r="BQ13">
+      <c r="BD13">
+        <v>1</v>
+      </c>
+      <c r="BS13">
         <v>0.1</v>
       </c>
-      <c r="CL13" t="s">
+      <c r="CN13" t="s">
         <v>388</v>
       </c>
-      <c r="CM13" t="s">
+      <c r="CO13" t="s">
         <v>389</v>
       </c>
-      <c r="CP13">
+      <c r="CR13">
         <v>0.2</v>
       </c>
     </row>
-    <row r="14" spans="1:111" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:113" x14ac:dyDescent="0.25">
       <c r="M14"/>
       <c r="N14"/>
       <c r="Y14" s="4"/>
       <c r="Z14" s="4"/>
     </row>
-    <row r="15" spans="1:111" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>394</v>
       </c>
@@ -7370,48 +7438,48 @@
       <c r="AG15" t="s">
         <v>375</v>
       </c>
-      <c r="BB15">
-        <v>1</v>
-      </c>
-      <c r="BM15" t="s">
+      <c r="BD15">
+        <v>1</v>
+      </c>
+      <c r="BO15" t="s">
         <v>399</v>
       </c>
-      <c r="BR15">
+      <c r="BT15">
         <v>9999</v>
       </c>
-      <c r="BT15" s="5">
+      <c r="BV15" s="5">
         <v>0</v>
       </c>
-      <c r="BU15" s="5">
+      <c r="BW15" s="5">
         <v>15</v>
       </c>
-      <c r="BV15" s="5">
-        <v>1</v>
-      </c>
-      <c r="BW15" s="5" t="s">
+      <c r="BX15" s="5">
+        <v>1</v>
+      </c>
+      <c r="BY15" s="5" t="s">
         <v>400</v>
       </c>
-      <c r="BZ15" s="4"/>
-      <c r="CA15" s="4"/>
       <c r="CB15" s="4"/>
       <c r="CC15" s="4"/>
       <c r="CD15" s="4"/>
+      <c r="CE15" s="4"/>
       <c r="CF15" s="4"/>
-      <c r="CG15" s="4"/>
       <c r="CH15" s="4"/>
       <c r="CI15" s="4"/>
+      <c r="CJ15" s="4"/>
       <c r="CK15" s="4"/>
-      <c r="CL15" t="s">
+      <c r="CM15" s="4"/>
+      <c r="CN15" t="s">
         <v>401</v>
       </c>
-      <c r="CM15" t="s">
+      <c r="CO15" t="s">
         <v>402</v>
       </c>
-      <c r="CP15">
+      <c r="CR15">
         <v>9999</v>
       </c>
     </row>
-    <row r="16" spans="1:111" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>403</v>
       </c>
@@ -7434,29 +7502,29 @@
       <c r="AO16" t="s">
         <v>368</v>
       </c>
-      <c r="AR16" t="s">
+      <c r="AT16" t="s">
         <v>369</v>
       </c>
-      <c r="AV16" t="s">
+      <c r="AX16" t="s">
         <v>404</v>
       </c>
-      <c r="AX16">
-        <v>1</v>
-      </c>
-      <c r="BB16">
-        <v>1</v>
-      </c>
-      <c r="BZ16" t="s">
+      <c r="AZ16">
+        <v>1</v>
+      </c>
+      <c r="BD16">
+        <v>1</v>
+      </c>
+      <c r="CB16" t="s">
         <v>57</v>
       </c>
-      <c r="CE16" t="s">
+      <c r="CG16" t="s">
         <v>371</v>
       </c>
-      <c r="CW16" t="s">
+      <c r="CY16" t="s">
         <v>405</v>
       </c>
     </row>
-    <row r="17" spans="1:110" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>406</v>
       </c>
@@ -7488,42 +7556,42 @@
       <c r="AE17">
         <v>1</v>
       </c>
-      <c r="AV17" t="s">
+      <c r="AX17" t="s">
         <v>404</v>
       </c>
-      <c r="AX17">
+      <c r="AZ17">
         <v>1.75</v>
       </c>
-      <c r="BB17">
-        <v>1</v>
-      </c>
-      <c r="CW17" t="s">
+      <c r="BD17">
+        <v>1</v>
+      </c>
+      <c r="CY17" t="s">
         <v>405</v>
       </c>
-      <c r="DB17">
-        <v>1</v>
-      </c>
-      <c r="DF17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="DD17">
+        <v>1</v>
+      </c>
+      <c r="DH17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:112" x14ac:dyDescent="0.25">
       <c r="M18"/>
       <c r="N18"/>
       <c r="Y18" s="4"/>
       <c r="Z18" s="4"/>
-      <c r="BZ18" s="4"/>
-      <c r="CA18" s="4"/>
       <c r="CB18" s="4"/>
       <c r="CC18" s="4"/>
       <c r="CD18" s="4"/>
+      <c r="CE18" s="4"/>
       <c r="CF18" s="4"/>
-      <c r="CG18" s="4"/>
       <c r="CH18" s="4"/>
       <c r="CI18" s="4"/>
+      <c r="CJ18" s="4"/>
       <c r="CK18" s="4"/>
-    </row>
-    <row r="19" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="CM18" s="4"/>
+    </row>
+    <row r="19" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>407</v>
       </c>
@@ -7561,60 +7629,60 @@
       <c r="AG19" t="s">
         <v>375</v>
       </c>
-      <c r="AR19" t="s">
+      <c r="AT19" t="s">
         <v>418</v>
       </c>
-      <c r="BB19">
-        <v>1</v>
-      </c>
-      <c r="BM19" t="s">
+      <c r="BD19">
+        <v>1</v>
+      </c>
+      <c r="BO19" t="s">
         <v>412</v>
       </c>
-      <c r="BN19" t="s">
+      <c r="BP19" t="s">
         <v>413</v>
       </c>
-      <c r="BR19">
+      <c r="BT19">
         <v>32</v>
       </c>
-      <c r="BS19">
-        <v>1</v>
-      </c>
-      <c r="BT19" s="5">
+      <c r="BU19">
+        <v>1</v>
+      </c>
+      <c r="BV19" s="5">
         <v>37</v>
       </c>
-      <c r="BU19" s="5">
+      <c r="BW19" s="5">
         <v>45</v>
       </c>
-      <c r="BV19" s="5">
-        <v>1</v>
-      </c>
-      <c r="BW19" s="5" t="s">
+      <c r="BX19" s="5">
+        <v>1</v>
+      </c>
+      <c r="BY19" s="5" t="s">
         <v>383</v>
       </c>
-      <c r="BZ19" s="4"/>
-      <c r="CA19" s="4"/>
       <c r="CB19" s="4"/>
       <c r="CC19" s="4"/>
       <c r="CD19" s="4"/>
+      <c r="CE19" s="4"/>
       <c r="CF19" s="4"/>
-      <c r="CG19" s="4"/>
       <c r="CH19" s="4"/>
       <c r="CI19" s="4"/>
+      <c r="CJ19" s="4"/>
       <c r="CK19" s="4"/>
-      <c r="CL19" t="s">
+      <c r="CM19" s="4"/>
+      <c r="CN19" t="s">
         <v>414</v>
       </c>
-      <c r="CM19" t="s">
+      <c r="CO19" t="s">
         <v>415</v>
       </c>
-      <c r="CP19">
+      <c r="CR19">
         <v>32</v>
       </c>
-      <c r="CS19" s="12" t="s">
+      <c r="CU19" s="12" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="20" spans="1:110" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>416</v>
       </c>
@@ -7640,35 +7708,35 @@
       <c r="AO20" t="s">
         <v>368</v>
       </c>
-      <c r="AR20" t="s">
+      <c r="AT20" t="s">
         <v>418</v>
       </c>
-      <c r="AV20" t="s">
+      <c r="AX20" t="s">
         <v>404</v>
       </c>
-      <c r="AX20">
-        <v>1</v>
-      </c>
-      <c r="BB20">
+      <c r="AZ20">
+        <v>1</v>
+      </c>
+      <c r="BD20">
         <v>3</v>
       </c>
-      <c r="BC20">
-        <v>1</v>
-      </c>
-      <c r="BD20">
+      <c r="BE20">
+        <v>1</v>
+      </c>
+      <c r="BF20">
         <v>0.1</v>
       </c>
-      <c r="BZ20" t="s">
+      <c r="CB20" t="s">
         <v>419</v>
       </c>
-      <c r="CE20" t="s">
+      <c r="CG20" t="s">
         <v>371</v>
       </c>
-      <c r="CW20" t="s">
+      <c r="CY20" t="s">
         <v>405</v>
       </c>
     </row>
-    <row r="21" spans="1:110" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>420</v>
       </c>
@@ -7695,26 +7763,26 @@
       <c r="AG21" t="s">
         <v>375</v>
       </c>
-      <c r="BB21">
-        <v>1</v>
-      </c>
-      <c r="BQ21">
+      <c r="BD21">
+        <v>1</v>
+      </c>
+      <c r="BS21">
         <v>0.4</v>
       </c>
-      <c r="CK21" t="s">
+      <c r="CM21" t="s">
         <v>417</v>
       </c>
-      <c r="DB21">
-        <v>1</v>
-      </c>
-      <c r="DE21">
-        <v>1</v>
-      </c>
-      <c r="DF21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="DD21">
+        <v>1</v>
+      </c>
+      <c r="DG21">
+        <v>1</v>
+      </c>
+      <c r="DH21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>422</v>
       </c>
@@ -7740,42 +7808,42 @@
       <c r="AG22" t="s">
         <v>375</v>
       </c>
-      <c r="AR22" t="s">
+      <c r="AT22" t="s">
         <v>418</v>
       </c>
-      <c r="BB22">
-        <v>1</v>
-      </c>
-      <c r="BM22" s="12" t="s">
+      <c r="BD22">
+        <v>1</v>
+      </c>
+      <c r="BO22" s="12" t="s">
         <v>534</v>
       </c>
-      <c r="BZ22" s="4"/>
-      <c r="CA22" s="4"/>
       <c r="CB22" s="4"/>
       <c r="CC22" s="4"/>
       <c r="CD22" s="4"/>
+      <c r="CE22" s="4"/>
       <c r="CF22" s="4"/>
-      <c r="CG22" s="4"/>
       <c r="CH22" s="4"/>
       <c r="CI22" s="4"/>
+      <c r="CJ22" s="4"/>
       <c r="CK22" s="4"/>
-      <c r="CL22" t="s">
+      <c r="CM22" s="4"/>
+      <c r="CN22" t="s">
         <v>424</v>
       </c>
-      <c r="CM22" t="s">
+      <c r="CO22" t="s">
         <v>415</v>
       </c>
-      <c r="CN22">
+      <c r="CP22">
         <v>-1</v>
       </c>
-      <c r="CP22">
+      <c r="CR22">
         <v>11</v>
       </c>
-      <c r="CS22" s="12" t="s">
+      <c r="CU22" s="12" t="s">
         <v>523</v>
       </c>
     </row>
-    <row r="23" spans="1:110" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>425</v>
       </c>
@@ -7801,38 +7869,38 @@
       <c r="AO23" t="s">
         <v>368</v>
       </c>
-      <c r="AR23" t="s">
+      <c r="AT23" t="s">
         <v>418</v>
       </c>
-      <c r="AV23" t="s">
+      <c r="AX23" t="s">
         <v>404</v>
       </c>
-      <c r="AX23">
-        <v>1</v>
-      </c>
-      <c r="BB23">
+      <c r="AZ23">
+        <v>1</v>
+      </c>
+      <c r="BD23">
         <v>3</v>
       </c>
-      <c r="BC23">
+      <c r="BE23">
         <v>3</v>
       </c>
-      <c r="BD23">
+      <c r="BF23">
         <v>0.1</v>
       </c>
-      <c r="BZ23" t="s">
+      <c r="CB23" t="s">
         <v>419</v>
       </c>
-      <c r="CE23" t="s">
+      <c r="CG23" t="s">
         <v>371</v>
       </c>
-      <c r="CW23" t="s">
+      <c r="CY23" t="s">
         <v>405</v>
       </c>
-      <c r="CX23" t="s">
+      <c r="CZ23" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="24" spans="1:110" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>428</v>
       </c>
@@ -7853,35 +7921,35 @@
       <c r="AC24">
         <v>1</v>
       </c>
-      <c r="AR24" t="s">
+      <c r="AT24" t="s">
         <v>418</v>
       </c>
-      <c r="AU24">
-        <v>1</v>
-      </c>
-      <c r="BB24">
+      <c r="AW24">
+        <v>1</v>
+      </c>
+      <c r="BD24">
         <v>99</v>
       </c>
-      <c r="BQ24">
+      <c r="BS24">
         <v>0.1</v>
       </c>
-      <c r="CL24" t="s">
+      <c r="CN24" t="s">
         <v>429</v>
       </c>
-      <c r="CP24">
+      <c r="CR24">
         <v>0.2</v>
       </c>
-      <c r="DB24">
-        <v>1</v>
-      </c>
-      <c r="DE24">
-        <v>1</v>
-      </c>
-      <c r="DF24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="DD24">
+        <v>1</v>
+      </c>
+      <c r="DG24">
+        <v>1</v>
+      </c>
+      <c r="DH24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
         <v>529</v>
       </c>
@@ -7905,35 +7973,35 @@
       <c r="AG25" s="12" t="s">
         <v>533</v>
       </c>
-      <c r="AR25" t="s">
+      <c r="AT25" t="s">
         <v>418</v>
       </c>
-      <c r="AU25">
-        <v>1</v>
-      </c>
-      <c r="BB25">
+      <c r="AW25">
+        <v>1</v>
+      </c>
+      <c r="BD25">
         <v>99</v>
       </c>
-      <c r="BQ25">
+      <c r="BS25">
         <v>0.1</v>
       </c>
-      <c r="CL25" s="12" t="s">
+      <c r="CN25" s="12" t="s">
         <v>529</v>
       </c>
-      <c r="CP25">
+      <c r="CR25">
         <v>0.2</v>
       </c>
-      <c r="DB25">
-        <v>1</v>
-      </c>
-      <c r="DE25">
-        <v>1</v>
-      </c>
-      <c r="DF25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="DD25">
+        <v>1</v>
+      </c>
+      <c r="DG25">
+        <v>1</v>
+      </c>
+      <c r="DH25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A26" s="12" t="s">
         <v>530</v>
       </c>
@@ -7957,32 +8025,32 @@
       <c r="AG26" s="12" t="s">
         <v>532</v>
       </c>
-      <c r="AU26">
-        <v>1</v>
-      </c>
-      <c r="BB26">
+      <c r="AW26">
+        <v>1</v>
+      </c>
+      <c r="BD26">
         <v>99</v>
       </c>
-      <c r="BQ26">
+      <c r="BS26">
         <v>0.1</v>
       </c>
-      <c r="CL26" s="12" t="s">
+      <c r="CN26" s="12" t="s">
         <v>530</v>
       </c>
-      <c r="CP26">
+      <c r="CR26">
         <v>0.2</v>
       </c>
-      <c r="DB26">
-        <v>1</v>
-      </c>
-      <c r="DE26">
-        <v>1</v>
-      </c>
-      <c r="DF26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="DD26">
+        <v>1</v>
+      </c>
+      <c r="DG26">
+        <v>1</v>
+      </c>
+      <c r="DH26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>430</v>
       </c>
@@ -8005,14 +8073,14 @@
       <c r="AG27" t="s">
         <v>375</v>
       </c>
-      <c r="BB27">
-        <v>1</v>
-      </c>
-      <c r="CS27" t="s">
+      <c r="BD27">
+        <v>1</v>
+      </c>
+      <c r="CU27" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="28" spans="1:110" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>413</v>
       </c>
@@ -8034,29 +8102,29 @@
       <c r="AG28" t="s">
         <v>375</v>
       </c>
-      <c r="BB28">
-        <v>1</v>
-      </c>
-      <c r="BQ28">
+      <c r="BD28">
+        <v>1</v>
+      </c>
+      <c r="BS28">
         <v>0.33300000000000002</v>
       </c>
-      <c r="BZ28" t="s">
+      <c r="CB28" t="s">
         <v>433</v>
       </c>
-      <c r="CE28" t="s">
+      <c r="CG28" t="s">
         <v>371</v>
       </c>
-      <c r="DB28">
-        <v>1</v>
-      </c>
-      <c r="DE28">
-        <v>1</v>
-      </c>
-      <c r="DF28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="DD28">
+        <v>1</v>
+      </c>
+      <c r="DG28">
+        <v>1</v>
+      </c>
+      <c r="DH28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>434</v>
       </c>
@@ -8081,1249 +8149,1249 @@
       <c r="AG29" t="s">
         <v>375</v>
       </c>
-      <c r="BB29">
-        <v>1</v>
-      </c>
-      <c r="BQ29">
+      <c r="BD29">
+        <v>1</v>
+      </c>
+      <c r="BS29">
         <v>0.33300000000000002</v>
       </c>
-      <c r="BZ29" t="s">
+      <c r="CB29" t="s">
         <v>435</v>
       </c>
-      <c r="CE29" t="s">
+      <c r="CG29" t="s">
         <v>371</v>
       </c>
-      <c r="DB29">
-        <v>1</v>
-      </c>
-      <c r="DE29">
-        <v>1</v>
-      </c>
-      <c r="DF29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="CJ30" s="4"/>
-    </row>
-    <row r="31" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="CJ31" s="4"/>
-    </row>
-    <row r="32" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="CJ32" s="4"/>
-    </row>
-    <row r="36" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ36" s="4"/>
-    </row>
-    <row r="38" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT38"/>
-    </row>
-    <row r="39" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT39"/>
-      <c r="CJ39" s="4"/>
-    </row>
-    <row r="40" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ40" s="4"/>
-    </row>
-    <row r="41" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ41" s="4"/>
-    </row>
-    <row r="42" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ42" s="4"/>
-    </row>
-    <row r="43" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ43" s="4"/>
-    </row>
-    <row r="45" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT45"/>
-    </row>
-    <row r="46" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ46" s="4"/>
-    </row>
-    <row r="47" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ47" s="4"/>
-    </row>
-    <row r="49" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ49" s="4"/>
-    </row>
-    <row r="50" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ50" s="4"/>
-    </row>
-    <row r="52" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT52"/>
-    </row>
-    <row r="53" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ53" s="4"/>
-    </row>
-    <row r="56" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ56" s="4"/>
-    </row>
-    <row r="57" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ57" s="4"/>
-    </row>
-    <row r="60" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ60" s="4"/>
-    </row>
-    <row r="62" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ62" s="4"/>
-    </row>
-    <row r="64" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT64"/>
-    </row>
-    <row r="65" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ65" s="4"/>
-    </row>
-    <row r="66" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ66" s="4"/>
-    </row>
-    <row r="68" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ68" s="4"/>
-    </row>
-    <row r="69" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ69" s="4"/>
-    </row>
-    <row r="70" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ70" s="4"/>
-    </row>
-    <row r="75" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ75" s="4"/>
-    </row>
-    <row r="76" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ76" s="4"/>
-    </row>
-    <row r="79" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ79" s="4"/>
-    </row>
-    <row r="80" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ80" s="4"/>
-    </row>
-    <row r="84" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ84" s="4"/>
-    </row>
-    <row r="88" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ88" s="4"/>
-    </row>
-    <row r="90" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ90" s="4"/>
-    </row>
-    <row r="91" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ91" s="4"/>
-    </row>
-    <row r="93" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ93" s="4"/>
-    </row>
-    <row r="94" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ94" s="4"/>
-    </row>
-    <row r="96" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT96"/>
-    </row>
-    <row r="97" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT97"/>
-      <c r="CJ97" s="4"/>
-    </row>
-    <row r="98" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ98" s="4"/>
-    </row>
-    <row r="100" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ100" s="4"/>
-    </row>
-    <row r="109" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT109"/>
-    </row>
-    <row r="110" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT110"/>
-      <c r="CJ110" s="4"/>
-    </row>
-    <row r="111" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ111" s="4"/>
-    </row>
-    <row r="112" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ112" s="4"/>
-    </row>
-    <row r="113" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT113"/>
-    </row>
-    <row r="114" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT114"/>
-      <c r="CJ114" s="4"/>
-    </row>
-    <row r="115" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ115" s="4"/>
-    </row>
-    <row r="117" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT117"/>
-    </row>
-    <row r="118" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT118"/>
-      <c r="CJ118" s="4"/>
-    </row>
-    <row r="119" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ119" s="4"/>
-    </row>
-    <row r="121" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT121"/>
-    </row>
-    <row r="122" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ122" s="4"/>
-    </row>
-    <row r="125" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ125" s="4"/>
-    </row>
-    <row r="129" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ129" s="4"/>
-    </row>
-    <row r="131" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT131"/>
-    </row>
-    <row r="132" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ132" s="4"/>
-    </row>
-    <row r="139" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT139"/>
-    </row>
-    <row r="140" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ140" s="4"/>
-    </row>
-    <row r="141" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ141" s="4"/>
-    </row>
-    <row r="143" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT143"/>
-    </row>
-    <row r="144" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT144"/>
-      <c r="CJ144" s="4"/>
-    </row>
-    <row r="145" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ145" s="4"/>
-    </row>
-    <row r="151" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT151"/>
-    </row>
-    <row r="152" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT152"/>
-      <c r="CJ152" s="4"/>
-    </row>
-    <row r="153" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT153"/>
-      <c r="CJ153" s="4"/>
-    </row>
-    <row r="154" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ154" s="4"/>
-    </row>
-    <row r="159" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT159"/>
-    </row>
-    <row r="160" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT160"/>
-    </row>
-    <row r="164" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT164"/>
-    </row>
-    <row r="165" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ165" s="4"/>
-    </row>
-    <row r="166" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT166"/>
-    </row>
-    <row r="167" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ167" s="4"/>
-    </row>
-    <row r="177" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT177"/>
-    </row>
-    <row r="178" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ178" s="4"/>
-    </row>
-    <row r="180" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT180"/>
-    </row>
-    <row r="181" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ181" s="4"/>
-    </row>
-    <row r="189" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT189"/>
-    </row>
-    <row r="190" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ190" s="4"/>
-    </row>
-    <row r="194" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT194"/>
-    </row>
-    <row r="195" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ195" s="4"/>
-    </row>
-    <row r="197" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT197"/>
-    </row>
-    <row r="198" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ198" s="4"/>
-    </row>
-    <row r="214" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT214"/>
-    </row>
-    <row r="215" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT215"/>
-      <c r="CJ215" s="4"/>
-    </row>
-    <row r="216" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT216"/>
-      <c r="CJ216" s="4"/>
-    </row>
-    <row r="217" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT217"/>
-      <c r="CJ217" s="4"/>
-    </row>
-    <row r="218" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT218"/>
-    </row>
-    <row r="220" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT220"/>
-    </row>
-    <row r="221" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT221"/>
-      <c r="CJ221" s="4"/>
-    </row>
-    <row r="222" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT222"/>
-      <c r="CJ222" s="4"/>
-    </row>
-    <row r="223" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ223" s="4"/>
-    </row>
-    <row r="227" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT227"/>
-    </row>
-    <row r="228" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ228" s="4"/>
-    </row>
-    <row r="230" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT230"/>
-    </row>
-    <row r="231" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT231"/>
-      <c r="CJ231" s="4"/>
-    </row>
-    <row r="232" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT232"/>
-      <c r="CJ232" s="4"/>
-    </row>
-    <row r="233" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ233" s="4"/>
-    </row>
-    <row r="249" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT249"/>
-    </row>
-    <row r="250" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ250" s="4"/>
-    </row>
-    <row r="258" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ258" s="4"/>
-    </row>
-    <row r="259" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ259" s="4"/>
-    </row>
-    <row r="260" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ260" s="4"/>
-    </row>
-    <row r="261" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ261" s="4"/>
-    </row>
-    <row r="262" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ262" s="4"/>
-    </row>
-    <row r="264" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT264"/>
-    </row>
-    <row r="265" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ265" s="4"/>
-    </row>
-    <row r="266" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT266"/>
-    </row>
-    <row r="267" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT267"/>
-      <c r="CJ267" s="4"/>
-    </row>
-    <row r="268" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ268" s="4"/>
-    </row>
-    <row r="270" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT270"/>
-    </row>
-    <row r="271" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT271"/>
-      <c r="CJ271" s="4"/>
-    </row>
-    <row r="272" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT272"/>
-      <c r="CJ272" s="4"/>
-    </row>
-    <row r="273" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ273" s="4"/>
-    </row>
-    <row r="275" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ275" s="4"/>
-    </row>
-    <row r="277" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ277" s="4"/>
-    </row>
-    <row r="279" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ279" s="4"/>
-    </row>
-    <row r="282" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ282" s="4"/>
-    </row>
-    <row r="283" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ283" s="4"/>
-    </row>
-    <row r="284" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ284" s="4"/>
-    </row>
-    <row r="285" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ285" s="4"/>
-    </row>
-    <row r="286" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ286" s="4"/>
-    </row>
-    <row r="287" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ287" s="4"/>
-    </row>
-    <row r="288" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT288"/>
-    </row>
-    <row r="289" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT289"/>
-      <c r="CJ289" s="4"/>
-    </row>
-    <row r="290" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT290"/>
-      <c r="CJ290" s="4"/>
-    </row>
-    <row r="291" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ291" s="4"/>
-    </row>
-    <row r="292" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ292" s="4"/>
-    </row>
-    <row r="293" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ293" s="4"/>
-    </row>
-    <row r="294" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ294" s="4"/>
-    </row>
-    <row r="296" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ296" s="4"/>
-    </row>
-    <row r="297" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ297" s="4"/>
-    </row>
-    <row r="298" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT298"/>
-    </row>
-    <row r="299" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT299"/>
-      <c r="CJ299" s="4"/>
-    </row>
-    <row r="300" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT300"/>
-      <c r="CJ300" s="4"/>
-    </row>
-    <row r="301" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ301" s="4"/>
-    </row>
-    <row r="302" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ302" s="4"/>
-    </row>
-    <row r="304" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ304" s="4"/>
-    </row>
-    <row r="305" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ305" s="4"/>
-    </row>
-    <row r="306" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT306"/>
-      <c r="CJ306" s="4"/>
-    </row>
-    <row r="307" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT307"/>
-      <c r="CJ307" s="4"/>
-    </row>
-    <row r="308" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ308" s="4"/>
-    </row>
-    <row r="309" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ309" s="4"/>
-    </row>
-    <row r="310" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ310" s="4"/>
-    </row>
-    <row r="312" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT312"/>
-      <c r="CJ312" s="4"/>
-    </row>
-    <row r="313" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ313" s="4"/>
-    </row>
-    <row r="314" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ314" s="4"/>
-    </row>
-    <row r="316" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT316"/>
-      <c r="CJ316" s="4"/>
-    </row>
-    <row r="317" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT317"/>
-      <c r="CJ317" s="4"/>
-    </row>
-    <row r="318" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ318" s="4"/>
-    </row>
-    <row r="320" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ320" s="4"/>
-    </row>
-    <row r="322" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ322" s="4"/>
-    </row>
-    <row r="325" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ325" s="4"/>
-    </row>
-    <row r="326" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ326" s="4"/>
-    </row>
-    <row r="330" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT330"/>
-    </row>
-    <row r="331" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT331"/>
-      <c r="CJ331" s="4"/>
-    </row>
-    <row r="332" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT332"/>
-      <c r="CJ332" s="4"/>
-    </row>
-    <row r="333" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ333" s="4"/>
-    </row>
-    <row r="334" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ334" s="4"/>
-    </row>
-    <row r="335" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT335"/>
-    </row>
-    <row r="336" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ336" s="4"/>
-    </row>
-    <row r="338" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ338" s="4"/>
-    </row>
-    <row r="339" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ339" s="4"/>
-    </row>
-    <row r="341" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ341" s="4"/>
-    </row>
-    <row r="342" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ342" s="4"/>
-    </row>
-    <row r="343" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ343" s="4"/>
-    </row>
-    <row r="344" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ344" s="4"/>
-    </row>
-    <row r="345" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ345" s="4"/>
-    </row>
-    <row r="346" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ346" s="4"/>
-    </row>
-    <row r="347" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ347" s="4"/>
-    </row>
-    <row r="349" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT349"/>
-    </row>
-    <row r="350" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ350" s="4"/>
-    </row>
-    <row r="351" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ351" s="4"/>
-    </row>
-    <row r="384" spans="71:72" x14ac:dyDescent="0.25">
-      <c r="BS384" s="6"/>
-      <c r="BT384" s="7"/>
-    </row>
-    <row r="385" spans="8:88" x14ac:dyDescent="0.25">
+      <c r="DD29">
+        <v>1</v>
+      </c>
+      <c r="DG29">
+        <v>1</v>
+      </c>
+      <c r="DH29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="CL30" s="4"/>
+    </row>
+    <row r="31" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="CL31" s="4"/>
+    </row>
+    <row r="32" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="CL32" s="4"/>
+    </row>
+    <row r="36" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL36" s="4"/>
+    </row>
+    <row r="38" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV38"/>
+    </row>
+    <row r="39" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV39"/>
+      <c r="CL39" s="4"/>
+    </row>
+    <row r="40" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL40" s="4"/>
+    </row>
+    <row r="41" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL41" s="4"/>
+    </row>
+    <row r="42" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL42" s="4"/>
+    </row>
+    <row r="43" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL43" s="4"/>
+    </row>
+    <row r="45" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV45"/>
+    </row>
+    <row r="46" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL46" s="4"/>
+    </row>
+    <row r="47" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL47" s="4"/>
+    </row>
+    <row r="49" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL49" s="4"/>
+    </row>
+    <row r="50" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL50" s="4"/>
+    </row>
+    <row r="52" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV52"/>
+    </row>
+    <row r="53" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL53" s="4"/>
+    </row>
+    <row r="56" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL56" s="4"/>
+    </row>
+    <row r="57" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL57" s="4"/>
+    </row>
+    <row r="60" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL60" s="4"/>
+    </row>
+    <row r="62" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL62" s="4"/>
+    </row>
+    <row r="64" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV64"/>
+    </row>
+    <row r="65" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL65" s="4"/>
+    </row>
+    <row r="66" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL66" s="4"/>
+    </row>
+    <row r="68" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL68" s="4"/>
+    </row>
+    <row r="69" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL69" s="4"/>
+    </row>
+    <row r="70" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL70" s="4"/>
+    </row>
+    <row r="75" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL75" s="4"/>
+    </row>
+    <row r="76" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL76" s="4"/>
+    </row>
+    <row r="79" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL79" s="4"/>
+    </row>
+    <row r="80" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL80" s="4"/>
+    </row>
+    <row r="84" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL84" s="4"/>
+    </row>
+    <row r="88" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL88" s="4"/>
+    </row>
+    <row r="90" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL90" s="4"/>
+    </row>
+    <row r="91" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL91" s="4"/>
+    </row>
+    <row r="93" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL93" s="4"/>
+    </row>
+    <row r="94" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL94" s="4"/>
+    </row>
+    <row r="96" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV96"/>
+    </row>
+    <row r="97" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV97"/>
+      <c r="CL97" s="4"/>
+    </row>
+    <row r="98" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL98" s="4"/>
+    </row>
+    <row r="100" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL100" s="4"/>
+    </row>
+    <row r="109" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV109"/>
+    </row>
+    <row r="110" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV110"/>
+      <c r="CL110" s="4"/>
+    </row>
+    <row r="111" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL111" s="4"/>
+    </row>
+    <row r="112" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL112" s="4"/>
+    </row>
+    <row r="113" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV113"/>
+    </row>
+    <row r="114" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV114"/>
+      <c r="CL114" s="4"/>
+    </row>
+    <row r="115" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL115" s="4"/>
+    </row>
+    <row r="117" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV117"/>
+    </row>
+    <row r="118" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV118"/>
+      <c r="CL118" s="4"/>
+    </row>
+    <row r="119" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL119" s="4"/>
+    </row>
+    <row r="121" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV121"/>
+    </row>
+    <row r="122" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL122" s="4"/>
+    </row>
+    <row r="125" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL125" s="4"/>
+    </row>
+    <row r="129" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL129" s="4"/>
+    </row>
+    <row r="131" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV131"/>
+    </row>
+    <row r="132" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL132" s="4"/>
+    </row>
+    <row r="139" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV139"/>
+    </row>
+    <row r="140" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL140" s="4"/>
+    </row>
+    <row r="141" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL141" s="4"/>
+    </row>
+    <row r="143" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV143"/>
+    </row>
+    <row r="144" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV144"/>
+      <c r="CL144" s="4"/>
+    </row>
+    <row r="145" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL145" s="4"/>
+    </row>
+    <row r="151" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV151"/>
+    </row>
+    <row r="152" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV152"/>
+      <c r="CL152" s="4"/>
+    </row>
+    <row r="153" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV153"/>
+      <c r="CL153" s="4"/>
+    </row>
+    <row r="154" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL154" s="4"/>
+    </row>
+    <row r="159" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV159"/>
+    </row>
+    <row r="160" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV160"/>
+    </row>
+    <row r="164" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV164"/>
+    </row>
+    <row r="165" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL165" s="4"/>
+    </row>
+    <row r="166" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV166"/>
+    </row>
+    <row r="167" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL167" s="4"/>
+    </row>
+    <row r="177" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV177"/>
+    </row>
+    <row r="178" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL178" s="4"/>
+    </row>
+    <row r="180" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV180"/>
+    </row>
+    <row r="181" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL181" s="4"/>
+    </row>
+    <row r="189" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV189"/>
+    </row>
+    <row r="190" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL190" s="4"/>
+    </row>
+    <row r="194" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV194"/>
+    </row>
+    <row r="195" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL195" s="4"/>
+    </row>
+    <row r="197" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV197"/>
+    </row>
+    <row r="198" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL198" s="4"/>
+    </row>
+    <row r="214" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV214"/>
+    </row>
+    <row r="215" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV215"/>
+      <c r="CL215" s="4"/>
+    </row>
+    <row r="216" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV216"/>
+      <c r="CL216" s="4"/>
+    </row>
+    <row r="217" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV217"/>
+      <c r="CL217" s="4"/>
+    </row>
+    <row r="218" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV218"/>
+    </row>
+    <row r="220" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV220"/>
+    </row>
+    <row r="221" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV221"/>
+      <c r="CL221" s="4"/>
+    </row>
+    <row r="222" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV222"/>
+      <c r="CL222" s="4"/>
+    </row>
+    <row r="223" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL223" s="4"/>
+    </row>
+    <row r="227" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV227"/>
+    </row>
+    <row r="228" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL228" s="4"/>
+    </row>
+    <row r="230" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV230"/>
+    </row>
+    <row r="231" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV231"/>
+      <c r="CL231" s="4"/>
+    </row>
+    <row r="232" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV232"/>
+      <c r="CL232" s="4"/>
+    </row>
+    <row r="233" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL233" s="4"/>
+    </row>
+    <row r="249" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV249"/>
+    </row>
+    <row r="250" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL250" s="4"/>
+    </row>
+    <row r="258" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL258" s="4"/>
+    </row>
+    <row r="259" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL259" s="4"/>
+    </row>
+    <row r="260" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL260" s="4"/>
+    </row>
+    <row r="261" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL261" s="4"/>
+    </row>
+    <row r="262" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL262" s="4"/>
+    </row>
+    <row r="264" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV264"/>
+    </row>
+    <row r="265" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL265" s="4"/>
+    </row>
+    <row r="266" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV266"/>
+    </row>
+    <row r="267" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV267"/>
+      <c r="CL267" s="4"/>
+    </row>
+    <row r="268" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL268" s="4"/>
+    </row>
+    <row r="270" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV270"/>
+    </row>
+    <row r="271" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV271"/>
+      <c r="CL271" s="4"/>
+    </row>
+    <row r="272" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV272"/>
+      <c r="CL272" s="4"/>
+    </row>
+    <row r="273" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL273" s="4"/>
+    </row>
+    <row r="275" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL275" s="4"/>
+    </row>
+    <row r="277" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL277" s="4"/>
+    </row>
+    <row r="279" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL279" s="4"/>
+    </row>
+    <row r="282" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL282" s="4"/>
+    </row>
+    <row r="283" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL283" s="4"/>
+    </row>
+    <row r="284" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL284" s="4"/>
+    </row>
+    <row r="285" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL285" s="4"/>
+    </row>
+    <row r="286" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL286" s="4"/>
+    </row>
+    <row r="287" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL287" s="4"/>
+    </row>
+    <row r="288" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV288"/>
+    </row>
+    <row r="289" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV289"/>
+      <c r="CL289" s="4"/>
+    </row>
+    <row r="290" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV290"/>
+      <c r="CL290" s="4"/>
+    </row>
+    <row r="291" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL291" s="4"/>
+    </row>
+    <row r="292" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL292" s="4"/>
+    </row>
+    <row r="293" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL293" s="4"/>
+    </row>
+    <row r="294" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL294" s="4"/>
+    </row>
+    <row r="296" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL296" s="4"/>
+    </row>
+    <row r="297" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL297" s="4"/>
+    </row>
+    <row r="298" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV298"/>
+    </row>
+    <row r="299" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV299"/>
+      <c r="CL299" s="4"/>
+    </row>
+    <row r="300" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV300"/>
+      <c r="CL300" s="4"/>
+    </row>
+    <row r="301" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL301" s="4"/>
+    </row>
+    <row r="302" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL302" s="4"/>
+    </row>
+    <row r="304" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL304" s="4"/>
+    </row>
+    <row r="305" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL305" s="4"/>
+    </row>
+    <row r="306" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV306"/>
+      <c r="CL306" s="4"/>
+    </row>
+    <row r="307" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV307"/>
+      <c r="CL307" s="4"/>
+    </row>
+    <row r="308" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL308" s="4"/>
+    </row>
+    <row r="309" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL309" s="4"/>
+    </row>
+    <row r="310" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL310" s="4"/>
+    </row>
+    <row r="312" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV312"/>
+      <c r="CL312" s="4"/>
+    </row>
+    <row r="313" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL313" s="4"/>
+    </row>
+    <row r="314" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL314" s="4"/>
+    </row>
+    <row r="316" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV316"/>
+      <c r="CL316" s="4"/>
+    </row>
+    <row r="317" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV317"/>
+      <c r="CL317" s="4"/>
+    </row>
+    <row r="318" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL318" s="4"/>
+    </row>
+    <row r="320" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL320" s="4"/>
+    </row>
+    <row r="322" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL322" s="4"/>
+    </row>
+    <row r="325" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL325" s="4"/>
+    </row>
+    <row r="326" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL326" s="4"/>
+    </row>
+    <row r="330" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV330"/>
+    </row>
+    <row r="331" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV331"/>
+      <c r="CL331" s="4"/>
+    </row>
+    <row r="332" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV332"/>
+      <c r="CL332" s="4"/>
+    </row>
+    <row r="333" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL333" s="4"/>
+    </row>
+    <row r="334" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL334" s="4"/>
+    </row>
+    <row r="335" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV335"/>
+    </row>
+    <row r="336" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL336" s="4"/>
+    </row>
+    <row r="338" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL338" s="4"/>
+    </row>
+    <row r="339" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL339" s="4"/>
+    </row>
+    <row r="341" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL341" s="4"/>
+    </row>
+    <row r="342" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL342" s="4"/>
+    </row>
+    <row r="343" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL343" s="4"/>
+    </row>
+    <row r="344" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL344" s="4"/>
+    </row>
+    <row r="345" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL345" s="4"/>
+    </row>
+    <row r="346" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL346" s="4"/>
+    </row>
+    <row r="347" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL347" s="4"/>
+    </row>
+    <row r="349" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV349"/>
+    </row>
+    <row r="350" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL350" s="4"/>
+    </row>
+    <row r="351" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL351" s="4"/>
+    </row>
+    <row r="384" spans="73:74" x14ac:dyDescent="0.25">
+      <c r="BU384" s="6"/>
+      <c r="BV384" s="7"/>
+    </row>
+    <row r="385" spans="8:90" x14ac:dyDescent="0.25">
       <c r="H385" s="6"/>
-      <c r="CJ385" s="6"/>
-    </row>
-    <row r="391" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT391"/>
-    </row>
-    <row r="392" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT392"/>
-      <c r="CJ392" s="4"/>
-    </row>
-    <row r="393" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT393"/>
-      <c r="CJ393" s="4"/>
-    </row>
-    <row r="394" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="CJ394" s="4"/>
-    </row>
-    <row r="411" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT411"/>
-    </row>
-    <row r="412" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ412" s="4"/>
-    </row>
-    <row r="444" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT444"/>
-    </row>
-    <row r="445" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT445"/>
-      <c r="CJ445" s="4"/>
-    </row>
-    <row r="446" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ446" s="4"/>
-    </row>
-    <row r="462" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT462"/>
-    </row>
-    <row r="463" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ463" s="4"/>
-    </row>
-    <row r="469" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT469"/>
-    </row>
-    <row r="470" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT470"/>
-      <c r="CJ470" s="4"/>
-    </row>
-    <row r="471" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ471" s="4"/>
-    </row>
-    <row r="476" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT476"/>
-    </row>
-    <row r="477" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT477"/>
-      <c r="CJ477" s="4"/>
-    </row>
-    <row r="478" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT478"/>
-      <c r="CJ478" s="4"/>
-    </row>
-    <row r="479" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT479"/>
-      <c r="CJ479" s="4"/>
-    </row>
-    <row r="480" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT480"/>
-      <c r="CJ480" s="4"/>
-    </row>
-    <row r="481" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT481"/>
-      <c r="CJ481" s="4"/>
-    </row>
-    <row r="482" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT482"/>
-      <c r="CJ482" s="4"/>
-    </row>
-    <row r="483" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT483"/>
-      <c r="CJ483" s="4"/>
-    </row>
-    <row r="484" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT484"/>
-      <c r="CJ484" s="4"/>
-    </row>
-    <row r="485" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT485"/>
-      <c r="CJ485" s="4"/>
-    </row>
-    <row r="486" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT486"/>
-      <c r="CJ486" s="4"/>
-    </row>
-    <row r="487" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT487"/>
-      <c r="CJ487" s="4"/>
-    </row>
-    <row r="488" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT488"/>
-      <c r="CJ488" s="4"/>
-    </row>
-    <row r="489" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT489"/>
-      <c r="CJ489" s="4"/>
-    </row>
-    <row r="490" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT490"/>
-      <c r="CJ490" s="4"/>
-    </row>
-    <row r="491" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT491"/>
-      <c r="CJ491" s="4"/>
-    </row>
-    <row r="492" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ492" s="4"/>
-    </row>
-    <row r="496" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT496"/>
-    </row>
-    <row r="497" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT497"/>
-      <c r="CJ497" s="4"/>
-    </row>
-    <row r="498" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ498" s="4"/>
-    </row>
-    <row r="499" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT499"/>
-    </row>
-    <row r="500" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ500" s="4"/>
-    </row>
-    <row r="503" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT503"/>
-    </row>
-    <row r="504" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT504"/>
-      <c r="CJ504" s="4"/>
-    </row>
-    <row r="505" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ505" s="4"/>
-    </row>
-    <row r="536" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT536"/>
-    </row>
-    <row r="537" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT537"/>
-      <c r="CJ537" s="4"/>
-    </row>
-    <row r="538" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT538"/>
-      <c r="CJ538" s="4"/>
-    </row>
-    <row r="539" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT539"/>
-      <c r="CJ539" s="4"/>
-    </row>
-    <row r="540" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT540"/>
-      <c r="CJ540" s="4"/>
-    </row>
-    <row r="541" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT541"/>
-      <c r="CJ541" s="4"/>
-    </row>
-    <row r="542" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT542"/>
-      <c r="CJ542" s="4"/>
-    </row>
-    <row r="543" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT543"/>
-      <c r="CJ543" s="4"/>
-    </row>
-    <row r="544" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ544" s="4"/>
-    </row>
-    <row r="546" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT546"/>
-    </row>
-    <row r="547" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ547" s="4"/>
-    </row>
-    <row r="551" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT551"/>
-    </row>
-    <row r="552" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ552" s="4"/>
-    </row>
-    <row r="555" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT555"/>
-    </row>
-    <row r="556" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT556"/>
-      <c r="CJ556" s="4"/>
-    </row>
-    <row r="557" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT557"/>
-      <c r="CJ557" s="4"/>
-    </row>
-    <row r="558" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT558"/>
-      <c r="CJ558" s="4"/>
-    </row>
-    <row r="559" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ559" s="4"/>
-    </row>
-    <row r="566" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT566"/>
-    </row>
-    <row r="567" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ567" s="4"/>
-    </row>
-    <row r="570" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT570"/>
-    </row>
-    <row r="571" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT571"/>
-      <c r="CJ571" s="4"/>
-    </row>
-    <row r="572" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT572"/>
-      <c r="CJ572" s="4"/>
-    </row>
-    <row r="573" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT573"/>
-      <c r="CJ573" s="4"/>
-    </row>
-    <row r="574" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ574" s="4"/>
-    </row>
-    <row r="576" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT576"/>
-    </row>
-    <row r="577" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT577"/>
-      <c r="CJ577" s="4"/>
-    </row>
-    <row r="578" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ578" s="4"/>
-    </row>
-    <row r="579" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ579">
+      <c r="CL385" s="6"/>
+    </row>
+    <row r="391" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV391"/>
+    </row>
+    <row r="392" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV392"/>
+      <c r="CL392" s="4"/>
+    </row>
+    <row r="393" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV393"/>
+      <c r="CL393" s="4"/>
+    </row>
+    <row r="394" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="CL394" s="4"/>
+    </row>
+    <row r="411" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV411"/>
+    </row>
+    <row r="412" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL412" s="4"/>
+    </row>
+    <row r="444" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV444"/>
+    </row>
+    <row r="445" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV445"/>
+      <c r="CL445" s="4"/>
+    </row>
+    <row r="446" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL446" s="4"/>
+    </row>
+    <row r="462" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV462"/>
+    </row>
+    <row r="463" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL463" s="4"/>
+    </row>
+    <row r="469" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV469"/>
+    </row>
+    <row r="470" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV470"/>
+      <c r="CL470" s="4"/>
+    </row>
+    <row r="471" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL471" s="4"/>
+    </row>
+    <row r="476" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV476"/>
+    </row>
+    <row r="477" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV477"/>
+      <c r="CL477" s="4"/>
+    </row>
+    <row r="478" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV478"/>
+      <c r="CL478" s="4"/>
+    </row>
+    <row r="479" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV479"/>
+      <c r="CL479" s="4"/>
+    </row>
+    <row r="480" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV480"/>
+      <c r="CL480" s="4"/>
+    </row>
+    <row r="481" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV481"/>
+      <c r="CL481" s="4"/>
+    </row>
+    <row r="482" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV482"/>
+      <c r="CL482" s="4"/>
+    </row>
+    <row r="483" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV483"/>
+      <c r="CL483" s="4"/>
+    </row>
+    <row r="484" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV484"/>
+      <c r="CL484" s="4"/>
+    </row>
+    <row r="485" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV485"/>
+      <c r="CL485" s="4"/>
+    </row>
+    <row r="486" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV486"/>
+      <c r="CL486" s="4"/>
+    </row>
+    <row r="487" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV487"/>
+      <c r="CL487" s="4"/>
+    </row>
+    <row r="488" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV488"/>
+      <c r="CL488" s="4"/>
+    </row>
+    <row r="489" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV489"/>
+      <c r="CL489" s="4"/>
+    </row>
+    <row r="490" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV490"/>
+      <c r="CL490" s="4"/>
+    </row>
+    <row r="491" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV491"/>
+      <c r="CL491" s="4"/>
+    </row>
+    <row r="492" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL492" s="4"/>
+    </row>
+    <row r="496" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV496"/>
+    </row>
+    <row r="497" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV497"/>
+      <c r="CL497" s="4"/>
+    </row>
+    <row r="498" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL498" s="4"/>
+    </row>
+    <row r="499" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV499"/>
+    </row>
+    <row r="500" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL500" s="4"/>
+    </row>
+    <row r="503" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV503"/>
+    </row>
+    <row r="504" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV504"/>
+      <c r="CL504" s="4"/>
+    </row>
+    <row r="505" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL505" s="4"/>
+    </row>
+    <row r="536" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV536"/>
+    </row>
+    <row r="537" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV537"/>
+      <c r="CL537" s="4"/>
+    </row>
+    <row r="538" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV538"/>
+      <c r="CL538" s="4"/>
+    </row>
+    <row r="539" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV539"/>
+      <c r="CL539" s="4"/>
+    </row>
+    <row r="540" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV540"/>
+      <c r="CL540" s="4"/>
+    </row>
+    <row r="541" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV541"/>
+      <c r="CL541" s="4"/>
+    </row>
+    <row r="542" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV542"/>
+      <c r="CL542" s="4"/>
+    </row>
+    <row r="543" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV543"/>
+      <c r="CL543" s="4"/>
+    </row>
+    <row r="544" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL544" s="4"/>
+    </row>
+    <row r="546" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV546"/>
+    </row>
+    <row r="547" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL547" s="4"/>
+    </row>
+    <row r="551" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV551"/>
+    </row>
+    <row r="552" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL552" s="4"/>
+    </row>
+    <row r="555" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV555"/>
+    </row>
+    <row r="556" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV556"/>
+      <c r="CL556" s="4"/>
+    </row>
+    <row r="557" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV557"/>
+      <c r="CL557" s="4"/>
+    </row>
+    <row r="558" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV558"/>
+      <c r="CL558" s="4"/>
+    </row>
+    <row r="559" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL559" s="4"/>
+    </row>
+    <row r="566" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV566"/>
+    </row>
+    <row r="567" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL567" s="4"/>
+    </row>
+    <row r="570" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV570"/>
+    </row>
+    <row r="571" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV571"/>
+      <c r="CL571" s="4"/>
+    </row>
+    <row r="572" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV572"/>
+      <c r="CL572" s="4"/>
+    </row>
+    <row r="573" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV573"/>
+      <c r="CL573" s="4"/>
+    </row>
+    <row r="574" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL574" s="4"/>
+    </row>
+    <row r="576" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV576"/>
+    </row>
+    <row r="577" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV577"/>
+      <c r="CL577" s="4"/>
+    </row>
+    <row r="578" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL578" s="4"/>
+    </row>
+    <row r="579" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL579">
         <v>0.15</v>
       </c>
     </row>
-    <row r="581" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ581">
+    <row r="581" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL581">
         <v>0.2</v>
       </c>
     </row>
-    <row r="582" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ582">
+    <row r="582" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL582">
         <v>0.1</v>
       </c>
     </row>
-    <row r="584" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ584">
+    <row r="584" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL584">
         <v>0.2</v>
       </c>
     </row>
-    <row r="591" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ591">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="593" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ593">
+    <row r="591" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL591">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="593" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL593">
         <v>0.4</v>
       </c>
     </row>
-    <row r="594" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ594">
+    <row r="594" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL594">
         <v>0.6</v>
       </c>
     </row>
-    <row r="597" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ597">
+    <row r="597" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL597">
         <v>0.5</v>
       </c>
     </row>
-    <row r="598" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ598">
+    <row r="598" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL598">
         <v>0.66700000000000004</v>
       </c>
     </row>
-    <row r="599" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ599">
+    <row r="599" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL599">
         <v>0.2</v>
       </c>
     </row>
-    <row r="602" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT602"/>
-    </row>
-    <row r="603" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT603"/>
-      <c r="CJ603" s="4"/>
-    </row>
-    <row r="604" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT604"/>
-      <c r="CJ604" s="4"/>
-    </row>
-    <row r="605" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT605"/>
-      <c r="CJ605" s="4"/>
-    </row>
-    <row r="606" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT606"/>
-      <c r="CJ606" s="4"/>
-    </row>
-    <row r="607" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT607"/>
-      <c r="CJ607" s="4"/>
-    </row>
-    <row r="608" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT608"/>
-      <c r="CJ608" s="4"/>
-    </row>
-    <row r="609" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT609"/>
-      <c r="CJ609" s="4"/>
-    </row>
-    <row r="610" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT610"/>
-      <c r="CJ610" s="4"/>
-    </row>
-    <row r="611" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ611" s="4"/>
-    </row>
-    <row r="612" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT612"/>
-    </row>
-    <row r="613" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ613" s="4"/>
-    </row>
-    <row r="622" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT622"/>
-    </row>
-    <row r="623" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT623"/>
-      <c r="CJ623" s="4"/>
-    </row>
-    <row r="624" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT624"/>
-      <c r="CJ624" s="4"/>
-    </row>
-    <row r="625" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT625"/>
-      <c r="CJ625" s="4"/>
-    </row>
-    <row r="626" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT626"/>
-      <c r="CJ626" s="4"/>
-    </row>
-    <row r="627" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT627"/>
-      <c r="CJ627" s="4"/>
-    </row>
-    <row r="628" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT628"/>
-      <c r="CJ628" s="4"/>
-    </row>
-    <row r="629" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT629"/>
-      <c r="CJ629" s="4"/>
-    </row>
-    <row r="630" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ630" s="4"/>
-    </row>
-    <row r="631" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT631"/>
-    </row>
-    <row r="632" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ632" s="4"/>
-    </row>
-    <row r="637" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT637"/>
-    </row>
-    <row r="638" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT638"/>
-      <c r="CJ638" s="4"/>
-    </row>
-    <row r="639" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ639" s="4"/>
-    </row>
-    <row r="640" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT640"/>
-    </row>
-    <row r="641" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT641"/>
-      <c r="CJ641" s="4"/>
-    </row>
-    <row r="642" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ642" s="4"/>
-    </row>
-    <row r="643" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT643"/>
-    </row>
-    <row r="644" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT644"/>
-      <c r="CJ644" s="4"/>
-    </row>
-    <row r="645" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT645"/>
-      <c r="CJ645" s="4"/>
-    </row>
-    <row r="646" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT646"/>
-      <c r="CJ646" s="4"/>
-    </row>
-    <row r="647" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ647" s="4"/>
-    </row>
-    <row r="651" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT651"/>
-    </row>
-    <row r="652" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT652"/>
-      <c r="CJ652" s="4"/>
-    </row>
-    <row r="653" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT653"/>
-      <c r="CJ653" s="4"/>
-    </row>
-    <row r="654" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ654" s="4"/>
-    </row>
-    <row r="655" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT655"/>
-    </row>
-    <row r="656" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ656" s="4"/>
-    </row>
-    <row r="657" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BS657" s="6"/>
-      <c r="BT657" s="7"/>
-    </row>
-    <row r="658" spans="8:88" x14ac:dyDescent="0.25">
+    <row r="602" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV602"/>
+    </row>
+    <row r="603" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV603"/>
+      <c r="CL603" s="4"/>
+    </row>
+    <row r="604" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV604"/>
+      <c r="CL604" s="4"/>
+    </row>
+    <row r="605" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV605"/>
+      <c r="CL605" s="4"/>
+    </row>
+    <row r="606" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV606"/>
+      <c r="CL606" s="4"/>
+    </row>
+    <row r="607" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV607"/>
+      <c r="CL607" s="4"/>
+    </row>
+    <row r="608" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV608"/>
+      <c r="CL608" s="4"/>
+    </row>
+    <row r="609" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV609"/>
+      <c r="CL609" s="4"/>
+    </row>
+    <row r="610" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV610"/>
+      <c r="CL610" s="4"/>
+    </row>
+    <row r="611" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL611" s="4"/>
+    </row>
+    <row r="612" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV612"/>
+    </row>
+    <row r="613" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL613" s="4"/>
+    </row>
+    <row r="622" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV622"/>
+    </row>
+    <row r="623" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV623"/>
+      <c r="CL623" s="4"/>
+    </row>
+    <row r="624" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV624"/>
+      <c r="CL624" s="4"/>
+    </row>
+    <row r="625" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV625"/>
+      <c r="CL625" s="4"/>
+    </row>
+    <row r="626" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV626"/>
+      <c r="CL626" s="4"/>
+    </row>
+    <row r="627" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV627"/>
+      <c r="CL627" s="4"/>
+    </row>
+    <row r="628" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV628"/>
+      <c r="CL628" s="4"/>
+    </row>
+    <row r="629" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV629"/>
+      <c r="CL629" s="4"/>
+    </row>
+    <row r="630" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL630" s="4"/>
+    </row>
+    <row r="631" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV631"/>
+    </row>
+    <row r="632" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL632" s="4"/>
+    </row>
+    <row r="637" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV637"/>
+    </row>
+    <row r="638" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV638"/>
+      <c r="CL638" s="4"/>
+    </row>
+    <row r="639" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL639" s="4"/>
+    </row>
+    <row r="640" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV640"/>
+    </row>
+    <row r="641" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV641"/>
+      <c r="CL641" s="4"/>
+    </row>
+    <row r="642" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL642" s="4"/>
+    </row>
+    <row r="643" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV643"/>
+    </row>
+    <row r="644" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV644"/>
+      <c r="CL644" s="4"/>
+    </row>
+    <row r="645" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV645"/>
+      <c r="CL645" s="4"/>
+    </row>
+    <row r="646" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV646"/>
+      <c r="CL646" s="4"/>
+    </row>
+    <row r="647" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL647" s="4"/>
+    </row>
+    <row r="651" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV651"/>
+    </row>
+    <row r="652" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV652"/>
+      <c r="CL652" s="4"/>
+    </row>
+    <row r="653" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV653"/>
+      <c r="CL653" s="4"/>
+    </row>
+    <row r="654" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL654" s="4"/>
+    </row>
+    <row r="655" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV655"/>
+    </row>
+    <row r="656" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL656" s="4"/>
+    </row>
+    <row r="657" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BU657" s="6"/>
+      <c r="BV657" s="7"/>
+    </row>
+    <row r="658" spans="8:90" x14ac:dyDescent="0.25">
       <c r="H658" s="6"/>
-      <c r="CJ658" s="6"/>
-    </row>
-    <row r="675" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT675"/>
-    </row>
-    <row r="676" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT676"/>
-      <c r="CJ676" s="4"/>
-    </row>
-    <row r="677" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT677"/>
-      <c r="CJ677" s="4"/>
-    </row>
-    <row r="678" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT678"/>
-      <c r="CJ678" s="4"/>
-    </row>
-    <row r="679" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="CJ679" s="4"/>
-    </row>
-    <row r="680" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT680"/>
-    </row>
-    <row r="681" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT681"/>
-      <c r="CJ681" s="4"/>
-    </row>
-    <row r="682" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BS682" s="6"/>
-      <c r="BT682" s="7"/>
-      <c r="CJ682" s="4"/>
-    </row>
-    <row r="683" spans="8:88" x14ac:dyDescent="0.25">
+      <c r="CL658" s="6"/>
+    </row>
+    <row r="675" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV675"/>
+    </row>
+    <row r="676" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV676"/>
+      <c r="CL676" s="4"/>
+    </row>
+    <row r="677" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV677"/>
+      <c r="CL677" s="4"/>
+    </row>
+    <row r="678" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV678"/>
+      <c r="CL678" s="4"/>
+    </row>
+    <row r="679" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="CL679" s="4"/>
+    </row>
+    <row r="680" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV680"/>
+    </row>
+    <row r="681" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV681"/>
+      <c r="CL681" s="4"/>
+    </row>
+    <row r="682" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BU682" s="6"/>
+      <c r="BV682" s="7"/>
+      <c r="CL682" s="4"/>
+    </row>
+    <row r="683" spans="8:90" x14ac:dyDescent="0.25">
       <c r="H683" s="6"/>
-      <c r="CJ683" s="6"/>
-    </row>
-    <row r="686" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT686"/>
-    </row>
-    <row r="687" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT687"/>
-      <c r="CJ687" s="4"/>
-    </row>
-    <row r="688" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT688"/>
-      <c r="CJ688" s="4"/>
-    </row>
-    <row r="689" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT689"/>
-      <c r="CJ689" s="4"/>
-    </row>
-    <row r="690" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT690"/>
-      <c r="CJ690" s="4"/>
-    </row>
-    <row r="691" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT691"/>
-      <c r="CJ691" s="4"/>
-    </row>
-    <row r="692" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT692"/>
-      <c r="CJ692" s="4"/>
-    </row>
-    <row r="693" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT693"/>
-      <c r="CJ693" s="4"/>
-    </row>
-    <row r="694" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ694" s="4"/>
-    </row>
-    <row r="696" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT696"/>
-    </row>
-    <row r="697" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT697"/>
-      <c r="CJ697" s="4"/>
-    </row>
-    <row r="698" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT698"/>
-      <c r="CJ698" s="4"/>
-    </row>
-    <row r="699" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT699"/>
-      <c r="CJ699" s="4"/>
-    </row>
-    <row r="700" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT700"/>
-      <c r="CJ700" s="4"/>
-    </row>
-    <row r="701" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT701"/>
-      <c r="CJ701" s="4"/>
-    </row>
-    <row r="702" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ702" s="4"/>
-    </row>
-    <row r="703" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT703"/>
-    </row>
-    <row r="704" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT704"/>
-      <c r="CJ704" s="4"/>
-    </row>
-    <row r="705" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT705"/>
-      <c r="CJ705" s="4"/>
-    </row>
-    <row r="706" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT706"/>
-      <c r="CJ706" s="4"/>
-    </row>
-    <row r="707" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT707"/>
-      <c r="CJ707" s="4"/>
-    </row>
-    <row r="708" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT708"/>
-      <c r="CJ708" s="4"/>
-    </row>
-    <row r="709" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT709"/>
-      <c r="CJ709" s="4"/>
-    </row>
-    <row r="710" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT710"/>
-      <c r="CJ710" s="4"/>
-    </row>
-    <row r="711" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT711"/>
-      <c r="CJ711" s="4"/>
-    </row>
-    <row r="712" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT712"/>
-      <c r="CJ712" s="4"/>
-    </row>
-    <row r="713" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT713"/>
-      <c r="CJ713" s="4"/>
-    </row>
-    <row r="714" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT714"/>
-      <c r="CJ714" s="4"/>
-    </row>
-    <row r="715" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT715"/>
-      <c r="CJ715" s="4"/>
-    </row>
-    <row r="716" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT716"/>
-      <c r="CJ716" s="4"/>
-    </row>
-    <row r="717" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT717"/>
-      <c r="CJ717" s="4"/>
-    </row>
-    <row r="718" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT718"/>
-      <c r="CJ718" s="4"/>
-    </row>
-    <row r="719" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT719"/>
-      <c r="CJ719" s="4"/>
-    </row>
-    <row r="720" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT720"/>
-      <c r="CJ720" s="4"/>
-    </row>
-    <row r="721" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT721"/>
-      <c r="CJ721" s="4"/>
-    </row>
-    <row r="722" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT722"/>
-      <c r="CJ722" s="4"/>
-    </row>
-    <row r="723" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT723"/>
-      <c r="CJ723" s="4"/>
-    </row>
-    <row r="724" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT724"/>
-      <c r="CJ724" s="4"/>
-    </row>
-    <row r="725" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT725"/>
-      <c r="CJ725" s="4"/>
-    </row>
-    <row r="726" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT726"/>
-      <c r="CJ726" s="4"/>
-    </row>
-    <row r="727" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT727"/>
-      <c r="CJ727" s="4"/>
-    </row>
-    <row r="728" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT728"/>
-      <c r="CJ728" s="4"/>
-    </row>
-    <row r="729" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT729"/>
-      <c r="CJ729" s="4"/>
-    </row>
-    <row r="730" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT730"/>
-      <c r="CJ730" s="4"/>
-    </row>
-    <row r="731" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT731"/>
-      <c r="CJ731" s="4"/>
-    </row>
-    <row r="732" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT732"/>
-      <c r="CJ732" s="4"/>
-    </row>
-    <row r="733" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ733" s="4"/>
-    </row>
-    <row r="734" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT734"/>
-    </row>
-    <row r="735" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT735"/>
-      <c r="CJ735" s="4"/>
-    </row>
-    <row r="736" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT736"/>
-      <c r="CJ736" s="4"/>
-    </row>
-    <row r="737" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ737" s="4"/>
+      <c r="CL683" s="6"/>
+    </row>
+    <row r="686" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV686"/>
+    </row>
+    <row r="687" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV687"/>
+      <c r="CL687" s="4"/>
+    </row>
+    <row r="688" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV688"/>
+      <c r="CL688" s="4"/>
+    </row>
+    <row r="689" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV689"/>
+      <c r="CL689" s="4"/>
+    </row>
+    <row r="690" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV690"/>
+      <c r="CL690" s="4"/>
+    </row>
+    <row r="691" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV691"/>
+      <c r="CL691" s="4"/>
+    </row>
+    <row r="692" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV692"/>
+      <c r="CL692" s="4"/>
+    </row>
+    <row r="693" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV693"/>
+      <c r="CL693" s="4"/>
+    </row>
+    <row r="694" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL694" s="4"/>
+    </row>
+    <row r="696" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV696"/>
+    </row>
+    <row r="697" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV697"/>
+      <c r="CL697" s="4"/>
+    </row>
+    <row r="698" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV698"/>
+      <c r="CL698" s="4"/>
+    </row>
+    <row r="699" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV699"/>
+      <c r="CL699" s="4"/>
+    </row>
+    <row r="700" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV700"/>
+      <c r="CL700" s="4"/>
+    </row>
+    <row r="701" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV701"/>
+      <c r="CL701" s="4"/>
+    </row>
+    <row r="702" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL702" s="4"/>
+    </row>
+    <row r="703" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV703"/>
+    </row>
+    <row r="704" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV704"/>
+      <c r="CL704" s="4"/>
+    </row>
+    <row r="705" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV705"/>
+      <c r="CL705" s="4"/>
+    </row>
+    <row r="706" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV706"/>
+      <c r="CL706" s="4"/>
+    </row>
+    <row r="707" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV707"/>
+      <c r="CL707" s="4"/>
+    </row>
+    <row r="708" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV708"/>
+      <c r="CL708" s="4"/>
+    </row>
+    <row r="709" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV709"/>
+      <c r="CL709" s="4"/>
+    </row>
+    <row r="710" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV710"/>
+      <c r="CL710" s="4"/>
+    </row>
+    <row r="711" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV711"/>
+      <c r="CL711" s="4"/>
+    </row>
+    <row r="712" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV712"/>
+      <c r="CL712" s="4"/>
+    </row>
+    <row r="713" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV713"/>
+      <c r="CL713" s="4"/>
+    </row>
+    <row r="714" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV714"/>
+      <c r="CL714" s="4"/>
+    </row>
+    <row r="715" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV715"/>
+      <c r="CL715" s="4"/>
+    </row>
+    <row r="716" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV716"/>
+      <c r="CL716" s="4"/>
+    </row>
+    <row r="717" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV717"/>
+      <c r="CL717" s="4"/>
+    </row>
+    <row r="718" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV718"/>
+      <c r="CL718" s="4"/>
+    </row>
+    <row r="719" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV719"/>
+      <c r="CL719" s="4"/>
+    </row>
+    <row r="720" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV720"/>
+      <c r="CL720" s="4"/>
+    </row>
+    <row r="721" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV721"/>
+      <c r="CL721" s="4"/>
+    </row>
+    <row r="722" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV722"/>
+      <c r="CL722" s="4"/>
+    </row>
+    <row r="723" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV723"/>
+      <c r="CL723" s="4"/>
+    </row>
+    <row r="724" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV724"/>
+      <c r="CL724" s="4"/>
+    </row>
+    <row r="725" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV725"/>
+      <c r="CL725" s="4"/>
+    </row>
+    <row r="726" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV726"/>
+      <c r="CL726" s="4"/>
+    </row>
+    <row r="727" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV727"/>
+      <c r="CL727" s="4"/>
+    </row>
+    <row r="728" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV728"/>
+      <c r="CL728" s="4"/>
+    </row>
+    <row r="729" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV729"/>
+      <c r="CL729" s="4"/>
+    </row>
+    <row r="730" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV730"/>
+      <c r="CL730" s="4"/>
+    </row>
+    <row r="731" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV731"/>
+      <c r="CL731" s="4"/>
+    </row>
+    <row r="732" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV732"/>
+      <c r="CL732" s="4"/>
+    </row>
+    <row r="733" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL733" s="4"/>
+    </row>
+    <row r="734" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV734"/>
+    </row>
+    <row r="735" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV735"/>
+      <c r="CL735" s="4"/>
+    </row>
+    <row r="736" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV736"/>
+      <c r="CL736" s="4"/>
+    </row>
+    <row r="737" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL737" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="9" type="noConversion"/>

--- a/Excel/一方通行/斩业星熊.xlsx
+++ b/Excel/一方通行/斩业星熊.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\一方通行\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF7D36AA-0C5C-4286-8A26-AA011B6CCA3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4611D3D-0020-4CB6-8AA4-9E9983E7F095}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CardData" sheetId="10" r:id="rId1"/>
@@ -299,7 +299,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="906" uniqueCount="540">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="909" uniqueCount="540">
   <si>
     <t>Id</t>
   </si>
@@ -9802,16 +9802,21 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A2:I3"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.25" customWidth="1"/>
     <col min="3" max="3" width="27.25" customWidth="1"/>
     <col min="4" max="4" width="10.83203125" customWidth="1"/>
-    <col min="9" max="9" width="9" customWidth="1"/>
+    <col min="10" max="10" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I1" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -9837,10 +9842,13 @@
         <v>475</v>
       </c>
       <c r="I2" t="s">
+        <v>323</v>
+      </c>
+      <c r="J2" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -9866,6 +9874,9 @@
         <v>118</v>
       </c>
       <c r="I3" t="s">
+        <v>363</v>
+      </c>
+      <c r="J3" t="s">
         <v>125</v>
       </c>
     </row>

--- a/Excel/一方通行/斩业星熊.xlsx
+++ b/Excel/一方通行/斩业星熊.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\一方通行\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4611D3D-0020-4CB6-8AA4-9E9983E7F095}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{710B858B-D939-488D-B2EF-C9FB7785981F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CardData" sheetId="10" r:id="rId1"/>
@@ -299,7 +299,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="909" uniqueCount="540">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="909" uniqueCount="541">
   <si>
     <t>Id</t>
   </si>
@@ -1936,6 +1936,9 @@
   <si>
     <t>string</t>
     <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>char_1044_hsgma2</t>
   </si>
 </sst>
 </file>
@@ -3048,7 +3051,7 @@
       </c>
       <c r="E4" s="8"/>
       <c r="F4" s="1" t="s">
-        <v>4</v>
+        <v>540</v>
       </c>
       <c r="G4">
         <v>1</v>

--- a/Excel/一方通行/斩业星熊.xlsx
+++ b/Excel/一方通行/斩业星熊.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\一方通行\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{710B858B-D939-488D-B2EF-C9FB7785981F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9808A396-E709-464C-B700-93FA7C2A9265}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -299,7 +299,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="909" uniqueCount="541">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="907" uniqueCount="541">
   <si>
     <t>Id</t>
   </si>
@@ -388,12 +388,6 @@
     <t>高度</t>
   </si>
   <si>
-    <t>高台单位？</t>
-  </si>
-  <si>
-    <t>地面</t>
-  </si>
-  <si>
     <t>阻挡个数</t>
   </si>
   <si>
@@ -548,12 +542,6 @@
   </si>
   <si>
     <t>Height</t>
-  </si>
-  <si>
-    <t>CanSetHigh</t>
-  </si>
-  <si>
-    <t>CanSetGround</t>
   </si>
   <si>
     <t>StopCount</t>
@@ -1939,6 +1927,22 @@
   </si>
   <si>
     <t>char_1044_hsgma2</t>
+  </si>
+  <si>
+    <t>可部署位</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>CanSetPos</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>string[]</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>地面位</t>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2448,7 +2452,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:BS583"/>
+  <dimension ref="A1:BR583"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.58203125" customWidth="1"/>
@@ -2478,22 +2482,22 @@
     <col min="34" max="34" width="13.83203125" customWidth="1"/>
     <col min="35" max="35" width="34.5" customWidth="1"/>
     <col min="36" max="37" width="9.83203125" customWidth="1"/>
-    <col min="43" max="43" width="12.5" customWidth="1"/>
-    <col min="50" max="50" width="24.33203125" customWidth="1"/>
-    <col min="52" max="52" width="17.75" customWidth="1"/>
-    <col min="53" max="53" width="7.83203125" customWidth="1"/>
-    <col min="56" max="56" width="24.25" customWidth="1"/>
-    <col min="57" max="57" width="13.25" customWidth="1"/>
-    <col min="58" max="58" width="16.08203125" customWidth="1"/>
-    <col min="59" max="59" width="8" customWidth="1"/>
-    <col min="64" max="64" width="39.58203125" customWidth="1"/>
-    <col min="65" max="65" width="14" customWidth="1"/>
-    <col min="66" max="66" width="14.83203125" customWidth="1"/>
-    <col min="67" max="70" width="14" customWidth="1"/>
-    <col min="71" max="71" width="19.1640625" customWidth="1"/>
+    <col min="42" max="42" width="12.5" customWidth="1"/>
+    <col min="49" max="49" width="24.33203125" customWidth="1"/>
+    <col min="51" max="51" width="17.75" customWidth="1"/>
+    <col min="52" max="52" width="7.83203125" customWidth="1"/>
+    <col min="55" max="55" width="24.25" customWidth="1"/>
+    <col min="56" max="56" width="13.25" customWidth="1"/>
+    <col min="57" max="57" width="16.08203125" customWidth="1"/>
+    <col min="58" max="58" width="8" customWidth="1"/>
+    <col min="63" max="63" width="39.58203125" customWidth="1"/>
+    <col min="64" max="64" width="14" customWidth="1"/>
+    <col min="65" max="65" width="14.83203125" customWidth="1"/>
+    <col min="66" max="69" width="14" customWidth="1"/>
+    <col min="70" max="70" width="19.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="D1" t="s">
         <v>5</v>
       </c>
@@ -2569,274 +2573,268 @@
       <c r="AL1" t="s">
         <v>28</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AM1" s="13" t="s">
+        <v>537</v>
+      </c>
+      <c r="AN1" t="s">
         <v>29</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AO1" t="s">
         <v>30</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AP1" t="s">
         <v>31</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AR1" t="s">
         <v>32</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AS1" t="s">
         <v>33</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AT1" t="s">
         <v>34</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AU1" t="s">
         <v>35</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AV1" t="s">
         <v>36</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AW1" t="s">
         <v>37</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AX1" t="s">
         <v>38</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AY1" t="s">
         <v>39</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="AZ1" t="s">
         <v>40</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="BC1" t="s">
         <v>41</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BD1" t="s">
         <v>42</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BE1" t="s">
         <v>43</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BF1" t="s">
         <v>44</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BG1" t="s">
         <v>45</v>
       </c>
-      <c r="BG1" t="s">
-        <v>46</v>
-      </c>
-      <c r="BH1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="2" spans="1:71" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F2" t="s">
         <v>48</v>
       </c>
-      <c r="C2" t="s">
+      <c r="G2" t="s">
         <v>49</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" t="s">
         <v>50</v>
       </c>
-      <c r="G2" t="s">
+      <c r="I2" t="s">
         <v>51</v>
       </c>
-      <c r="H2" t="s">
+      <c r="J2" t="s">
         <v>52</v>
       </c>
-      <c r="I2" t="s">
+      <c r="K2" t="s">
         <v>53</v>
       </c>
-      <c r="J2" t="s">
+      <c r="L2" t="s">
         <v>54</v>
       </c>
-      <c r="K2" t="s">
+      <c r="M2" t="s">
         <v>55</v>
       </c>
-      <c r="L2" t="s">
+      <c r="N2" t="s">
         <v>56</v>
       </c>
-      <c r="M2" t="s">
+      <c r="O2" t="s">
         <v>57</v>
       </c>
-      <c r="N2" t="s">
+      <c r="P2" t="s">
         <v>58</v>
       </c>
-      <c r="O2" t="s">
+      <c r="Q2" t="s">
         <v>59</v>
       </c>
-      <c r="P2" t="s">
+      <c r="R2" t="s">
         <v>60</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="S2" t="s">
         <v>61</v>
       </c>
-      <c r="R2" t="s">
+      <c r="T2" t="s">
         <v>62</v>
       </c>
-      <c r="S2" t="s">
+      <c r="U2" t="s">
         <v>63</v>
       </c>
-      <c r="T2" t="s">
+      <c r="V2" t="s">
         <v>64</v>
       </c>
-      <c r="U2" t="s">
+      <c r="W2" t="s">
         <v>65</v>
       </c>
-      <c r="V2" t="s">
+      <c r="X2" t="s">
         <v>66</v>
       </c>
-      <c r="W2" t="s">
+      <c r="Y2" t="s">
         <v>67</v>
       </c>
-      <c r="X2" t="s">
+      <c r="Z2" t="s">
         <v>68</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="AA2" t="s">
         <v>69</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="AB2" t="s">
         <v>70</v>
       </c>
-      <c r="AA2" t="s">
+      <c r="AC2" t="s">
         <v>71</v>
       </c>
-      <c r="AB2" t="s">
+      <c r="AD2" t="s">
         <v>72</v>
       </c>
-      <c r="AC2" t="s">
+      <c r="AE2" t="s">
         <v>73</v>
       </c>
-      <c r="AD2" t="s">
+      <c r="AF2" t="s">
         <v>74</v>
       </c>
-      <c r="AE2" t="s">
+      <c r="AG2" t="s">
         <v>75</v>
       </c>
-      <c r="AF2" t="s">
+      <c r="AH2" t="s">
         <v>76</v>
       </c>
-      <c r="AG2" t="s">
+      <c r="AI2" t="s">
         <v>77</v>
       </c>
-      <c r="AH2" t="s">
+      <c r="AJ2" t="s">
         <v>78</v>
       </c>
-      <c r="AI2" t="s">
+      <c r="AK2" t="s">
         <v>79</v>
       </c>
-      <c r="AJ2" t="s">
+      <c r="AL2" t="s">
         <v>80</v>
       </c>
-      <c r="AK2" t="s">
+      <c r="AM2" s="13" t="s">
+        <v>538</v>
+      </c>
+      <c r="AN2" t="s">
         <v>81</v>
       </c>
-      <c r="AL2" t="s">
+      <c r="AO2" t="s">
         <v>82</v>
       </c>
-      <c r="AM2" t="s">
+      <c r="AP2" t="s">
         <v>83</v>
       </c>
-      <c r="AN2" t="s">
+      <c r="AQ2" t="s">
         <v>84</v>
       </c>
-      <c r="AO2" t="s">
+      <c r="AR2" t="s">
         <v>85</v>
       </c>
-      <c r="AP2" t="s">
+      <c r="AS2" t="s">
         <v>86</v>
       </c>
-      <c r="AQ2" t="s">
+      <c r="AT2" t="s">
         <v>87</v>
       </c>
-      <c r="AR2" t="s">
+      <c r="AU2" t="s">
         <v>88</v>
       </c>
-      <c r="AS2" t="s">
+      <c r="AV2" t="s">
         <v>89</v>
       </c>
-      <c r="AT2" t="s">
+      <c r="AW2" t="s">
         <v>90</v>
       </c>
-      <c r="AU2" t="s">
+      <c r="AX2" t="s">
         <v>91</v>
       </c>
-      <c r="AV2" t="s">
+      <c r="AY2" t="s">
         <v>92</v>
       </c>
-      <c r="AW2" t="s">
+      <c r="AZ2" t="s">
         <v>93</v>
       </c>
-      <c r="AX2" t="s">
+      <c r="BA2" t="s">
         <v>94</v>
       </c>
-      <c r="AY2" t="s">
+      <c r="BB2" t="s">
         <v>95</v>
       </c>
-      <c r="AZ2" t="s">
+      <c r="BC2" t="s">
         <v>96</v>
       </c>
-      <c r="BA2" t="s">
+      <c r="BD2" t="s">
         <v>97</v>
       </c>
-      <c r="BB2" t="s">
+      <c r="BE2" t="s">
         <v>98</v>
       </c>
-      <c r="BC2" t="s">
+      <c r="BF2" t="s">
         <v>99</v>
       </c>
-      <c r="BD2" t="s">
+      <c r="BG2" t="s">
         <v>100</v>
       </c>
-      <c r="BE2" t="s">
+      <c r="BH2" t="s">
         <v>101</v>
       </c>
-      <c r="BF2" t="s">
+      <c r="BI2" t="s">
         <v>102</v>
       </c>
-      <c r="BG2" t="s">
+      <c r="BJ2" t="s">
         <v>103</v>
       </c>
-      <c r="BH2" t="s">
+      <c r="BK2" t="s">
         <v>104</v>
       </c>
-      <c r="BI2" t="s">
+      <c r="BL2" t="s">
         <v>105</v>
       </c>
-      <c r="BJ2" t="s">
+      <c r="BM2" t="s">
         <v>106</v>
       </c>
-      <c r="BK2" t="s">
+      <c r="BN2" t="s">
         <v>107</v>
       </c>
-      <c r="BL2" t="s">
+      <c r="BO2" t="s">
         <v>108</v>
       </c>
-      <c r="BM2" t="s">
+      <c r="BP2" t="s">
         <v>109</v>
       </c>
-      <c r="BN2" t="s">
+      <c r="BQ2" t="s">
         <v>110</v>
       </c>
-      <c r="BO2" t="s">
+      <c r="BR2" t="s">
         <v>111</v>
       </c>
-      <c r="BP2" t="s">
-        <v>112</v>
-      </c>
-      <c r="BQ2" t="s">
-        <v>113</v>
-      </c>
-      <c r="BR2" t="s">
-        <v>114</v>
-      </c>
-      <c r="BS2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="3" spans="1:71" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -2844,88 +2842,88 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="F3" t="s">
         <v>2</v>
       </c>
       <c r="G3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="H3" t="s">
         <v>2</v>
       </c>
       <c r="I3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="J3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="K3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="L3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="M3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="N3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="O3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="P3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="Q3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="R3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="S3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="T3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="U3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="V3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="W3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="X3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="Y3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="Z3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="AA3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="AB3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="AC3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="AD3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="AE3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="AF3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="AG3" t="s">
         <v>2</v>
@@ -2934,61 +2932,61 @@
         <v>2</v>
       </c>
       <c r="AI3" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="AJ3" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="AK3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="AL3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AM3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AM3" s="13" t="s">
+        <v>539</v>
+      </c>
+      <c r="AN3" t="s">
+        <v>114</v>
+      </c>
+      <c r="AO3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AP3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AR3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AS3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AT3" t="s">
+        <v>114</v>
+      </c>
+      <c r="AU3" t="s">
         <v>116</v>
       </c>
-      <c r="AN3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AO3" t="s">
-        <v>118</v>
-      </c>
-      <c r="AP3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AQ3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AS3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AT3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AU3" t="s">
-        <v>118</v>
-      </c>
       <c r="AV3" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="AW3" t="s">
         <v>117</v>
       </c>
       <c r="AX3" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="AY3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="AZ3" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="BA3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="BB3" t="s">
-        <v>122</v>
+        <v>2</v>
       </c>
       <c r="BC3" t="s">
         <v>2</v>
@@ -3000,58 +2998,55 @@
         <v>2</v>
       </c>
       <c r="BF3" t="s">
+        <v>119</v>
+      </c>
+      <c r="BG3" t="s">
+        <v>114</v>
+      </c>
+      <c r="BH3" t="s">
         <v>2</v>
       </c>
-      <c r="BG3" t="s">
-        <v>123</v>
-      </c>
-      <c r="BH3" t="s">
-        <v>118</v>
-      </c>
       <c r="BI3" t="s">
+        <v>120</v>
+      </c>
+      <c r="BJ3" t="s">
         <v>2</v>
       </c>
-      <c r="BJ3" t="s">
-        <v>124</v>
-      </c>
       <c r="BK3" t="s">
-        <v>2</v>
+        <v>121</v>
       </c>
       <c r="BL3" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="BM3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="BN3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="BO3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="BP3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="BQ3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="BR3" t="s">
-        <v>124</v>
-      </c>
-      <c r="BS3" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="4" spans="1:71" x14ac:dyDescent="0.25">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="4" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="E4" s="8"/>
       <c r="F4" s="1" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -3096,2418 +3091,2424 @@
         <v>4</v>
       </c>
       <c r="AH4" t="s">
+        <v>123</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>124</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>125</v>
+      </c>
+      <c r="AM4" s="13" t="s">
+        <v>540</v>
+      </c>
+      <c r="AN4">
+        <v>3</v>
+      </c>
+      <c r="AO4">
+        <v>0.5</v>
+      </c>
+      <c r="AV4">
+        <v>0.25</v>
+      </c>
+      <c r="BA4" t="s">
+        <v>126</v>
+      </c>
+      <c r="BB4" t="s">
         <v>127</v>
       </c>
-      <c r="AI4" t="s">
+      <c r="BC4" t="s">
         <v>128</v>
       </c>
-      <c r="AJ4" t="s">
+      <c r="BD4" t="s">
         <v>129</v>
       </c>
-      <c r="AN4">
-        <v>1</v>
-      </c>
-      <c r="AO4">
-        <v>3</v>
-      </c>
-      <c r="AP4">
-        <v>0.5</v>
-      </c>
-      <c r="AW4">
-        <v>0.25</v>
-      </c>
-      <c r="BB4" t="s">
+      <c r="BE4" t="s">
         <v>130</v>
       </c>
-      <c r="BC4" t="s">
+      <c r="BF4" t="s">
         <v>131</v>
       </c>
-      <c r="BD4" t="s">
+      <c r="BG4">
+        <v>6</v>
+      </c>
+      <c r="BH4" t="s">
         <v>132</v>
       </c>
-      <c r="BE4" t="s">
+      <c r="BI4" t="s">
         <v>133</v>
       </c>
-      <c r="BF4" t="s">
+      <c r="BL4" t="s">
         <v>134</v>
       </c>
-      <c r="BG4" t="s">
+      <c r="BM4" t="s">
         <v>135</v>
       </c>
-      <c r="BH4">
-        <v>6</v>
-      </c>
-      <c r="BI4" t="s">
+      <c r="BO4" t="s">
         <v>136</v>
       </c>
-      <c r="BJ4" t="s">
-        <v>137</v>
-      </c>
-      <c r="BM4" t="s">
-        <v>138</v>
-      </c>
-      <c r="BN4" t="s">
-        <v>139</v>
-      </c>
       <c r="BP4" t="s">
-        <v>140</v>
-      </c>
-      <c r="BQ4" t="s">
-        <v>140</v>
-      </c>
-      <c r="BS4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+        <v>136</v>
+      </c>
+      <c r="BR4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:70" x14ac:dyDescent="0.25">
+      <c r="AM5" s="13"/>
+    </row>
+    <row r="6" spans="1:70" x14ac:dyDescent="0.25">
+      <c r="AM6" s="13"/>
+    </row>
+    <row r="21" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D21" s="9"/>
       <c r="E21" s="10"/>
-      <c r="BO21" s="11"/>
-      <c r="BR21" s="11"/>
-    </row>
-    <row r="22" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN21" s="11"/>
+      <c r="BQ21" s="11"/>
+    </row>
+    <row r="22" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D22" s="9"/>
       <c r="E22" s="10"/>
-      <c r="BO22" s="11"/>
-      <c r="BR22" s="11"/>
-    </row>
-    <row r="23" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN22" s="11"/>
+      <c r="BQ22" s="11"/>
+    </row>
+    <row r="23" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D23" s="9"/>
       <c r="E23" s="10"/>
-      <c r="BO23" s="11"/>
-      <c r="BR23" s="11"/>
-    </row>
-    <row r="24" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN23" s="11"/>
+      <c r="BQ23" s="11"/>
+    </row>
+    <row r="24" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D24" s="9"/>
       <c r="E24" s="10"/>
-      <c r="BO24" s="11"/>
-      <c r="BR24" s="11"/>
-    </row>
-    <row r="25" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN24" s="11"/>
+      <c r="BQ24" s="11"/>
+    </row>
+    <row r="25" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D25" s="9"/>
       <c r="E25" s="10"/>
-      <c r="BO25" s="11"/>
-      <c r="BR25" s="11"/>
-    </row>
-    <row r="26" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN25" s="11"/>
+      <c r="BQ25" s="11"/>
+    </row>
+    <row r="26" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D26" s="9"/>
       <c r="E26" s="10"/>
-      <c r="BO26" s="11"/>
-      <c r="BR26" s="11"/>
-    </row>
-    <row r="27" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN26" s="11"/>
+      <c r="BQ26" s="11"/>
+    </row>
+    <row r="27" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D27" s="9"/>
       <c r="E27" s="10"/>
-      <c r="BO27" s="11"/>
-      <c r="BR27" s="11"/>
-    </row>
-    <row r="28" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN27" s="11"/>
+      <c r="BQ27" s="11"/>
+    </row>
+    <row r="28" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D28" s="9"/>
       <c r="E28" s="10"/>
-      <c r="BR28" s="11"/>
-    </row>
-    <row r="29" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ28" s="11"/>
+    </row>
+    <row r="29" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D29" s="9"/>
       <c r="E29" s="10"/>
-      <c r="BR29" s="11"/>
-    </row>
-    <row r="30" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ29" s="11"/>
+    </row>
+    <row r="30" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D30" s="9"/>
       <c r="E30" s="10"/>
-      <c r="BR30" s="11"/>
-    </row>
-    <row r="31" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ30" s="11"/>
+    </row>
+    <row r="31" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D31" s="9"/>
       <c r="E31" s="10"/>
-      <c r="BO31" s="11"/>
-      <c r="BR31" s="11"/>
-    </row>
-    <row r="32" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN31" s="11"/>
+      <c r="BQ31" s="11"/>
+    </row>
+    <row r="32" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D32" s="9"/>
       <c r="E32" s="10"/>
-      <c r="BO32" s="11"/>
-      <c r="BR32" s="11"/>
-    </row>
-    <row r="33" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN32" s="11"/>
+      <c r="BQ32" s="11"/>
+    </row>
+    <row r="33" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D33" s="9"/>
       <c r="E33" s="10"/>
-      <c r="BO33" s="11"/>
-      <c r="BR33" s="11"/>
-    </row>
-    <row r="34" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN33" s="11"/>
+      <c r="BQ33" s="11"/>
+    </row>
+    <row r="34" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D34" s="9"/>
       <c r="E34" s="10"/>
-      <c r="BO34" s="11"/>
-      <c r="BR34" s="11"/>
-    </row>
-    <row r="35" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN34" s="11"/>
+      <c r="BQ34" s="11"/>
+    </row>
+    <row r="35" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D35" s="9"/>
       <c r="E35" s="10"/>
-      <c r="BO35" s="11"/>
-      <c r="BR35" s="11"/>
-    </row>
-    <row r="36" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN35" s="11"/>
+      <c r="BQ35" s="11"/>
+    </row>
+    <row r="36" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D36" s="9"/>
       <c r="E36" s="10"/>
-      <c r="BO36" s="11"/>
-      <c r="BR36" s="11"/>
-    </row>
-    <row r="37" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN36" s="11"/>
+      <c r="BQ36" s="11"/>
+    </row>
+    <row r="37" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D37" s="9"/>
       <c r="E37" s="10"/>
-      <c r="BO37" s="11"/>
-      <c r="BR37" s="11"/>
-    </row>
-    <row r="38" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN37" s="11"/>
+      <c r="BQ37" s="11"/>
+    </row>
+    <row r="38" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D38" s="9"/>
       <c r="E38" s="10"/>
-      <c r="BO38" s="11"/>
-      <c r="BR38" s="11"/>
-    </row>
-    <row r="39" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN38" s="11"/>
+      <c r="BQ38" s="11"/>
+    </row>
+    <row r="39" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D39" s="9"/>
       <c r="E39" s="10"/>
-      <c r="BO39" s="11"/>
-      <c r="BR39" s="11"/>
-    </row>
-    <row r="40" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN39" s="11"/>
+      <c r="BQ39" s="11"/>
+    </row>
+    <row r="40" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D40" s="9"/>
       <c r="E40" s="10"/>
-      <c r="BO40" s="11"/>
-      <c r="BR40" s="11"/>
-    </row>
-    <row r="41" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN40" s="11"/>
+      <c r="BQ40" s="11"/>
+    </row>
+    <row r="41" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D41" s="9"/>
       <c r="E41" s="10"/>
-      <c r="BO41" s="11"/>
-      <c r="BR41" s="11"/>
-    </row>
-    <row r="42" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN41" s="11"/>
+      <c r="BQ41" s="11"/>
+    </row>
+    <row r="42" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D42" s="9"/>
       <c r="E42" s="10"/>
-      <c r="BO42" s="11"/>
-      <c r="BR42" s="11"/>
-    </row>
-    <row r="43" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN42" s="11"/>
+      <c r="BQ42" s="11"/>
+    </row>
+    <row r="43" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D43" s="9"/>
       <c r="E43" s="10"/>
-      <c r="BO43" s="11"/>
-      <c r="BR43" s="11"/>
-    </row>
-    <row r="44" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN43" s="11"/>
+      <c r="BQ43" s="11"/>
+    </row>
+    <row r="44" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D44" s="9"/>
       <c r="E44" s="10"/>
-      <c r="BO44" s="11"/>
-      <c r="BR44" s="11"/>
-    </row>
-    <row r="45" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN44" s="11"/>
+      <c r="BQ44" s="11"/>
+    </row>
+    <row r="45" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D45" s="9"/>
       <c r="E45" s="10"/>
-      <c r="BO45" s="11"/>
-      <c r="BR45" s="11"/>
-    </row>
-    <row r="46" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN45" s="11"/>
+      <c r="BQ45" s="11"/>
+    </row>
+    <row r="46" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D46" s="9"/>
       <c r="E46" s="10"/>
-      <c r="BO46" s="11"/>
-      <c r="BR46" s="11"/>
-    </row>
-    <row r="47" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN46" s="11"/>
+      <c r="BQ46" s="11"/>
+    </row>
+    <row r="47" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D47" s="9"/>
       <c r="E47" s="10"/>
-      <c r="BO47" s="11"/>
-      <c r="BR47" s="11"/>
-    </row>
-    <row r="48" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN47" s="11"/>
+      <c r="BQ47" s="11"/>
+    </row>
+    <row r="48" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D48" s="9"/>
       <c r="E48" s="10"/>
-      <c r="BO48" s="11"/>
-      <c r="BR48" s="11"/>
-    </row>
-    <row r="49" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN48" s="11"/>
+      <c r="BQ48" s="11"/>
+    </row>
+    <row r="49" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D49" s="9"/>
       <c r="E49" s="10"/>
-      <c r="BO49" s="11"/>
-      <c r="BR49" s="11"/>
-    </row>
-    <row r="50" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN49" s="11"/>
+      <c r="BQ49" s="11"/>
+    </row>
+    <row r="50" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D50" s="9"/>
       <c r="E50" s="10"/>
-      <c r="BO50" s="11"/>
-      <c r="BR50" s="11"/>
-    </row>
-    <row r="51" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN50" s="11"/>
+      <c r="BQ50" s="11"/>
+    </row>
+    <row r="51" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D51" s="9"/>
       <c r="E51" s="10"/>
-      <c r="BO51" s="11"/>
-      <c r="BR51" s="11"/>
-    </row>
-    <row r="52" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN51" s="11"/>
+      <c r="BQ51" s="11"/>
+    </row>
+    <row r="52" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D52" s="9"/>
       <c r="E52" s="10"/>
-      <c r="BO52" s="11"/>
-      <c r="BR52" s="11"/>
-    </row>
-    <row r="53" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN52" s="11"/>
+      <c r="BQ52" s="11"/>
+    </row>
+    <row r="53" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D53" s="9"/>
       <c r="E53" s="10"/>
-      <c r="BO53" s="11"/>
-      <c r="BR53" s="11"/>
-    </row>
-    <row r="54" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN53" s="11"/>
+      <c r="BQ53" s="11"/>
+    </row>
+    <row r="54" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D54" s="9"/>
       <c r="E54" s="10"/>
-      <c r="BO54" s="11"/>
-      <c r="BR54" s="11"/>
-    </row>
-    <row r="55" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN54" s="11"/>
+      <c r="BQ54" s="11"/>
+    </row>
+    <row r="55" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D55" s="9"/>
       <c r="E55" s="10"/>
-      <c r="BO55" s="11"/>
-      <c r="BR55" s="11"/>
-    </row>
-    <row r="56" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN55" s="11"/>
+      <c r="BQ55" s="11"/>
+    </row>
+    <row r="56" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D56" s="9"/>
       <c r="E56" s="10"/>
-      <c r="BO56" s="11"/>
-      <c r="BR56" s="11"/>
-    </row>
-    <row r="57" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN56" s="11"/>
+      <c r="BQ56" s="11"/>
+    </row>
+    <row r="57" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D57" s="9"/>
       <c r="E57" s="10"/>
-      <c r="BO57" s="11"/>
-      <c r="BR57" s="11"/>
-    </row>
-    <row r="58" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN57" s="11"/>
+      <c r="BQ57" s="11"/>
+    </row>
+    <row r="58" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D58" s="9"/>
       <c r="E58" s="10"/>
-      <c r="BO58" s="11"/>
-      <c r="BR58" s="11"/>
-    </row>
-    <row r="59" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN58" s="11"/>
+      <c r="BQ58" s="11"/>
+    </row>
+    <row r="59" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D59" s="9"/>
       <c r="E59" s="10"/>
-      <c r="BO59" s="11"/>
-      <c r="BR59" s="11"/>
-    </row>
-    <row r="60" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN59" s="11"/>
+      <c r="BQ59" s="11"/>
+    </row>
+    <row r="60" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D60" s="9"/>
       <c r="E60" s="10"/>
-      <c r="BO60" s="11"/>
-      <c r="BR60" s="11"/>
-    </row>
-    <row r="61" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN60" s="11"/>
+      <c r="BQ60" s="11"/>
+    </row>
+    <row r="61" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D61" s="9"/>
       <c r="E61" s="10"/>
-      <c r="BO61" s="11"/>
-      <c r="BR61" s="11"/>
-    </row>
-    <row r="62" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN61" s="11"/>
+      <c r="BQ61" s="11"/>
+    </row>
+    <row r="62" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D62" s="9"/>
       <c r="E62" s="10"/>
-      <c r="BO62" s="11"/>
-      <c r="BR62" s="11"/>
-    </row>
-    <row r="63" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN62" s="11"/>
+      <c r="BQ62" s="11"/>
+    </row>
+    <row r="63" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D63" s="9"/>
       <c r="E63" s="10"/>
-      <c r="BO63" s="11"/>
-      <c r="BR63" s="11"/>
-    </row>
-    <row r="64" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN63" s="11"/>
+      <c r="BQ63" s="11"/>
+    </row>
+    <row r="64" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D64" s="9"/>
       <c r="E64" s="10"/>
-      <c r="BO64" s="11"/>
-      <c r="BR64" s="11"/>
-    </row>
-    <row r="65" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN64" s="11"/>
+      <c r="BQ64" s="11"/>
+    </row>
+    <row r="65" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D65" s="9"/>
       <c r="E65" s="10"/>
-      <c r="BO65" s="11"/>
-      <c r="BR65" s="11"/>
-    </row>
-    <row r="66" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN65" s="11"/>
+      <c r="BQ65" s="11"/>
+    </row>
+    <row r="66" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D66" s="9"/>
       <c r="E66" s="10"/>
-      <c r="BO66" s="11"/>
-      <c r="BR66" s="11"/>
-    </row>
-    <row r="67" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN66" s="11"/>
+      <c r="BQ66" s="11"/>
+    </row>
+    <row r="67" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D67" s="9"/>
       <c r="E67" s="10"/>
-      <c r="BO67" s="11"/>
-      <c r="BR67" s="11"/>
-    </row>
-    <row r="68" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN67" s="11"/>
+      <c r="BQ67" s="11"/>
+    </row>
+    <row r="68" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D68" s="9"/>
       <c r="E68" s="10"/>
-      <c r="BO68" s="11"/>
-      <c r="BR68" s="11"/>
-    </row>
-    <row r="69" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN68" s="11"/>
+      <c r="BQ68" s="11"/>
+    </row>
+    <row r="69" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D69" s="9"/>
       <c r="E69" s="10"/>
-      <c r="BO69" s="11"/>
-      <c r="BR69" s="11"/>
-    </row>
-    <row r="70" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN69" s="11"/>
+      <c r="BQ69" s="11"/>
+    </row>
+    <row r="70" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D70" s="9"/>
       <c r="E70" s="10"/>
-      <c r="BO70" s="11"/>
-      <c r="BR70" s="11"/>
-    </row>
-    <row r="71" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN70" s="11"/>
+      <c r="BQ70" s="11"/>
+    </row>
+    <row r="71" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D71" s="9"/>
       <c r="E71" s="10"/>
-      <c r="BO71" s="11"/>
-      <c r="BR71" s="11"/>
-    </row>
-    <row r="72" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN71" s="11"/>
+      <c r="BQ71" s="11"/>
+    </row>
+    <row r="72" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D72" s="9"/>
       <c r="E72" s="10"/>
-      <c r="BO72" s="11"/>
-      <c r="BR72" s="11"/>
-    </row>
-    <row r="73" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN72" s="11"/>
+      <c r="BQ72" s="11"/>
+    </row>
+    <row r="73" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D73" s="9"/>
       <c r="E73" s="10"/>
-      <c r="BO73" s="11"/>
-      <c r="BR73" s="11"/>
-    </row>
-    <row r="74" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN73" s="11"/>
+      <c r="BQ73" s="11"/>
+    </row>
+    <row r="74" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D74" s="9"/>
       <c r="E74" s="10"/>
-      <c r="BO74" s="11"/>
-      <c r="BR74" s="11"/>
-    </row>
-    <row r="75" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN74" s="11"/>
+      <c r="BQ74" s="11"/>
+    </row>
+    <row r="75" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D75" s="9"/>
       <c r="E75" s="10"/>
-      <c r="BO75" s="11"/>
-      <c r="BR75" s="11"/>
-    </row>
-    <row r="76" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN75" s="11"/>
+      <c r="BQ75" s="11"/>
+    </row>
+    <row r="76" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D76" s="9"/>
       <c r="E76" s="10"/>
-      <c r="BO76" s="11"/>
-      <c r="BR76" s="11"/>
-    </row>
-    <row r="77" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN76" s="11"/>
+      <c r="BQ76" s="11"/>
+    </row>
+    <row r="77" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D77" s="9"/>
       <c r="E77" s="10"/>
-      <c r="BO77" s="11"/>
-      <c r="BR77" s="11"/>
-    </row>
-    <row r="78" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN77" s="11"/>
+      <c r="BQ77" s="11"/>
+    </row>
+    <row r="78" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D78" s="9"/>
       <c r="E78" s="10"/>
-      <c r="BO78" s="11"/>
-      <c r="BR78" s="11"/>
-    </row>
-    <row r="79" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN78" s="11"/>
+      <c r="BQ78" s="11"/>
+    </row>
+    <row r="79" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D79" s="9"/>
       <c r="E79" s="10"/>
-      <c r="BO79" s="11"/>
-      <c r="BR79" s="11"/>
-    </row>
-    <row r="80" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN79" s="11"/>
+      <c r="BQ79" s="11"/>
+    </row>
+    <row r="80" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D80" s="9"/>
       <c r="E80" s="10"/>
-      <c r="BO80" s="11"/>
-      <c r="BR80" s="11"/>
-    </row>
-    <row r="81" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN80" s="11"/>
+      <c r="BQ80" s="11"/>
+    </row>
+    <row r="81" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D81" s="9"/>
       <c r="E81" s="10"/>
-      <c r="BO81" s="11"/>
-      <c r="BR81" s="11"/>
-    </row>
-    <row r="82" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN81" s="11"/>
+      <c r="BQ81" s="11"/>
+    </row>
+    <row r="82" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D82" s="9"/>
       <c r="E82" s="10"/>
-      <c r="BO82" s="11"/>
-      <c r="BR82" s="11"/>
-    </row>
-    <row r="83" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN82" s="11"/>
+      <c r="BQ82" s="11"/>
+    </row>
+    <row r="83" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D83" s="9"/>
       <c r="E83" s="10"/>
-      <c r="BO83" s="11"/>
-      <c r="BR83" s="11"/>
-    </row>
-    <row r="84" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN83" s="11"/>
+      <c r="BQ83" s="11"/>
+    </row>
+    <row r="84" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D84" s="9"/>
       <c r="E84" s="10"/>
-      <c r="BO84" s="11"/>
-      <c r="BR84" s="11"/>
-    </row>
-    <row r="85" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN84" s="11"/>
+      <c r="BQ84" s="11"/>
+    </row>
+    <row r="85" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D85" s="9"/>
       <c r="E85" s="10"/>
-      <c r="BO85" s="11"/>
-      <c r="BR85" s="11"/>
-    </row>
-    <row r="86" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN85" s="11"/>
+      <c r="BQ85" s="11"/>
+    </row>
+    <row r="86" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D86" s="9"/>
       <c r="E86" s="10"/>
-      <c r="BO86" s="11"/>
-      <c r="BR86" s="11"/>
-    </row>
-    <row r="87" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN86" s="11"/>
+      <c r="BQ86" s="11"/>
+    </row>
+    <row r="87" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D87" s="9"/>
       <c r="E87" s="10"/>
-      <c r="BO87" s="11"/>
-      <c r="BR87" s="11"/>
-    </row>
-    <row r="88" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN87" s="11"/>
+      <c r="BQ87" s="11"/>
+    </row>
+    <row r="88" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D88" s="9"/>
       <c r="E88" s="10"/>
-      <c r="BO88" s="11"/>
-      <c r="BR88" s="11"/>
-    </row>
-    <row r="89" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN88" s="11"/>
+      <c r="BQ88" s="11"/>
+    </row>
+    <row r="89" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D89" s="9"/>
       <c r="E89" s="10"/>
-      <c r="BO89" s="11"/>
-      <c r="BR89" s="11"/>
-    </row>
-    <row r="90" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN89" s="11"/>
+      <c r="BQ89" s="11"/>
+    </row>
+    <row r="90" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D90" s="9"/>
       <c r="E90" s="10"/>
-      <c r="BO90" s="11"/>
-      <c r="BR90" s="11"/>
-    </row>
-    <row r="91" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN90" s="11"/>
+      <c r="BQ90" s="11"/>
+    </row>
+    <row r="91" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D91" s="9"/>
       <c r="E91" s="10"/>
-      <c r="BO91" s="11"/>
-      <c r="BR91" s="11"/>
-    </row>
-    <row r="92" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN91" s="11"/>
+      <c r="BQ91" s="11"/>
+    </row>
+    <row r="92" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D92" s="9"/>
       <c r="E92" s="10"/>
-      <c r="BO92" s="11"/>
-      <c r="BR92" s="11"/>
-    </row>
-    <row r="93" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN92" s="11"/>
+      <c r="BQ92" s="11"/>
+    </row>
+    <row r="93" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D93" s="9"/>
       <c r="E93" s="10"/>
-      <c r="BO93" s="11"/>
-      <c r="BR93" s="11"/>
-    </row>
-    <row r="94" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN93" s="11"/>
+      <c r="BQ93" s="11"/>
+    </row>
+    <row r="94" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D94" s="9"/>
       <c r="E94" s="10"/>
-      <c r="BO94" s="11"/>
-      <c r="BR94" s="11"/>
-    </row>
-    <row r="95" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN94" s="11"/>
+      <c r="BQ94" s="11"/>
+    </row>
+    <row r="95" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D95" s="9"/>
       <c r="E95" s="10"/>
-      <c r="BO95" s="11"/>
-      <c r="BR95" s="11"/>
-    </row>
-    <row r="96" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN95" s="11"/>
+      <c r="BQ95" s="11"/>
+    </row>
+    <row r="96" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D96" s="9"/>
       <c r="E96" s="10"/>
-      <c r="BO96" s="11"/>
-      <c r="BR96" s="11"/>
-    </row>
-    <row r="97" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN96" s="11"/>
+      <c r="BQ96" s="11"/>
+    </row>
+    <row r="97" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D97" s="9"/>
       <c r="E97" s="10"/>
-      <c r="BO97" s="11"/>
-      <c r="BR97" s="11"/>
-    </row>
-    <row r="98" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN97" s="11"/>
+      <c r="BQ97" s="11"/>
+    </row>
+    <row r="98" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D98" s="9"/>
       <c r="E98" s="10"/>
-      <c r="BO98" s="11"/>
-      <c r="BR98" s="11"/>
-    </row>
-    <row r="99" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN98" s="11"/>
+      <c r="BQ98" s="11"/>
+    </row>
+    <row r="99" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D99" s="9"/>
       <c r="E99" s="10"/>
-      <c r="BO99" s="11"/>
-      <c r="BR99" s="11"/>
-    </row>
-    <row r="100" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN99" s="11"/>
+      <c r="BQ99" s="11"/>
+    </row>
+    <row r="100" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D100" s="9"/>
       <c r="E100" s="10"/>
-      <c r="BO100" s="11"/>
-      <c r="BR100" s="11"/>
-    </row>
-    <row r="101" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN100" s="11"/>
+      <c r="BQ100" s="11"/>
+    </row>
+    <row r="101" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D101" s="9"/>
       <c r="E101" s="10"/>
-      <c r="BO101" s="11"/>
-      <c r="BR101" s="11"/>
-    </row>
-    <row r="102" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN101" s="11"/>
+      <c r="BQ101" s="11"/>
+    </row>
+    <row r="102" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D102" s="9"/>
       <c r="E102" s="10"/>
-      <c r="BO102" s="11"/>
-      <c r="BR102" s="11"/>
-    </row>
-    <row r="103" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN102" s="11"/>
+      <c r="BQ102" s="11"/>
+    </row>
+    <row r="103" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D103" s="9"/>
       <c r="E103" s="10"/>
-      <c r="BO103" s="11"/>
-      <c r="BR103" s="11"/>
-    </row>
-    <row r="104" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN103" s="11"/>
+      <c r="BQ103" s="11"/>
+    </row>
+    <row r="104" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D104" s="9"/>
       <c r="E104" s="10"/>
-      <c r="BO104" s="11"/>
-      <c r="BR104" s="11"/>
-    </row>
-    <row r="105" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN104" s="11"/>
+      <c r="BQ104" s="11"/>
+    </row>
+    <row r="105" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D105" s="9"/>
       <c r="E105" s="10"/>
-      <c r="BO105" s="11"/>
-      <c r="BR105" s="11"/>
-    </row>
-    <row r="106" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN105" s="11"/>
+      <c r="BQ105" s="11"/>
+    </row>
+    <row r="106" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D106" s="9"/>
       <c r="E106" s="10"/>
-      <c r="BO106" s="11"/>
-      <c r="BR106" s="11"/>
-    </row>
-    <row r="107" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN106" s="11"/>
+      <c r="BQ106" s="11"/>
+    </row>
+    <row r="107" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D107" s="9"/>
       <c r="E107" s="10"/>
-      <c r="BO107" s="11"/>
-      <c r="BR107" s="11"/>
-    </row>
-    <row r="108" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN107" s="11"/>
+      <c r="BQ107" s="11"/>
+    </row>
+    <row r="108" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D108" s="9"/>
       <c r="E108" s="10"/>
-      <c r="BO108" s="11"/>
-      <c r="BR108" s="11"/>
-    </row>
-    <row r="109" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN108" s="11"/>
+      <c r="BQ108" s="11"/>
+    </row>
+    <row r="109" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D109" s="9"/>
       <c r="E109" s="10"/>
-      <c r="BO109" s="11"/>
-      <c r="BR109" s="11"/>
-    </row>
-    <row r="110" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN109" s="11"/>
+      <c r="BQ109" s="11"/>
+    </row>
+    <row r="110" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D110" s="9"/>
       <c r="E110" s="10"/>
-      <c r="BO110" s="11"/>
-      <c r="BR110" s="11"/>
-    </row>
-    <row r="111" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN110" s="11"/>
+      <c r="BQ110" s="11"/>
+    </row>
+    <row r="111" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D111" s="9"/>
       <c r="E111" s="10"/>
-      <c r="BO111" s="11"/>
-      <c r="BR111" s="11"/>
-    </row>
-    <row r="112" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN111" s="11"/>
+      <c r="BQ111" s="11"/>
+    </row>
+    <row r="112" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D112" s="9"/>
       <c r="E112" s="10"/>
-      <c r="BO112" s="11"/>
-      <c r="BR112" s="11"/>
-    </row>
-    <row r="113" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN112" s="11"/>
+      <c r="BQ112" s="11"/>
+    </row>
+    <row r="113" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D113" s="9"/>
       <c r="E113" s="10"/>
-      <c r="BO113" s="11"/>
-      <c r="BR113" s="11"/>
-    </row>
-    <row r="114" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN113" s="11"/>
+      <c r="BQ113" s="11"/>
+    </row>
+    <row r="114" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D114" s="9"/>
       <c r="E114" s="10"/>
-      <c r="BO114" s="11"/>
-      <c r="BR114" s="11"/>
-    </row>
-    <row r="115" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN114" s="11"/>
+      <c r="BQ114" s="11"/>
+    </row>
+    <row r="115" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D115" s="9"/>
       <c r="E115" s="10"/>
-      <c r="BO115" s="11"/>
-      <c r="BR115" s="11"/>
-    </row>
-    <row r="116" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN115" s="11"/>
+      <c r="BQ115" s="11"/>
+    </row>
+    <row r="116" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D116" s="9"/>
       <c r="E116" s="10"/>
-      <c r="BO116" s="11"/>
-      <c r="BR116" s="11"/>
-    </row>
-    <row r="117" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN116" s="11"/>
+      <c r="BQ116" s="11"/>
+    </row>
+    <row r="117" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D117" s="9"/>
       <c r="E117" s="10"/>
-      <c r="BO117" s="11"/>
-      <c r="BR117" s="11"/>
-    </row>
-    <row r="118" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN117" s="11"/>
+      <c r="BQ117" s="11"/>
+    </row>
+    <row r="118" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D118" s="9"/>
       <c r="E118" s="10"/>
-      <c r="BO118" s="11"/>
-      <c r="BR118" s="11"/>
-    </row>
-    <row r="119" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN118" s="11"/>
+      <c r="BQ118" s="11"/>
+    </row>
+    <row r="119" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D119" s="9"/>
       <c r="E119" s="10"/>
-      <c r="BO119" s="11"/>
-      <c r="BR119" s="11"/>
-    </row>
-    <row r="120" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN119" s="11"/>
+      <c r="BQ119" s="11"/>
+    </row>
+    <row r="120" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D120" s="9"/>
       <c r="E120" s="10"/>
-      <c r="BO120" s="11"/>
-      <c r="BR120" s="11"/>
-    </row>
-    <row r="121" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN120" s="11"/>
+      <c r="BQ120" s="11"/>
+    </row>
+    <row r="121" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D121" s="9"/>
       <c r="E121" s="10"/>
-      <c r="BO121" s="11"/>
-      <c r="BR121" s="11"/>
-    </row>
-    <row r="122" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN121" s="11"/>
+      <c r="BQ121" s="11"/>
+    </row>
+    <row r="122" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D122" s="9"/>
       <c r="E122" s="10"/>
-      <c r="BO122" s="11"/>
-      <c r="BR122" s="11"/>
-    </row>
-    <row r="123" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN122" s="11"/>
+      <c r="BQ122" s="11"/>
+    </row>
+    <row r="123" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D123" s="9"/>
       <c r="E123" s="10"/>
-      <c r="BO123" s="11"/>
-      <c r="BR123" s="11"/>
-    </row>
-    <row r="124" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN123" s="11"/>
+      <c r="BQ123" s="11"/>
+    </row>
+    <row r="124" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D124" s="9"/>
       <c r="E124" s="10"/>
-      <c r="BO124" s="11"/>
-      <c r="BR124" s="11"/>
-    </row>
-    <row r="125" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN124" s="11"/>
+      <c r="BQ124" s="11"/>
+    </row>
+    <row r="125" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D125" s="9"/>
       <c r="E125" s="10"/>
-      <c r="BO125" s="11"/>
-      <c r="BR125" s="11"/>
-    </row>
-    <row r="126" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN125" s="11"/>
+      <c r="BQ125" s="11"/>
+    </row>
+    <row r="126" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D126" s="9"/>
       <c r="E126" s="10"/>
-      <c r="BO126" s="11"/>
-      <c r="BR126" s="11"/>
-    </row>
-    <row r="127" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN126" s="11"/>
+      <c r="BQ126" s="11"/>
+    </row>
+    <row r="127" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D127" s="9"/>
       <c r="E127" s="10"/>
-      <c r="BO127" s="11"/>
-      <c r="BR127" s="11"/>
-    </row>
-    <row r="128" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN127" s="11"/>
+      <c r="BQ127" s="11"/>
+    </row>
+    <row r="128" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D128" s="9"/>
       <c r="E128" s="10"/>
-      <c r="BO128" s="11"/>
-      <c r="BR128" s="11"/>
-    </row>
-    <row r="129" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN128" s="11"/>
+      <c r="BQ128" s="11"/>
+    </row>
+    <row r="129" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D129" s="9"/>
       <c r="E129" s="10"/>
-      <c r="BO129" s="11"/>
-      <c r="BR129" s="11"/>
-    </row>
-    <row r="130" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN129" s="11"/>
+      <c r="BQ129" s="11"/>
+    </row>
+    <row r="130" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D130" s="9"/>
       <c r="E130" s="10"/>
-      <c r="BO130" s="11"/>
-      <c r="BR130" s="11"/>
-    </row>
-    <row r="131" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN130" s="11"/>
+      <c r="BQ130" s="11"/>
+    </row>
+    <row r="131" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D131" s="9"/>
       <c r="E131" s="10"/>
-      <c r="BO131" s="11"/>
-      <c r="BR131" s="11"/>
-    </row>
-    <row r="132" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN131" s="11"/>
+      <c r="BQ131" s="11"/>
+    </row>
+    <row r="132" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D132" s="9"/>
       <c r="E132" s="10"/>
-      <c r="BO132" s="11"/>
-      <c r="BR132" s="11"/>
-    </row>
-    <row r="133" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN132" s="11"/>
+      <c r="BQ132" s="11"/>
+    </row>
+    <row r="133" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D133" s="9"/>
       <c r="E133" s="10"/>
-      <c r="BO133" s="11"/>
-      <c r="BR133" s="11"/>
-    </row>
-    <row r="134" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN133" s="11"/>
+      <c r="BQ133" s="11"/>
+    </row>
+    <row r="134" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D134" s="9"/>
       <c r="E134" s="10"/>
-      <c r="BO134" s="11"/>
-      <c r="BR134" s="11"/>
-    </row>
-    <row r="135" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN134" s="11"/>
+      <c r="BQ134" s="11"/>
+    </row>
+    <row r="135" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D135" s="9"/>
       <c r="E135" s="10"/>
-      <c r="BO135" s="11"/>
-      <c r="BR135" s="11"/>
-    </row>
-    <row r="136" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN135" s="11"/>
+      <c r="BQ135" s="11"/>
+    </row>
+    <row r="136" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D136" s="9"/>
       <c r="E136" s="10"/>
-      <c r="BO136" s="11"/>
-      <c r="BR136" s="11"/>
-    </row>
-    <row r="137" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN136" s="11"/>
+      <c r="BQ136" s="11"/>
+    </row>
+    <row r="137" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D137" s="9"/>
       <c r="E137" s="10"/>
-      <c r="BO137" s="11"/>
-      <c r="BR137" s="11"/>
-    </row>
-    <row r="138" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN137" s="11"/>
+      <c r="BQ137" s="11"/>
+    </row>
+    <row r="138" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D138" s="9"/>
       <c r="E138" s="10"/>
-      <c r="BO138" s="11"/>
-      <c r="BR138" s="11"/>
-    </row>
-    <row r="139" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN138" s="11"/>
+      <c r="BQ138" s="11"/>
+    </row>
+    <row r="139" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D139" s="9"/>
       <c r="E139" s="10"/>
-      <c r="BO139" s="11"/>
-      <c r="BR139" s="11"/>
-    </row>
-    <row r="140" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN139" s="11"/>
+      <c r="BQ139" s="11"/>
+    </row>
+    <row r="140" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D140" s="9"/>
       <c r="E140" s="10"/>
-      <c r="BO140" s="11"/>
-      <c r="BR140" s="11"/>
-    </row>
-    <row r="141" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN140" s="11"/>
+      <c r="BQ140" s="11"/>
+    </row>
+    <row r="141" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D141" s="9"/>
       <c r="E141" s="10"/>
-      <c r="BO141" s="11"/>
-      <c r="BR141" s="11"/>
-    </row>
-    <row r="142" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN141" s="11"/>
+      <c r="BQ141" s="11"/>
+    </row>
+    <row r="142" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D142" s="9"/>
       <c r="E142" s="10"/>
-      <c r="BO142" s="11"/>
-      <c r="BR142" s="11"/>
-    </row>
-    <row r="143" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN142" s="11"/>
+      <c r="BQ142" s="11"/>
+    </row>
+    <row r="143" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D143" s="9"/>
       <c r="E143" s="10"/>
-      <c r="BO143" s="11"/>
-      <c r="BR143" s="11"/>
-    </row>
-    <row r="144" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN143" s="11"/>
+      <c r="BQ143" s="11"/>
+    </row>
+    <row r="144" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D144" s="9"/>
       <c r="E144" s="10"/>
-      <c r="BO144" s="11"/>
-      <c r="BR144" s="11"/>
-    </row>
-    <row r="145" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN144" s="11"/>
+      <c r="BQ144" s="11"/>
+    </row>
+    <row r="145" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D145" s="9"/>
       <c r="E145" s="10"/>
-      <c r="BO145" s="11"/>
-      <c r="BR145" s="11"/>
-    </row>
-    <row r="146" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN145" s="11"/>
+      <c r="BQ145" s="11"/>
+    </row>
+    <row r="146" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D146" s="9"/>
       <c r="E146" s="10"/>
-      <c r="BO146" s="11"/>
-      <c r="BR146" s="11"/>
-    </row>
-    <row r="147" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN146" s="11"/>
+      <c r="BQ146" s="11"/>
+    </row>
+    <row r="147" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D147" s="9"/>
       <c r="E147" s="10"/>
-      <c r="BO147" s="11"/>
-      <c r="BR147" s="11"/>
-    </row>
-    <row r="148" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN147" s="11"/>
+      <c r="BQ147" s="11"/>
+    </row>
+    <row r="148" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D148" s="9"/>
       <c r="E148" s="10"/>
-      <c r="BO148" s="11"/>
-      <c r="BR148" s="11"/>
-    </row>
-    <row r="149" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN148" s="11"/>
+      <c r="BQ148" s="11"/>
+    </row>
+    <row r="149" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D149" s="9"/>
       <c r="E149" s="10"/>
-      <c r="BO149" s="11"/>
-      <c r="BR149" s="11"/>
-    </row>
-    <row r="150" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN149" s="11"/>
+      <c r="BQ149" s="11"/>
+    </row>
+    <row r="150" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D150" s="9"/>
       <c r="E150" s="10"/>
-      <c r="BO150" s="11"/>
-      <c r="BR150" s="11"/>
-    </row>
-    <row r="151" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN150" s="11"/>
+      <c r="BQ150" s="11"/>
+    </row>
+    <row r="151" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D151" s="9"/>
       <c r="E151" s="10"/>
-      <c r="BO151" s="11"/>
-      <c r="BR151" s="11"/>
-    </row>
-    <row r="152" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN151" s="11"/>
+      <c r="BQ151" s="11"/>
+    </row>
+    <row r="152" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D152" s="9"/>
       <c r="E152" s="10"/>
-      <c r="BO152" s="11"/>
-      <c r="BR152" s="11"/>
-    </row>
-    <row r="153" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN152" s="11"/>
+      <c r="BQ152" s="11"/>
+    </row>
+    <row r="153" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D153" s="9"/>
       <c r="E153" s="10"/>
-      <c r="BO153" s="11"/>
-      <c r="BR153" s="11"/>
-    </row>
-    <row r="154" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN153" s="11"/>
+      <c r="BQ153" s="11"/>
+    </row>
+    <row r="154" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D154" s="9"/>
       <c r="E154" s="10"/>
-      <c r="BO154" s="11"/>
-      <c r="BR154" s="11"/>
-    </row>
-    <row r="155" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN154" s="11"/>
+      <c r="BQ154" s="11"/>
+    </row>
+    <row r="155" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D155" s="9"/>
       <c r="E155" s="10"/>
-      <c r="BO155" s="11"/>
-      <c r="BR155" s="11"/>
-    </row>
-    <row r="156" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN155" s="11"/>
+      <c r="BQ155" s="11"/>
+    </row>
+    <row r="156" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D156" s="9"/>
       <c r="E156" s="10"/>
-      <c r="BO156" s="11"/>
-      <c r="BR156" s="11"/>
-    </row>
-    <row r="157" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN156" s="11"/>
+      <c r="BQ156" s="11"/>
+    </row>
+    <row r="157" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D157" s="9"/>
       <c r="E157" s="10"/>
-      <c r="BO157" s="11"/>
-      <c r="BR157" s="11"/>
-    </row>
-    <row r="158" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN157" s="11"/>
+      <c r="BQ157" s="11"/>
+    </row>
+    <row r="158" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D158" s="9"/>
       <c r="E158" s="10"/>
-      <c r="BO158" s="11"/>
-      <c r="BR158" s="11"/>
-    </row>
-    <row r="159" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN158" s="11"/>
+      <c r="BQ158" s="11"/>
+    </row>
+    <row r="159" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D159" s="9"/>
       <c r="E159" s="10"/>
-      <c r="BO159" s="11"/>
-      <c r="BR159" s="11"/>
-    </row>
-    <row r="160" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN159" s="11"/>
+      <c r="BQ159" s="11"/>
+    </row>
+    <row r="160" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D160" s="9"/>
       <c r="E160" s="10"/>
-      <c r="BO160" s="11"/>
-      <c r="BR160" s="11"/>
-    </row>
-    <row r="161" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN160" s="11"/>
+      <c r="BQ160" s="11"/>
+    </row>
+    <row r="161" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D161" s="9"/>
       <c r="E161" s="10"/>
-      <c r="BO161" s="11"/>
-      <c r="BR161" s="11"/>
-    </row>
-    <row r="162" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN161" s="11"/>
+      <c r="BQ161" s="11"/>
+    </row>
+    <row r="162" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D162" s="9"/>
       <c r="E162" s="10"/>
-      <c r="BO162" s="11"/>
-      <c r="BR162" s="11"/>
-    </row>
-    <row r="163" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN162" s="11"/>
+      <c r="BQ162" s="11"/>
+    </row>
+    <row r="163" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D163" s="9"/>
       <c r="E163" s="10"/>
-      <c r="BO163" s="11"/>
-      <c r="BR163" s="11"/>
-    </row>
-    <row r="164" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN163" s="11"/>
+      <c r="BQ163" s="11"/>
+    </row>
+    <row r="164" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D164" s="9"/>
       <c r="E164" s="10"/>
-      <c r="BO164" s="11"/>
-      <c r="BR164" s="11"/>
-    </row>
-    <row r="165" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN164" s="11"/>
+      <c r="BQ164" s="11"/>
+    </row>
+    <row r="165" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D165" s="9"/>
       <c r="E165" s="10"/>
-      <c r="BO165" s="11"/>
-      <c r="BR165" s="11"/>
-    </row>
-    <row r="166" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN165" s="11"/>
+      <c r="BQ165" s="11"/>
+    </row>
+    <row r="166" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D166" s="9"/>
       <c r="E166" s="10"/>
-      <c r="BO166" s="11"/>
-      <c r="BR166" s="11"/>
-    </row>
-    <row r="167" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN166" s="11"/>
+      <c r="BQ166" s="11"/>
+    </row>
+    <row r="167" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D167" s="9"/>
       <c r="E167" s="10"/>
-      <c r="BO167" s="11"/>
-      <c r="BR167" s="11"/>
-    </row>
-    <row r="168" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN167" s="11"/>
+      <c r="BQ167" s="11"/>
+    </row>
+    <row r="168" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D168" s="9"/>
       <c r="E168" s="10"/>
-      <c r="BO168" s="11"/>
-      <c r="BR168" s="11"/>
-    </row>
-    <row r="169" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN168" s="11"/>
+      <c r="BQ168" s="11"/>
+    </row>
+    <row r="169" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D169" s="9"/>
       <c r="E169" s="10"/>
-      <c r="BO169" s="11"/>
-      <c r="BR169" s="11"/>
-    </row>
-    <row r="170" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN169" s="11"/>
+      <c r="BQ169" s="11"/>
+    </row>
+    <row r="170" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D170" s="9"/>
       <c r="E170" s="10"/>
-      <c r="BO170" s="11"/>
-      <c r="BR170" s="11"/>
-    </row>
-    <row r="171" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN170" s="11"/>
+      <c r="BQ170" s="11"/>
+    </row>
+    <row r="171" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D171" s="9"/>
       <c r="E171" s="10"/>
-      <c r="BO171" s="11"/>
-      <c r="BR171" s="11"/>
-    </row>
-    <row r="172" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN171" s="11"/>
+      <c r="BQ171" s="11"/>
+    </row>
+    <row r="172" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D172" s="9"/>
       <c r="E172" s="10"/>
-      <c r="BO172" s="11"/>
-      <c r="BR172" s="11"/>
-    </row>
-    <row r="173" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN172" s="11"/>
+      <c r="BQ172" s="11"/>
+    </row>
+    <row r="173" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D173" s="9"/>
       <c r="E173" s="10"/>
-      <c r="BO173" s="11"/>
-      <c r="BR173" s="11"/>
-    </row>
-    <row r="174" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN173" s="11"/>
+      <c r="BQ173" s="11"/>
+    </row>
+    <row r="174" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D174" s="9"/>
       <c r="E174" s="10"/>
-      <c r="BO174" s="11"/>
-      <c r="BR174" s="11"/>
-    </row>
-    <row r="175" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN174" s="11"/>
+      <c r="BQ174" s="11"/>
+    </row>
+    <row r="175" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D175" s="9"/>
       <c r="E175" s="10"/>
-      <c r="BO175" s="11"/>
-      <c r="BR175" s="11"/>
-    </row>
-    <row r="176" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN175" s="11"/>
+      <c r="BQ175" s="11"/>
+    </row>
+    <row r="176" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D176" s="9"/>
       <c r="E176" s="10"/>
-      <c r="BO176" s="11"/>
-      <c r="BR176" s="11"/>
-    </row>
-    <row r="177" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN176" s="11"/>
+      <c r="BQ176" s="11"/>
+    </row>
+    <row r="177" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D177" s="9"/>
       <c r="E177" s="10"/>
-      <c r="BO177" s="11"/>
-      <c r="BR177" s="11"/>
-    </row>
-    <row r="178" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN177" s="11"/>
+      <c r="BQ177" s="11"/>
+    </row>
+    <row r="178" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D178" s="9"/>
       <c r="E178" s="10"/>
-      <c r="BO178" s="11"/>
-      <c r="BR178" s="11"/>
-    </row>
-    <row r="179" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN178" s="11"/>
+      <c r="BQ178" s="11"/>
+    </row>
+    <row r="179" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D179" s="9"/>
       <c r="E179" s="10"/>
-      <c r="BO179" s="11"/>
-      <c r="BR179" s="11"/>
-    </row>
-    <row r="180" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN179" s="11"/>
+      <c r="BQ179" s="11"/>
+    </row>
+    <row r="180" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D180" s="9"/>
       <c r="E180" s="10"/>
-      <c r="BO180" s="11"/>
-      <c r="BR180" s="11"/>
-    </row>
-    <row r="181" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN180" s="11"/>
+      <c r="BQ180" s="11"/>
+    </row>
+    <row r="181" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D181" s="9"/>
       <c r="E181" s="10"/>
-      <c r="BO181" s="11"/>
-      <c r="BR181" s="11"/>
-    </row>
-    <row r="182" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN181" s="11"/>
+      <c r="BQ181" s="11"/>
+    </row>
+    <row r="182" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D182" s="9"/>
       <c r="E182" s="10"/>
-      <c r="BO182" s="11"/>
-      <c r="BR182" s="11"/>
-    </row>
-    <row r="183" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN182" s="11"/>
+      <c r="BQ182" s="11"/>
+    </row>
+    <row r="183" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D183" s="9"/>
       <c r="E183" s="10"/>
-      <c r="BO183" s="11"/>
-      <c r="BR183" s="11"/>
-    </row>
-    <row r="184" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN183" s="11"/>
+      <c r="BQ183" s="11"/>
+    </row>
+    <row r="184" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D184" s="9"/>
       <c r="E184" s="10"/>
-      <c r="BO184" s="11"/>
-      <c r="BR184" s="11"/>
-    </row>
-    <row r="185" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN184" s="11"/>
+      <c r="BQ184" s="11"/>
+    </row>
+    <row r="185" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D185" s="9"/>
       <c r="E185" s="10"/>
-      <c r="BO185" s="11"/>
-      <c r="BR185" s="11"/>
-    </row>
-    <row r="186" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN185" s="11"/>
+      <c r="BQ185" s="11"/>
+    </row>
+    <row r="186" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D186" s="9"/>
       <c r="E186" s="10"/>
-      <c r="BO186" s="11"/>
-      <c r="BR186" s="11"/>
-    </row>
-    <row r="187" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN186" s="11"/>
+      <c r="BQ186" s="11"/>
+    </row>
+    <row r="187" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D187" s="9"/>
       <c r="E187" s="10"/>
-      <c r="BO187" s="11"/>
-      <c r="BR187" s="11"/>
-    </row>
-    <row r="188" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN187" s="11"/>
+      <c r="BQ187" s="11"/>
+    </row>
+    <row r="188" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D188" s="9"/>
       <c r="E188" s="10"/>
-      <c r="BO188" s="11"/>
-      <c r="BR188" s="11"/>
-    </row>
-    <row r="189" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN188" s="11"/>
+      <c r="BQ188" s="11"/>
+    </row>
+    <row r="189" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D189" s="9"/>
       <c r="E189" s="10"/>
-      <c r="BO189" s="11"/>
-      <c r="BR189" s="11"/>
-    </row>
-    <row r="190" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN189" s="11"/>
+      <c r="BQ189" s="11"/>
+    </row>
+    <row r="190" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D190" s="9"/>
       <c r="E190" s="10"/>
-      <c r="BO190" s="11"/>
-      <c r="BR190" s="11"/>
-    </row>
-    <row r="191" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN190" s="11"/>
+      <c r="BQ190" s="11"/>
+    </row>
+    <row r="191" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D191" s="9"/>
       <c r="E191" s="10"/>
-      <c r="BO191" s="11"/>
-      <c r="BR191" s="11"/>
-    </row>
-    <row r="192" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN191" s="11"/>
+      <c r="BQ191" s="11"/>
+    </row>
+    <row r="192" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D192" s="9"/>
       <c r="E192" s="10"/>
-      <c r="BO192" s="11"/>
-      <c r="BR192" s="11"/>
-    </row>
-    <row r="193" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN192" s="11"/>
+      <c r="BQ192" s="11"/>
+    </row>
+    <row r="193" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D193" s="9"/>
       <c r="E193" s="10"/>
-      <c r="BO193" s="11"/>
-      <c r="BR193" s="11"/>
-    </row>
-    <row r="194" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN193" s="11"/>
+      <c r="BQ193" s="11"/>
+    </row>
+    <row r="194" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D194" s="9"/>
       <c r="E194" s="10"/>
-      <c r="BO194" s="11"/>
-      <c r="BR194" s="11"/>
-    </row>
-    <row r="195" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN194" s="11"/>
+      <c r="BQ194" s="11"/>
+    </row>
+    <row r="195" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D195" s="9"/>
       <c r="E195" s="10"/>
-      <c r="BO195" s="11"/>
-      <c r="BR195" s="11"/>
-    </row>
-    <row r="196" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN195" s="11"/>
+      <c r="BQ195" s="11"/>
+    </row>
+    <row r="196" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D196" s="9"/>
       <c r="E196" s="10"/>
-      <c r="BO196" s="11"/>
-      <c r="BR196" s="11"/>
-    </row>
-    <row r="197" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN196" s="11"/>
+      <c r="BQ196" s="11"/>
+    </row>
+    <row r="197" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D197" s="9"/>
       <c r="E197" s="10"/>
-      <c r="BO197" s="11"/>
-      <c r="BR197" s="11"/>
-    </row>
-    <row r="198" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN197" s="11"/>
+      <c r="BQ197" s="11"/>
+    </row>
+    <row r="198" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D198" s="9"/>
       <c r="E198" s="10"/>
-      <c r="BO198" s="11"/>
-      <c r="BR198" s="11"/>
-    </row>
-    <row r="199" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN198" s="11"/>
+      <c r="BQ198" s="11"/>
+    </row>
+    <row r="199" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D199" s="9"/>
       <c r="E199" s="10"/>
-      <c r="BO199" s="11"/>
-      <c r="BR199" s="11"/>
-    </row>
-    <row r="200" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN199" s="11"/>
+      <c r="BQ199" s="11"/>
+    </row>
+    <row r="200" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D200" s="9"/>
       <c r="E200" s="10"/>
-      <c r="BO200" s="11"/>
-      <c r="BR200" s="11"/>
-    </row>
-    <row r="201" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN200" s="11"/>
+      <c r="BQ200" s="11"/>
+    </row>
+    <row r="201" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D201" s="9"/>
       <c r="E201" s="10"/>
-      <c r="BO201" s="11"/>
-      <c r="BR201" s="11"/>
-    </row>
-    <row r="202" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN201" s="11"/>
+      <c r="BQ201" s="11"/>
+    </row>
+    <row r="202" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D202" s="9"/>
       <c r="E202" s="10"/>
-      <c r="BO202" s="11"/>
-      <c r="BR202" s="11"/>
-    </row>
-    <row r="203" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN202" s="11"/>
+      <c r="BQ202" s="11"/>
+    </row>
+    <row r="203" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D203" s="9"/>
       <c r="E203" s="10"/>
-      <c r="BO203" s="11"/>
-      <c r="BR203" s="11"/>
-    </row>
-    <row r="204" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN203" s="11"/>
+      <c r="BQ203" s="11"/>
+    </row>
+    <row r="204" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D204" s="9"/>
       <c r="E204" s="10"/>
-      <c r="BO204" s="11"/>
-      <c r="BR204" s="11"/>
-    </row>
-    <row r="205" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN204" s="11"/>
+      <c r="BQ204" s="11"/>
+    </row>
+    <row r="205" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D205" s="9"/>
       <c r="E205" s="10"/>
-      <c r="BO205" s="11"/>
-      <c r="BR205" s="11"/>
-    </row>
-    <row r="206" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN205" s="11"/>
+      <c r="BQ205" s="11"/>
+    </row>
+    <row r="206" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D206" s="9"/>
       <c r="E206" s="10"/>
-      <c r="BO206" s="11"/>
-      <c r="BR206" s="11"/>
-    </row>
-    <row r="207" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN206" s="11"/>
+      <c r="BQ206" s="11"/>
+    </row>
+    <row r="207" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D207" s="9"/>
       <c r="E207" s="10"/>
-      <c r="BO207" s="11"/>
-      <c r="BR207" s="11"/>
-    </row>
-    <row r="208" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN207" s="11"/>
+      <c r="BQ207" s="11"/>
+    </row>
+    <row r="208" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D208" s="9"/>
       <c r="E208" s="10"/>
-      <c r="BO208" s="11"/>
-      <c r="BR208" s="11"/>
-    </row>
-    <row r="209" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN208" s="11"/>
+      <c r="BQ208" s="11"/>
+    </row>
+    <row r="209" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D209" s="9"/>
       <c r="E209" s="10"/>
-      <c r="BO209" s="11"/>
-      <c r="BR209" s="11"/>
-    </row>
-    <row r="210" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN209" s="11"/>
+      <c r="BQ209" s="11"/>
+    </row>
+    <row r="210" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D210" s="9"/>
       <c r="E210" s="10"/>
-      <c r="BO210" s="11"/>
-      <c r="BR210" s="11"/>
-    </row>
-    <row r="211" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN210" s="11"/>
+      <c r="BQ210" s="11"/>
+    </row>
+    <row r="211" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D211" s="9"/>
       <c r="E211" s="10"/>
-      <c r="BO211" s="11"/>
-      <c r="BR211" s="11"/>
-    </row>
-    <row r="212" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN211" s="11"/>
+      <c r="BQ211" s="11"/>
+    </row>
+    <row r="212" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D212" s="9"/>
       <c r="E212" s="10"/>
-      <c r="BO212" s="11"/>
-      <c r="BR212" s="11"/>
-    </row>
-    <row r="213" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN212" s="11"/>
+      <c r="BQ212" s="11"/>
+    </row>
+    <row r="213" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D213" s="9"/>
       <c r="E213" s="10"/>
-      <c r="BO213" s="11"/>
-      <c r="BR213" s="11"/>
-    </row>
-    <row r="214" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN213" s="11"/>
+      <c r="BQ213" s="11"/>
+    </row>
+    <row r="214" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D214" s="9"/>
       <c r="E214" s="10"/>
-      <c r="BO214" s="11"/>
-      <c r="BR214" s="11"/>
-    </row>
-    <row r="215" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN214" s="11"/>
+      <c r="BQ214" s="11"/>
+    </row>
+    <row r="215" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D215" s="9"/>
       <c r="E215" s="10"/>
-      <c r="BO215" s="11"/>
-      <c r="BR215" s="11"/>
-    </row>
-    <row r="216" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN215" s="11"/>
+      <c r="BQ215" s="11"/>
+    </row>
+    <row r="216" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D216" s="9"/>
       <c r="E216" s="10"/>
-      <c r="BO216" s="11"/>
-      <c r="BR216" s="11"/>
-    </row>
-    <row r="217" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN216" s="11"/>
+      <c r="BQ216" s="11"/>
+    </row>
+    <row r="217" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D217" s="9"/>
       <c r="E217" s="10"/>
-      <c r="BO217" s="11"/>
-      <c r="BR217" s="11"/>
-    </row>
-    <row r="218" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN217" s="11"/>
+      <c r="BQ217" s="11"/>
+    </row>
+    <row r="218" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D218" s="9"/>
       <c r="E218" s="10"/>
-      <c r="BO218" s="11"/>
-      <c r="BR218" s="11"/>
-    </row>
-    <row r="219" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN218" s="11"/>
+      <c r="BQ218" s="11"/>
+    </row>
+    <row r="219" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D219" s="9"/>
       <c r="E219" s="10"/>
-      <c r="BO219" s="11"/>
-      <c r="BR219" s="11"/>
-    </row>
-    <row r="220" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN219" s="11"/>
+      <c r="BQ219" s="11"/>
+    </row>
+    <row r="220" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D220" s="9"/>
       <c r="E220" s="10"/>
-      <c r="BO220" s="11"/>
-      <c r="BR220" s="11"/>
-    </row>
-    <row r="221" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN220" s="11"/>
+      <c r="BQ220" s="11"/>
+    </row>
+    <row r="221" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D221" s="9"/>
       <c r="E221" s="10"/>
-      <c r="BO221" s="11"/>
-      <c r="BR221" s="11"/>
-    </row>
-    <row r="222" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN221" s="11"/>
+      <c r="BQ221" s="11"/>
+    </row>
+    <row r="222" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D222" s="9"/>
       <c r="E222" s="10"/>
-      <c r="BO222" s="11"/>
-      <c r="BR222" s="11"/>
-    </row>
-    <row r="223" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN222" s="11"/>
+      <c r="BQ222" s="11"/>
+    </row>
+    <row r="223" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D223" s="9"/>
       <c r="E223" s="10"/>
-      <c r="BO223" s="11"/>
-      <c r="BR223" s="11"/>
-    </row>
-    <row r="224" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN223" s="11"/>
+      <c r="BQ223" s="11"/>
+    </row>
+    <row r="224" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D224" s="9"/>
       <c r="E224" s="10"/>
-      <c r="BO224" s="11"/>
-      <c r="BR224" s="11"/>
-    </row>
-    <row r="225" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN224" s="11"/>
+      <c r="BQ224" s="11"/>
+    </row>
+    <row r="225" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D225" s="9"/>
       <c r="E225" s="10"/>
-      <c r="BO225" s="11"/>
-      <c r="BR225" s="11"/>
-    </row>
-    <row r="226" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN225" s="11"/>
+      <c r="BQ225" s="11"/>
+    </row>
+    <row r="226" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D226" s="9"/>
       <c r="E226" s="10"/>
-      <c r="BO226" s="11"/>
-      <c r="BR226" s="11"/>
-    </row>
-    <row r="227" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN226" s="11"/>
+      <c r="BQ226" s="11"/>
+    </row>
+    <row r="227" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D227" s="9"/>
       <c r="E227" s="10"/>
-      <c r="BO227" s="11"/>
-      <c r="BR227" s="11"/>
-    </row>
-    <row r="228" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN227" s="11"/>
+      <c r="BQ227" s="11"/>
+    </row>
+    <row r="228" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D228" s="9"/>
       <c r="E228" s="10"/>
-      <c r="BR228" s="11"/>
-    </row>
-    <row r="229" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ228" s="11"/>
+    </row>
+    <row r="229" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D229" s="9"/>
       <c r="E229" s="10"/>
-      <c r="BO229" s="11"/>
-      <c r="BR229" s="11"/>
-    </row>
-    <row r="230" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN229" s="11"/>
+      <c r="BQ229" s="11"/>
+    </row>
+    <row r="230" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D230" s="9"/>
       <c r="E230" s="10"/>
-      <c r="BO230" s="11"/>
-      <c r="BR230" s="11"/>
-    </row>
-    <row r="231" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN230" s="11"/>
+      <c r="BQ230" s="11"/>
+    </row>
+    <row r="231" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D231" s="9"/>
       <c r="E231" s="10"/>
-      <c r="BO231" s="11"/>
-      <c r="BR231" s="11"/>
-    </row>
-    <row r="232" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN231" s="11"/>
+      <c r="BQ231" s="11"/>
+    </row>
+    <row r="232" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D232" s="9"/>
       <c r="E232" s="10"/>
-      <c r="BO232" s="11"/>
-      <c r="BR232" s="11"/>
-    </row>
-    <row r="233" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN232" s="11"/>
+      <c r="BQ232" s="11"/>
+    </row>
+    <row r="233" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D233" s="9"/>
       <c r="E233" s="10"/>
-      <c r="BO233" s="11"/>
-      <c r="BR233" s="11"/>
-    </row>
-    <row r="234" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN233" s="11"/>
+      <c r="BQ233" s="11"/>
+    </row>
+    <row r="234" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D234" s="9"/>
       <c r="E234" s="10"/>
-      <c r="BO234" s="11"/>
-      <c r="BR234" s="11"/>
-    </row>
-    <row r="235" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN234" s="11"/>
+      <c r="BQ234" s="11"/>
+    </row>
+    <row r="235" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D235" s="9"/>
       <c r="E235" s="10"/>
-      <c r="BO235" s="11"/>
-      <c r="BR235" s="11"/>
-    </row>
-    <row r="236" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN235" s="11"/>
+      <c r="BQ235" s="11"/>
+    </row>
+    <row r="236" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D236" s="9"/>
       <c r="E236" s="10"/>
-      <c r="BO236" s="11"/>
-      <c r="BR236" s="11"/>
-    </row>
-    <row r="237" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN236" s="11"/>
+      <c r="BQ236" s="11"/>
+    </row>
+    <row r="237" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D237" s="9"/>
       <c r="E237" s="10"/>
-      <c r="BO237" s="11"/>
-      <c r="BR237" s="11"/>
-    </row>
-    <row r="238" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN237" s="11"/>
+      <c r="BQ237" s="11"/>
+    </row>
+    <row r="238" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D238" s="9"/>
       <c r="E238" s="10"/>
-      <c r="BO238" s="11"/>
-      <c r="BR238" s="11"/>
-    </row>
-    <row r="239" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN238" s="11"/>
+      <c r="BQ238" s="11"/>
+    </row>
+    <row r="239" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D239" s="9"/>
       <c r="E239" s="10"/>
-      <c r="BO239" s="11"/>
-      <c r="BR239" s="11"/>
-    </row>
-    <row r="240" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN239" s="11"/>
+      <c r="BQ239" s="11"/>
+    </row>
+    <row r="240" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D240" s="9"/>
       <c r="E240" s="10"/>
-      <c r="BO240" s="11"/>
-      <c r="BR240" s="11"/>
-    </row>
-    <row r="241" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN240" s="11"/>
+      <c r="BQ240" s="11"/>
+    </row>
+    <row r="241" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D241" s="9"/>
       <c r="E241" s="10"/>
-      <c r="BO241" s="11"/>
-      <c r="BR241" s="11"/>
-    </row>
-    <row r="242" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN241" s="11"/>
+      <c r="BQ241" s="11"/>
+    </row>
+    <row r="242" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D242" s="9"/>
       <c r="E242" s="10"/>
-      <c r="BO242" s="11"/>
-      <c r="BR242" s="11"/>
-    </row>
-    <row r="243" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN242" s="11"/>
+      <c r="BQ242" s="11"/>
+    </row>
+    <row r="243" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D243" s="9"/>
       <c r="E243" s="10"/>
-      <c r="BO243" s="11"/>
-      <c r="BR243" s="11"/>
-    </row>
-    <row r="244" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN243" s="11"/>
+      <c r="BQ243" s="11"/>
+    </row>
+    <row r="244" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D244" s="9"/>
       <c r="E244" s="10"/>
-      <c r="BO244" s="11"/>
-      <c r="BR244" s="11"/>
-    </row>
-    <row r="245" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN244" s="11"/>
+      <c r="BQ244" s="11"/>
+    </row>
+    <row r="245" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D245" s="9"/>
       <c r="E245" s="10"/>
-      <c r="BO245" s="11"/>
-      <c r="BR245" s="11"/>
-    </row>
-    <row r="246" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN245" s="11"/>
+      <c r="BQ245" s="11"/>
+    </row>
+    <row r="246" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D246" s="9"/>
       <c r="E246" s="10"/>
-      <c r="BO246" s="11"/>
-      <c r="BR246" s="11"/>
-    </row>
-    <row r="247" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN246" s="11"/>
+      <c r="BQ246" s="11"/>
+    </row>
+    <row r="247" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D247" s="9"/>
       <c r="E247" s="10"/>
-      <c r="BO247" s="11"/>
-      <c r="BR247" s="11"/>
-    </row>
-    <row r="248" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN247" s="11"/>
+      <c r="BQ247" s="11"/>
+    </row>
+    <row r="248" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D248" s="9"/>
       <c r="E248" s="10"/>
-      <c r="BO248" s="11"/>
-      <c r="BR248" s="11"/>
-    </row>
-    <row r="249" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN248" s="11"/>
+      <c r="BQ248" s="11"/>
+    </row>
+    <row r="249" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D249" s="9"/>
       <c r="E249" s="10"/>
-      <c r="BO249" s="11"/>
-      <c r="BR249" s="11"/>
-    </row>
-    <row r="250" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN249" s="11"/>
+      <c r="BQ249" s="11"/>
+    </row>
+    <row r="250" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D250" s="9"/>
       <c r="E250" s="10"/>
-      <c r="BO250" s="11"/>
-      <c r="BR250" s="11"/>
-    </row>
-    <row r="251" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN250" s="11"/>
+      <c r="BQ250" s="11"/>
+    </row>
+    <row r="251" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D251" s="9"/>
       <c r="E251" s="10"/>
-      <c r="BO251" s="11"/>
-      <c r="BR251" s="11"/>
-    </row>
-    <row r="252" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN251" s="11"/>
+      <c r="BQ251" s="11"/>
+    </row>
+    <row r="252" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D252" s="9"/>
       <c r="E252" s="10"/>
-      <c r="BO252" s="11"/>
-      <c r="BR252" s="11"/>
-    </row>
-    <row r="253" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN252" s="11"/>
+      <c r="BQ252" s="11"/>
+    </row>
+    <row r="253" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D253" s="9"/>
       <c r="E253" s="10"/>
-      <c r="BO253" s="11"/>
-      <c r="BR253" s="11"/>
-    </row>
-    <row r="254" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN253" s="11"/>
+      <c r="BQ253" s="11"/>
+    </row>
+    <row r="254" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D254" s="9"/>
       <c r="E254" s="10"/>
-      <c r="BO254" s="11"/>
-      <c r="BR254" s="11"/>
-    </row>
-    <row r="255" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN254" s="11"/>
+      <c r="BQ254" s="11"/>
+    </row>
+    <row r="255" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D255" s="9"/>
       <c r="E255" s="10"/>
-      <c r="BO255" s="11"/>
-      <c r="BR255" s="11"/>
-    </row>
-    <row r="256" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN255" s="11"/>
+      <c r="BQ255" s="11"/>
+    </row>
+    <row r="256" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D256" s="9"/>
       <c r="E256" s="10"/>
-      <c r="BO256" s="11"/>
-      <c r="BR256" s="11"/>
-    </row>
-    <row r="257" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN256" s="11"/>
+      <c r="BQ256" s="11"/>
+    </row>
+    <row r="257" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D257" s="9"/>
       <c r="E257" s="10"/>
-      <c r="BO257" s="11"/>
-      <c r="BR257" s="11"/>
-    </row>
-    <row r="258" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN257" s="11"/>
+      <c r="BQ257" s="11"/>
+    </row>
+    <row r="258" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D258" s="9"/>
       <c r="E258" s="10"/>
-      <c r="BO258" s="11"/>
-      <c r="BR258" s="11"/>
-    </row>
-    <row r="259" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN258" s="11"/>
+      <c r="BQ258" s="11"/>
+    </row>
+    <row r="259" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D259" s="9"/>
       <c r="E259" s="10"/>
-      <c r="BO259" s="11"/>
-      <c r="BR259" s="11"/>
-    </row>
-    <row r="260" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN259" s="11"/>
+      <c r="BQ259" s="11"/>
+    </row>
+    <row r="260" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D260" s="9"/>
       <c r="E260" s="10"/>
-      <c r="BO260" s="11"/>
-      <c r="BR260" s="11"/>
-    </row>
-    <row r="261" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN260" s="11"/>
+      <c r="BQ260" s="11"/>
+    </row>
+    <row r="261" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D261" s="9"/>
       <c r="E261" s="10"/>
-      <c r="BO261" s="11"/>
-      <c r="BR261" s="11"/>
-    </row>
-    <row r="262" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN261" s="11"/>
+      <c r="BQ261" s="11"/>
+    </row>
+    <row r="262" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D262" s="9"/>
       <c r="E262" s="10"/>
-      <c r="BO262" s="11"/>
-      <c r="BR262" s="11"/>
-    </row>
-    <row r="263" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN262" s="11"/>
+      <c r="BQ262" s="11"/>
+    </row>
+    <row r="263" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D263" s="9"/>
       <c r="E263" s="10"/>
-      <c r="BO263" s="11"/>
-      <c r="BR263" s="11"/>
-    </row>
-    <row r="264" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN263" s="11"/>
+      <c r="BQ263" s="11"/>
+    </row>
+    <row r="264" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D264" s="9"/>
       <c r="E264" s="10"/>
-      <c r="BO264" s="11"/>
-      <c r="BR264" s="11"/>
-    </row>
-    <row r="265" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN264" s="11"/>
+      <c r="BQ264" s="11"/>
+    </row>
+    <row r="265" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D265" s="9"/>
       <c r="E265" s="10"/>
-      <c r="BO265" s="11"/>
-      <c r="BR265" s="11"/>
-    </row>
-    <row r="266" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN265" s="11"/>
+      <c r="BQ265" s="11"/>
+    </row>
+    <row r="266" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D266" s="9"/>
       <c r="E266" s="10"/>
-      <c r="BO266" s="11"/>
-      <c r="BR266" s="11"/>
-    </row>
-    <row r="267" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN266" s="11"/>
+      <c r="BQ266" s="11"/>
+    </row>
+    <row r="267" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D267" s="9"/>
       <c r="E267" s="10"/>
-      <c r="BO267" s="11"/>
-      <c r="BR267" s="11"/>
-    </row>
-    <row r="268" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN267" s="11"/>
+      <c r="BQ267" s="11"/>
+    </row>
+    <row r="268" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D268" s="9"/>
       <c r="E268" s="10"/>
-      <c r="BO268" s="11"/>
-      <c r="BR268" s="11"/>
-    </row>
-    <row r="269" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN268" s="11"/>
+      <c r="BQ268" s="11"/>
+    </row>
+    <row r="269" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D269" s="9"/>
       <c r="E269" s="10"/>
-      <c r="BO269" s="11"/>
-      <c r="BR269" s="11"/>
-    </row>
-    <row r="270" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN269" s="11"/>
+      <c r="BQ269" s="11"/>
+    </row>
+    <row r="270" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D270" s="9"/>
       <c r="E270" s="10"/>
-      <c r="BO270" s="11"/>
-      <c r="BR270" s="11"/>
-    </row>
-    <row r="271" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN270" s="11"/>
+      <c r="BQ270" s="11"/>
+    </row>
+    <row r="271" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D271" s="9"/>
       <c r="E271" s="10"/>
-      <c r="BR271" s="11"/>
-    </row>
-    <row r="272" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ271" s="11"/>
+    </row>
+    <row r="272" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D272" s="9"/>
       <c r="E272" s="10"/>
-      <c r="BO272" s="11"/>
-      <c r="BR272" s="11"/>
-    </row>
-    <row r="273" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN272" s="11"/>
+      <c r="BQ272" s="11"/>
+    </row>
+    <row r="273" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D273" s="9"/>
       <c r="E273" s="10"/>
-      <c r="BO273" s="11"/>
-      <c r="BR273" s="11"/>
-    </row>
-    <row r="274" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN273" s="11"/>
+      <c r="BQ273" s="11"/>
+    </row>
+    <row r="274" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D274" s="9"/>
       <c r="E274" s="10"/>
-      <c r="BO274" s="11"/>
-      <c r="BR274" s="11"/>
-    </row>
-    <row r="275" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN274" s="11"/>
+      <c r="BQ274" s="11"/>
+    </row>
+    <row r="275" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D275" s="9"/>
       <c r="E275" s="10"/>
-      <c r="BO275" s="11"/>
-      <c r="BR275" s="11"/>
-    </row>
-    <row r="276" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN275" s="11"/>
+      <c r="BQ275" s="11"/>
+    </row>
+    <row r="276" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D276" s="9"/>
       <c r="E276" s="10"/>
-      <c r="BO276" s="11"/>
-      <c r="BR276" s="11"/>
-    </row>
-    <row r="277" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN276" s="11"/>
+      <c r="BQ276" s="11"/>
+    </row>
+    <row r="277" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D277" s="9"/>
       <c r="E277" s="10"/>
-      <c r="BO277" s="11"/>
-      <c r="BR277" s="11"/>
-    </row>
-    <row r="278" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN277" s="11"/>
+      <c r="BQ277" s="11"/>
+    </row>
+    <row r="278" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D278" s="9"/>
       <c r="E278" s="10"/>
-      <c r="BO278" s="11"/>
-      <c r="BR278" s="11"/>
-    </row>
-    <row r="279" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN278" s="11"/>
+      <c r="BQ278" s="11"/>
+    </row>
+    <row r="279" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D279" s="9"/>
       <c r="E279" s="10"/>
-      <c r="BO279" s="11"/>
-      <c r="BR279" s="11"/>
-    </row>
-    <row r="280" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN279" s="11"/>
+      <c r="BQ279" s="11"/>
+    </row>
+    <row r="280" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D280" s="9"/>
       <c r="E280" s="10"/>
-      <c r="BO280" s="11"/>
-      <c r="BR280" s="11"/>
-    </row>
-    <row r="281" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN280" s="11"/>
+      <c r="BQ280" s="11"/>
+    </row>
+    <row r="281" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D281" s="9"/>
       <c r="E281" s="10"/>
-      <c r="BO281" s="11"/>
-      <c r="BR281" s="11"/>
-    </row>
-    <row r="282" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN281" s="11"/>
+      <c r="BQ281" s="11"/>
+    </row>
+    <row r="282" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D282" s="9"/>
       <c r="E282" s="10"/>
-      <c r="BO282" s="11"/>
-      <c r="BR282" s="11"/>
-    </row>
-    <row r="283" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN282" s="11"/>
+      <c r="BQ282" s="11"/>
+    </row>
+    <row r="283" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D283" s="9"/>
       <c r="E283" s="10"/>
-      <c r="BO283" s="11"/>
-      <c r="BR283" s="11"/>
-    </row>
-    <row r="284" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN283" s="11"/>
+      <c r="BQ283" s="11"/>
+    </row>
+    <row r="284" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D284" s="9"/>
       <c r="E284" s="10"/>
-      <c r="BO284" s="11"/>
-      <c r="BR284" s="11"/>
-    </row>
-    <row r="285" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN284" s="11"/>
+      <c r="BQ284" s="11"/>
+    </row>
+    <row r="285" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D285" s="9"/>
       <c r="E285" s="10"/>
-      <c r="BO285" s="11"/>
-      <c r="BR285" s="11"/>
-    </row>
-    <row r="286" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN285" s="11"/>
+      <c r="BQ285" s="11"/>
+    </row>
+    <row r="286" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D286" s="9"/>
       <c r="E286" s="10"/>
-      <c r="BO286" s="11"/>
-      <c r="BR286" s="11"/>
-    </row>
-    <row r="287" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN286" s="11"/>
+      <c r="BQ286" s="11"/>
+    </row>
+    <row r="287" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D287" s="9"/>
       <c r="E287" s="10"/>
-      <c r="BO287" s="11"/>
-      <c r="BR287" s="11"/>
-    </row>
-    <row r="288" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN287" s="11"/>
+      <c r="BQ287" s="11"/>
+    </row>
+    <row r="288" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D288" s="9"/>
       <c r="E288" s="10"/>
-      <c r="BO288" s="11"/>
-      <c r="BR288" s="11"/>
-    </row>
-    <row r="289" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN288" s="11"/>
+      <c r="BQ288" s="11"/>
+    </row>
+    <row r="289" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D289" s="9"/>
       <c r="E289" s="10"/>
-      <c r="BO289" s="11"/>
-      <c r="BR289" s="11"/>
-    </row>
-    <row r="290" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN289" s="11"/>
+      <c r="BQ289" s="11"/>
+    </row>
+    <row r="290" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D290" s="9"/>
       <c r="E290" s="10"/>
-      <c r="BO290" s="11"/>
-      <c r="BR290" s="11"/>
-    </row>
-    <row r="291" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN290" s="11"/>
+      <c r="BQ290" s="11"/>
+    </row>
+    <row r="291" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D291" s="9"/>
       <c r="E291" s="10"/>
-      <c r="BO291" s="11"/>
-      <c r="BR291" s="11"/>
-    </row>
-    <row r="292" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN291" s="11"/>
+      <c r="BQ291" s="11"/>
+    </row>
+    <row r="292" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D292" s="9"/>
       <c r="E292" s="10"/>
-      <c r="BO292" s="11"/>
-      <c r="BR292" s="11"/>
-    </row>
-    <row r="293" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN292" s="11"/>
+      <c r="BQ292" s="11"/>
+    </row>
+    <row r="293" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D293" s="9"/>
       <c r="E293" s="10"/>
-      <c r="BO293" s="11"/>
-      <c r="BR293" s="11"/>
-    </row>
-    <row r="294" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN293" s="11"/>
+      <c r="BQ293" s="11"/>
+    </row>
+    <row r="294" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D294" s="9"/>
       <c r="E294" s="10"/>
-      <c r="BO294" s="11"/>
-      <c r="BR294" s="11"/>
-    </row>
-    <row r="295" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN294" s="11"/>
+      <c r="BQ294" s="11"/>
+    </row>
+    <row r="295" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D295" s="9"/>
       <c r="E295" s="10"/>
-      <c r="BO295" s="11"/>
-      <c r="BR295" s="11"/>
-    </row>
-    <row r="296" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN295" s="11"/>
+      <c r="BQ295" s="11"/>
+    </row>
+    <row r="296" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D296" s="9"/>
       <c r="E296" s="10"/>
-      <c r="BO296" s="11"/>
-      <c r="BR296" s="11"/>
-    </row>
-    <row r="297" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN296" s="11"/>
+      <c r="BQ296" s="11"/>
+    </row>
+    <row r="297" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D297" s="9"/>
       <c r="E297" s="10"/>
-      <c r="BO297" s="11"/>
-      <c r="BR297" s="11"/>
-    </row>
-    <row r="298" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN297" s="11"/>
+      <c r="BQ297" s="11"/>
+    </row>
+    <row r="298" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D298" s="9"/>
       <c r="E298" s="10"/>
-      <c r="BO298" s="11"/>
-      <c r="BR298" s="11"/>
-    </row>
-    <row r="299" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN298" s="11"/>
+      <c r="BQ298" s="11"/>
+    </row>
+    <row r="299" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D299" s="9"/>
       <c r="E299" s="10"/>
-      <c r="BO299" s="11"/>
-      <c r="BR299" s="11"/>
-    </row>
-    <row r="300" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN299" s="11"/>
+      <c r="BQ299" s="11"/>
+    </row>
+    <row r="300" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D300" s="9"/>
       <c r="E300" s="10"/>
-      <c r="BO300" s="11"/>
-      <c r="BR300" s="11"/>
-    </row>
-    <row r="301" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN300" s="11"/>
+      <c r="BQ300" s="11"/>
+    </row>
+    <row r="301" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D301" s="9"/>
       <c r="E301" s="10"/>
-      <c r="BO301" s="11"/>
-      <c r="BR301" s="11"/>
-    </row>
-    <row r="302" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN301" s="11"/>
+      <c r="BQ301" s="11"/>
+    </row>
+    <row r="302" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D302" s="9"/>
       <c r="E302" s="10"/>
-      <c r="BO302" s="11"/>
-      <c r="BR302" s="11"/>
-    </row>
-    <row r="303" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN302" s="11"/>
+      <c r="BQ302" s="11"/>
+    </row>
+    <row r="303" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D303" s="9"/>
       <c r="E303" s="10"/>
-      <c r="BO303" s="11"/>
-      <c r="BR303" s="11"/>
-    </row>
-    <row r="304" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN303" s="11"/>
+      <c r="BQ303" s="11"/>
+    </row>
+    <row r="304" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D304" s="9"/>
       <c r="E304" s="10"/>
-      <c r="BO304" s="11"/>
-      <c r="BR304" s="11"/>
-    </row>
-    <row r="305" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN304" s="11"/>
+      <c r="BQ304" s="11"/>
+    </row>
+    <row r="305" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D305" s="9"/>
       <c r="E305" s="10"/>
-      <c r="BO305" s="11"/>
-      <c r="BR305" s="11"/>
-    </row>
-    <row r="306" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN305" s="11"/>
+      <c r="BQ305" s="11"/>
+    </row>
+    <row r="306" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D306" s="9"/>
       <c r="E306" s="10"/>
-      <c r="BO306" s="11"/>
-      <c r="BR306" s="11"/>
-    </row>
-    <row r="307" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN306" s="11"/>
+      <c r="BQ306" s="11"/>
+    </row>
+    <row r="307" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D307" s="9"/>
       <c r="E307" s="10"/>
-      <c r="BO307" s="11"/>
-      <c r="BR307" s="11"/>
-    </row>
-    <row r="308" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN307" s="11"/>
+      <c r="BQ307" s="11"/>
+    </row>
+    <row r="308" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D308" s="9"/>
       <c r="E308" s="10"/>
-      <c r="BO308" s="11"/>
-      <c r="BR308" s="11"/>
-    </row>
-    <row r="309" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN308" s="11"/>
+      <c r="BQ308" s="11"/>
+    </row>
+    <row r="309" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D309" s="9"/>
       <c r="E309" s="10"/>
-      <c r="BO309" s="11"/>
-      <c r="BR309" s="11"/>
-    </row>
-    <row r="310" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN309" s="11"/>
+      <c r="BQ309" s="11"/>
+    </row>
+    <row r="310" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D310" s="9"/>
       <c r="E310" s="10"/>
-      <c r="BO310" s="11"/>
-      <c r="BR310" s="11"/>
-    </row>
-    <row r="311" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN310" s="11"/>
+      <c r="BQ310" s="11"/>
+    </row>
+    <row r="311" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D311" s="9"/>
       <c r="E311" s="10"/>
-      <c r="BO311" s="11"/>
-      <c r="BR311" s="11"/>
-    </row>
-    <row r="312" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN311" s="11"/>
+      <c r="BQ311" s="11"/>
+    </row>
+    <row r="312" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D312" s="9"/>
       <c r="E312" s="10"/>
-      <c r="BO312" s="11"/>
-      <c r="BR312" s="11"/>
-    </row>
-    <row r="313" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN312" s="11"/>
+      <c r="BQ312" s="11"/>
+    </row>
+    <row r="313" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D313" s="9"/>
       <c r="E313" s="10"/>
-      <c r="BO313" s="11"/>
-      <c r="BR313" s="11"/>
-    </row>
-    <row r="314" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN313" s="11"/>
+      <c r="BQ313" s="11"/>
+    </row>
+    <row r="314" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D314" s="9"/>
       <c r="E314" s="10"/>
-      <c r="BO314" s="11"/>
-      <c r="BR314" s="11"/>
-    </row>
-    <row r="315" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN314" s="11"/>
+      <c r="BQ314" s="11"/>
+    </row>
+    <row r="315" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D315" s="9"/>
       <c r="E315" s="10"/>
-      <c r="BO315" s="11"/>
-      <c r="BR315" s="11"/>
-    </row>
-    <row r="316" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN315" s="11"/>
+      <c r="BQ315" s="11"/>
+    </row>
+    <row r="316" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D316" s="9"/>
       <c r="E316" s="10"/>
-      <c r="BO316" s="11"/>
-      <c r="BR316" s="11"/>
-    </row>
-    <row r="317" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN316" s="11"/>
+      <c r="BQ316" s="11"/>
+    </row>
+    <row r="317" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D317" s="9"/>
       <c r="E317" s="10"/>
-      <c r="BO317" s="11"/>
-      <c r="BR317" s="11"/>
-    </row>
-    <row r="318" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN317" s="11"/>
+      <c r="BQ317" s="11"/>
+    </row>
+    <row r="318" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D318" s="9"/>
       <c r="E318" s="10"/>
-      <c r="BO318" s="11"/>
-      <c r="BR318" s="11"/>
-    </row>
-    <row r="319" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN318" s="11"/>
+      <c r="BQ318" s="11"/>
+    </row>
+    <row r="319" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D319" s="9"/>
       <c r="E319" s="10"/>
-      <c r="BO319" s="11"/>
-      <c r="BR319" s="11"/>
-    </row>
-    <row r="320" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN319" s="11"/>
+      <c r="BQ319" s="11"/>
+    </row>
+    <row r="320" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D320" s="9"/>
       <c r="E320" s="10"/>
-      <c r="BO320" s="11"/>
-      <c r="BR320" s="11"/>
-    </row>
-    <row r="321" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN320" s="11"/>
+      <c r="BQ320" s="11"/>
+    </row>
+    <row r="321" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D321" s="9"/>
       <c r="E321" s="10"/>
-      <c r="BO321" s="11"/>
-      <c r="BR321" s="11"/>
-    </row>
-    <row r="322" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN321" s="11"/>
+      <c r="BQ321" s="11"/>
+    </row>
+    <row r="322" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D322" s="9"/>
       <c r="E322" s="10"/>
-      <c r="BO322" s="11"/>
-      <c r="BR322" s="11"/>
-    </row>
-    <row r="323" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN322" s="11"/>
+      <c r="BQ322" s="11"/>
+    </row>
+    <row r="323" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D323" s="9"/>
       <c r="E323" s="10"/>
-      <c r="BO323" s="11"/>
-      <c r="BR323" s="11"/>
-    </row>
-    <row r="324" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN323" s="11"/>
+      <c r="BQ323" s="11"/>
+    </row>
+    <row r="324" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D324" s="9"/>
       <c r="E324" s="10"/>
-      <c r="BO324" s="11"/>
-      <c r="BR324" s="11"/>
-    </row>
-    <row r="325" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN324" s="11"/>
+      <c r="BQ324" s="11"/>
+    </row>
+    <row r="325" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D325" s="9"/>
       <c r="E325" s="10"/>
-      <c r="BO325" s="11"/>
-      <c r="BR325" s="11"/>
-    </row>
-    <row r="326" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN325" s="11"/>
+      <c r="BQ325" s="11"/>
+    </row>
+    <row r="326" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D326" s="9"/>
       <c r="E326" s="10"/>
-      <c r="BO326" s="11"/>
-      <c r="BR326" s="11"/>
-    </row>
-    <row r="327" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN326" s="11"/>
+      <c r="BQ326" s="11"/>
+    </row>
+    <row r="327" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D327" s="9"/>
       <c r="E327" s="10"/>
-      <c r="BR327" s="11"/>
-    </row>
-    <row r="328" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ327" s="11"/>
+    </row>
+    <row r="328" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D328" s="9"/>
       <c r="E328" s="10"/>
-      <c r="BR328" s="11"/>
-    </row>
-    <row r="329" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ328" s="11"/>
+    </row>
+    <row r="329" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D329" s="9"/>
       <c r="E329" s="10"/>
-      <c r="BR329" s="11"/>
-    </row>
-    <row r="330" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ329" s="11"/>
+    </row>
+    <row r="330" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D330" s="9"/>
       <c r="E330" s="10"/>
-      <c r="BO330" s="11"/>
-      <c r="BR330" s="11"/>
-    </row>
-    <row r="331" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN330" s="11"/>
+      <c r="BQ330" s="11"/>
+    </row>
+    <row r="331" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D331" s="9"/>
       <c r="E331" s="10"/>
-      <c r="BO331" s="11"/>
-      <c r="BR331" s="11"/>
-    </row>
-    <row r="332" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN331" s="11"/>
+      <c r="BQ331" s="11"/>
+    </row>
+    <row r="332" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D332" s="9"/>
       <c r="E332" s="10"/>
-      <c r="BO332" s="11"/>
-      <c r="BR332" s="11"/>
-    </row>
-    <row r="333" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN332" s="11"/>
+      <c r="BQ332" s="11"/>
+    </row>
+    <row r="333" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D333" s="9"/>
       <c r="E333" s="10"/>
-      <c r="BO333" s="11"/>
-      <c r="BR333" s="11"/>
-    </row>
-    <row r="334" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN333" s="11"/>
+      <c r="BQ333" s="11"/>
+    </row>
+    <row r="334" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D334" s="9"/>
       <c r="E334" s="10"/>
-      <c r="BO334" s="11"/>
-      <c r="BR334" s="11"/>
-    </row>
-    <row r="335" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN334" s="11"/>
+      <c r="BQ334" s="11"/>
+    </row>
+    <row r="335" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D335" s="9"/>
       <c r="E335" s="10"/>
-      <c r="BO335" s="11"/>
-      <c r="BR335" s="11"/>
-    </row>
-    <row r="336" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN335" s="11"/>
+      <c r="BQ335" s="11"/>
+    </row>
+    <row r="336" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D336" s="9"/>
       <c r="E336" s="10"/>
-      <c r="BO336" s="11"/>
-      <c r="BR336" s="11"/>
-    </row>
-    <row r="337" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN336" s="11"/>
+      <c r="BQ336" s="11"/>
+    </row>
+    <row r="337" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D337" s="9"/>
       <c r="E337" s="10"/>
-      <c r="BO337" s="11"/>
-      <c r="BR337" s="11"/>
-    </row>
-    <row r="338" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN337" s="11"/>
+      <c r="BQ337" s="11"/>
+    </row>
+    <row r="338" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D338" s="9"/>
       <c r="E338" s="10"/>
-      <c r="BO338" s="11"/>
-      <c r="BR338" s="11"/>
-    </row>
-    <row r="339" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN338" s="11"/>
+      <c r="BQ338" s="11"/>
+    </row>
+    <row r="339" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D339" s="9"/>
       <c r="E339" s="10"/>
-      <c r="BO339" s="11"/>
-      <c r="BR339" s="11"/>
-    </row>
-    <row r="340" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN339" s="11"/>
+      <c r="BQ339" s="11"/>
+    </row>
+    <row r="340" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D340" s="9"/>
       <c r="E340" s="10"/>
-      <c r="BO340" s="11"/>
-      <c r="BR340" s="11"/>
-    </row>
-    <row r="341" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN340" s="11"/>
+      <c r="BQ340" s="11"/>
+    </row>
+    <row r="341" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D341" s="9"/>
       <c r="E341" s="10"/>
-      <c r="BO341" s="11"/>
-      <c r="BR341" s="11"/>
-    </row>
-    <row r="342" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN341" s="11"/>
+      <c r="BQ341" s="11"/>
+    </row>
+    <row r="342" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D342" s="9"/>
       <c r="E342" s="10"/>
-      <c r="BO342" s="11"/>
-      <c r="BR342" s="11"/>
-    </row>
-    <row r="343" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN342" s="11"/>
+      <c r="BQ342" s="11"/>
+    </row>
+    <row r="343" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D343" s="9"/>
       <c r="E343" s="10"/>
-      <c r="BO343" s="11"/>
-      <c r="BR343" s="11"/>
-    </row>
-    <row r="344" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN343" s="11"/>
+      <c r="BQ343" s="11"/>
+    </row>
+    <row r="344" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D344" s="9"/>
       <c r="E344" s="10"/>
-      <c r="BO344" s="11"/>
-      <c r="BR344" s="11"/>
-    </row>
-    <row r="345" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN344" s="11"/>
+      <c r="BQ344" s="11"/>
+    </row>
+    <row r="345" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D345" s="9"/>
       <c r="E345" s="10"/>
-      <c r="BO345" s="11"/>
-      <c r="BR345" s="11"/>
-    </row>
-    <row r="346" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN345" s="11"/>
+      <c r="BQ345" s="11"/>
+    </row>
+    <row r="346" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D346" s="9"/>
       <c r="E346" s="10"/>
-      <c r="BO346" s="11"/>
-      <c r="BR346" s="11"/>
-    </row>
-    <row r="347" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN346" s="11"/>
+      <c r="BQ346" s="11"/>
+    </row>
+    <row r="347" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D347" s="9"/>
       <c r="E347" s="10"/>
-      <c r="BO347" s="11"/>
-      <c r="BR347" s="11"/>
-    </row>
-    <row r="348" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN347" s="11"/>
+      <c r="BQ347" s="11"/>
+    </row>
+    <row r="348" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D348" s="9"/>
       <c r="E348" s="10"/>
-      <c r="BO348" s="11"/>
-      <c r="BR348" s="11"/>
-    </row>
-    <row r="349" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN348" s="11"/>
+      <c r="BQ348" s="11"/>
+    </row>
+    <row r="349" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D349" s="9"/>
       <c r="E349" s="10"/>
-      <c r="BO349" s="11"/>
-      <c r="BR349" s="11"/>
-    </row>
-    <row r="350" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN349" s="11"/>
+      <c r="BQ349" s="11"/>
+    </row>
+    <row r="350" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D350" s="9"/>
       <c r="E350" s="10"/>
-      <c r="BO350" s="11"/>
-      <c r="BR350" s="11"/>
-    </row>
-    <row r="351" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN350" s="11"/>
+      <c r="BQ350" s="11"/>
+    </row>
+    <row r="351" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D351" s="9"/>
       <c r="E351" s="10"/>
-      <c r="BO351" s="11"/>
-      <c r="BR351" s="11"/>
-    </row>
-    <row r="352" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN351" s="11"/>
+      <c r="BQ351" s="11"/>
+    </row>
+    <row r="352" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D352" s="9"/>
       <c r="E352" s="10"/>
-      <c r="BO352" s="11"/>
-      <c r="BR352" s="11"/>
-    </row>
-    <row r="353" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN352" s="11"/>
+      <c r="BQ352" s="11"/>
+    </row>
+    <row r="353" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D353" s="9"/>
       <c r="E353" s="10"/>
-      <c r="BO353" s="11"/>
-      <c r="BR353" s="11"/>
-    </row>
-    <row r="354" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN353" s="11"/>
+      <c r="BQ353" s="11"/>
+    </row>
+    <row r="354" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D354" s="9"/>
       <c r="E354" s="10"/>
-      <c r="BO354" s="11"/>
-      <c r="BR354" s="11"/>
-    </row>
-    <row r="355" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN354" s="11"/>
+      <c r="BQ354" s="11"/>
+    </row>
+    <row r="355" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D355" s="9"/>
       <c r="E355" s="10"/>
-      <c r="BO355" s="11"/>
-      <c r="BR355" s="11"/>
-    </row>
-    <row r="356" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN355" s="11"/>
+      <c r="BQ355" s="11"/>
+    </row>
+    <row r="356" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D356" s="9"/>
       <c r="E356" s="10"/>
-      <c r="BO356" s="11"/>
-      <c r="BR356" s="11"/>
-    </row>
-    <row r="357" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN356" s="11"/>
+      <c r="BQ356" s="11"/>
+    </row>
+    <row r="357" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D357" s="9"/>
       <c r="E357" s="10"/>
-      <c r="BO357" s="11"/>
-      <c r="BR357" s="11"/>
-    </row>
-    <row r="358" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN357" s="11"/>
+      <c r="BQ357" s="11"/>
+    </row>
+    <row r="358" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D358" s="9"/>
       <c r="E358" s="10"/>
-      <c r="BO358" s="11"/>
-      <c r="BR358" s="11"/>
-    </row>
-    <row r="359" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN358" s="11"/>
+      <c r="BQ358" s="11"/>
+    </row>
+    <row r="359" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D359" s="9"/>
       <c r="E359" s="10"/>
-      <c r="BO359" s="11"/>
-      <c r="BR359" s="11"/>
-    </row>
-    <row r="360" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN359" s="11"/>
+      <c r="BQ359" s="11"/>
+    </row>
+    <row r="360" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D360" s="9"/>
       <c r="E360" s="10"/>
-      <c r="BO360" s="11"/>
-      <c r="BR360" s="11"/>
-    </row>
-    <row r="361" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN360" s="11"/>
+      <c r="BQ360" s="11"/>
+    </row>
+    <row r="361" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D361" s="9"/>
       <c r="E361" s="10"/>
-      <c r="BO361" s="11"/>
-      <c r="BR361" s="11"/>
-    </row>
-    <row r="362" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN361" s="11"/>
+      <c r="BQ361" s="11"/>
+    </row>
+    <row r="362" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D362" s="9"/>
       <c r="E362" s="10"/>
-      <c r="BO362" s="11"/>
-      <c r="BR362" s="11"/>
-    </row>
-    <row r="363" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN362" s="11"/>
+      <c r="BQ362" s="11"/>
+    </row>
+    <row r="363" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D363" s="9"/>
       <c r="E363" s="10"/>
-      <c r="BO363" s="11"/>
-      <c r="BR363" s="11"/>
-    </row>
-    <row r="364" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN363" s="11"/>
+      <c r="BQ363" s="11"/>
+    </row>
+    <row r="364" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D364" s="9"/>
       <c r="E364" s="10"/>
-      <c r="BR364" s="11"/>
-    </row>
-    <row r="365" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ364" s="11"/>
+    </row>
+    <row r="365" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D365" s="9"/>
       <c r="E365" s="10"/>
-      <c r="BR365" s="11"/>
-    </row>
-    <row r="366" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ365" s="11"/>
+    </row>
+    <row r="366" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D366" s="9"/>
       <c r="E366" s="10"/>
-      <c r="BO366" s="11"/>
-      <c r="BR366" s="11"/>
-    </row>
-    <row r="367" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN366" s="11"/>
+      <c r="BQ366" s="11"/>
+    </row>
+    <row r="367" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D367" s="9"/>
       <c r="E367" s="10"/>
-      <c r="BO367" s="11"/>
-      <c r="BR367" s="11"/>
-    </row>
-    <row r="368" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN367" s="11"/>
+      <c r="BQ367" s="11"/>
+    </row>
+    <row r="368" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D368" s="9"/>
       <c r="E368" s="10"/>
-      <c r="BO368" s="11"/>
-      <c r="BR368" s="11"/>
-    </row>
-    <row r="369" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN368" s="11"/>
+      <c r="BQ368" s="11"/>
+    </row>
+    <row r="369" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D369" s="9"/>
       <c r="E369" s="10"/>
-      <c r="BO369" s="11"/>
-      <c r="BR369" s="11"/>
-    </row>
-    <row r="370" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN369" s="11"/>
+      <c r="BQ369" s="11"/>
+    </row>
+    <row r="370" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D370" s="9"/>
       <c r="E370" s="10"/>
-      <c r="BO370" s="11"/>
-      <c r="BR370" s="11"/>
-    </row>
-    <row r="371" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN370" s="11"/>
+      <c r="BQ370" s="11"/>
+    </row>
+    <row r="371" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D371" s="9"/>
       <c r="E371" s="10"/>
-      <c r="BO371" s="11"/>
-      <c r="BR371" s="11"/>
-    </row>
-    <row r="372" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN371" s="11"/>
+      <c r="BQ371" s="11"/>
+    </row>
+    <row r="372" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D372" s="9"/>
       <c r="E372" s="10"/>
-      <c r="BO372" s="11"/>
-      <c r="BR372" s="11"/>
-    </row>
-    <row r="373" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN372" s="11"/>
+      <c r="BQ372" s="11"/>
+    </row>
+    <row r="373" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D373" s="9"/>
       <c r="E373" s="10"/>
-      <c r="BO373" s="11"/>
-      <c r="BR373" s="11"/>
-    </row>
-    <row r="374" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN373" s="11"/>
+      <c r="BQ373" s="11"/>
+    </row>
+    <row r="374" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D374" s="9"/>
       <c r="E374" s="10"/>
-      <c r="BO374" s="11"/>
-      <c r="BR374" s="11"/>
-    </row>
-    <row r="375" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN374" s="11"/>
+      <c r="BQ374" s="11"/>
+    </row>
+    <row r="375" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D375" s="9"/>
       <c r="E375" s="10"/>
-      <c r="BO375" s="11"/>
-      <c r="BR375" s="11"/>
-    </row>
-    <row r="376" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN375" s="11"/>
+      <c r="BQ375" s="11"/>
+    </row>
+    <row r="376" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D376" s="9"/>
       <c r="E376" s="10"/>
-      <c r="BO376" s="11"/>
-      <c r="BR376" s="11"/>
-    </row>
-    <row r="377" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN376" s="11"/>
+      <c r="BQ376" s="11"/>
+    </row>
+    <row r="377" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D377" s="9"/>
       <c r="E377" s="10"/>
-      <c r="BO377" s="11"/>
-      <c r="BR377" s="11"/>
-    </row>
-    <row r="378" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN377" s="11"/>
+      <c r="BQ377" s="11"/>
+    </row>
+    <row r="378" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D378" s="9"/>
       <c r="E378" s="10"/>
-      <c r="BO378" s="11"/>
-      <c r="BR378" s="11"/>
-    </row>
-    <row r="379" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN378" s="11"/>
+      <c r="BQ378" s="11"/>
+    </row>
+    <row r="379" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D379" s="9"/>
       <c r="E379" s="10"/>
-      <c r="BO379" s="11"/>
-      <c r="BR379" s="11"/>
-    </row>
-    <row r="380" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN379" s="11"/>
+      <c r="BQ379" s="11"/>
+    </row>
+    <row r="380" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D380" s="9"/>
       <c r="E380" s="10"/>
-      <c r="BO380" s="11"/>
-      <c r="BR380" s="11"/>
-    </row>
-    <row r="381" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN380" s="11"/>
+      <c r="BQ380" s="11"/>
+    </row>
+    <row r="381" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D381" s="9"/>
       <c r="E381" s="10"/>
-      <c r="BO381" s="11"/>
-      <c r="BR381" s="11"/>
-    </row>
-    <row r="382" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN381" s="11"/>
+      <c r="BQ381" s="11"/>
+    </row>
+    <row r="382" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D382" s="9"/>
       <c r="E382" s="10"/>
-      <c r="BO382" s="11"/>
-      <c r="BR382" s="11"/>
-    </row>
-    <row r="383" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN382" s="11"/>
+      <c r="BQ382" s="11"/>
+    </row>
+    <row r="383" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D383" s="9"/>
       <c r="E383" s="10"/>
-      <c r="BO383" s="11"/>
-      <c r="BR383" s="11"/>
-    </row>
-    <row r="384" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN383" s="11"/>
+      <c r="BQ383" s="11"/>
+    </row>
+    <row r="384" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D384" s="9"/>
       <c r="E384" s="10"/>
-      <c r="BO384" s="11"/>
-      <c r="BR384" s="11"/>
-    </row>
-    <row r="385" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN384" s="11"/>
+      <c r="BQ384" s="11"/>
+    </row>
+    <row r="385" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D385" s="9"/>
       <c r="E385" s="10"/>
-      <c r="BO385" s="11"/>
-      <c r="BR385" s="11"/>
-    </row>
-    <row r="386" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN385" s="11"/>
+      <c r="BQ385" s="11"/>
+    </row>
+    <row r="386" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D386" s="9"/>
       <c r="E386" s="10"/>
-      <c r="BO386" s="11"/>
-      <c r="BR386" s="11"/>
-    </row>
-    <row r="387" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN386" s="11"/>
+      <c r="BQ386" s="11"/>
+    </row>
+    <row r="387" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D387" s="9"/>
       <c r="E387" s="10"/>
-      <c r="BO387" s="11"/>
-      <c r="BR387" s="11"/>
-    </row>
-    <row r="388" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN387" s="11"/>
+      <c r="BQ387" s="11"/>
+    </row>
+    <row r="388" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D388" s="9"/>
       <c r="E388" s="10"/>
-      <c r="BO388" s="11"/>
-      <c r="BR388" s="11"/>
-    </row>
-    <row r="389" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN388" s="11"/>
+      <c r="BQ388" s="11"/>
+    </row>
+    <row r="389" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D389" s="9"/>
       <c r="E389" s="10"/>
-      <c r="BR389" s="11"/>
-    </row>
-    <row r="390" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ389" s="11"/>
+    </row>
+    <row r="390" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D390" s="9"/>
       <c r="E390" s="10"/>
-      <c r="BR390" s="11"/>
-    </row>
-    <row r="391" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ390" s="11"/>
+    </row>
+    <row r="391" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D391" s="9"/>
       <c r="E391" s="10"/>
-      <c r="BO391" s="11"/>
-      <c r="BR391" s="11"/>
-    </row>
-    <row r="392" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN391" s="11"/>
+      <c r="BQ391" s="11"/>
+    </row>
+    <row r="392" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D392" s="9"/>
       <c r="E392" s="10"/>
-      <c r="BO392" s="11"/>
-      <c r="BR392" s="11"/>
-    </row>
-    <row r="393" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN392" s="11"/>
+      <c r="BQ392" s="11"/>
+    </row>
+    <row r="393" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D393" s="9"/>
       <c r="E393" s="10"/>
-      <c r="BR393" s="11"/>
-    </row>
-    <row r="394" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ393" s="11"/>
+    </row>
+    <row r="394" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D394" s="9"/>
       <c r="E394" s="10"/>
-      <c r="BR394" s="11"/>
-    </row>
-    <row r="395" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ394" s="11"/>
+    </row>
+    <row r="395" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D395" s="9"/>
       <c r="E395" s="10"/>
-      <c r="BO395" s="11"/>
-      <c r="BR395" s="11"/>
-    </row>
-    <row r="396" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN395" s="11"/>
+      <c r="BQ395" s="11"/>
+    </row>
+    <row r="396" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D396" s="9"/>
       <c r="E396" s="10"/>
-      <c r="BO396" s="11"/>
-      <c r="BR396" s="11"/>
-    </row>
-    <row r="397" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN396" s="11"/>
+      <c r="BQ396" s="11"/>
+    </row>
+    <row r="397" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D397" s="9"/>
       <c r="E397" s="10"/>
-      <c r="BO397" s="11"/>
-      <c r="BR397" s="11"/>
-    </row>
-    <row r="398" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN397" s="11"/>
+      <c r="BQ397" s="11"/>
+    </row>
+    <row r="398" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D398" s="9"/>
       <c r="E398" s="10"/>
-      <c r="BO398" s="11"/>
-      <c r="BR398" s="11"/>
-    </row>
-    <row r="399" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN398" s="11"/>
+      <c r="BQ398" s="11"/>
+    </row>
+    <row r="399" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D399" s="9"/>
       <c r="E399" s="10"/>
-      <c r="BO399" s="11"/>
-      <c r="BR399" s="11"/>
-    </row>
-    <row r="400" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN399" s="11"/>
+      <c r="BQ399" s="11"/>
+    </row>
+    <row r="400" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D400" s="9"/>
       <c r="E400" s="10"/>
-      <c r="BO400" s="11"/>
-      <c r="BR400" s="11"/>
-    </row>
-    <row r="401" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN400" s="11"/>
+      <c r="BQ400" s="11"/>
+    </row>
+    <row r="401" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D401" s="9"/>
       <c r="E401" s="10"/>
-      <c r="BO401" s="11"/>
-      <c r="BR401" s="11"/>
-    </row>
-    <row r="402" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN401" s="11"/>
+      <c r="BQ401" s="11"/>
+    </row>
+    <row r="402" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D402" s="9"/>
       <c r="E402" s="10"/>
-      <c r="BO402" s="11"/>
-      <c r="BR402" s="11"/>
-    </row>
-    <row r="403" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN402" s="11"/>
+      <c r="BQ402" s="11"/>
+    </row>
+    <row r="403" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D403" s="9"/>
       <c r="E403" s="10"/>
-      <c r="BO403" s="11"/>
-      <c r="BR403" s="11"/>
-    </row>
-    <row r="404" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN403" s="11"/>
+      <c r="BQ403" s="11"/>
+    </row>
+    <row r="404" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D404" s="9"/>
       <c r="E404" s="10"/>
-      <c r="BO404" s="11"/>
-      <c r="BR404" s="11"/>
-    </row>
-    <row r="405" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN404" s="11"/>
+      <c r="BQ404" s="11"/>
+    </row>
+    <row r="405" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D405" s="9"/>
       <c r="E405" s="10"/>
-      <c r="BO405" s="11"/>
-      <c r="BR405" s="11"/>
-    </row>
-    <row r="406" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN405" s="11"/>
+      <c r="BQ405" s="11"/>
+    </row>
+    <row r="406" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D406" s="9"/>
       <c r="E406" s="10"/>
-      <c r="BO406" s="11"/>
-      <c r="BR406" s="11"/>
-    </row>
-    <row r="407" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN406" s="11"/>
+      <c r="BQ406" s="11"/>
+    </row>
+    <row r="407" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D407" s="9"/>
       <c r="E407" s="10"/>
-      <c r="BO407" s="11"/>
-      <c r="BR407" s="11"/>
-    </row>
-    <row r="408" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN407" s="11"/>
+      <c r="BQ407" s="11"/>
+    </row>
+    <row r="408" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D408" s="9"/>
       <c r="E408" s="10"/>
-      <c r="BO408" s="11"/>
-      <c r="BR408" s="11"/>
-    </row>
-    <row r="409" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN408" s="11"/>
+      <c r="BQ408" s="11"/>
+    </row>
+    <row r="409" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D409" s="9"/>
       <c r="E409" s="10"/>
-      <c r="BO409" s="11"/>
-      <c r="BR409" s="11"/>
-    </row>
-    <row r="410" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN409" s="11"/>
+      <c r="BQ409" s="11"/>
+    </row>
+    <row r="410" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D410" s="9"/>
       <c r="E410" s="10"/>
-      <c r="BO410" s="11"/>
-      <c r="BR410" s="11"/>
-    </row>
-    <row r="411" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN410" s="11"/>
+      <c r="BQ410" s="11"/>
+    </row>
+    <row r="411" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D411" s="9"/>
       <c r="E411" s="10"/>
-      <c r="BO411" s="11"/>
-      <c r="BR411" s="11"/>
-    </row>
-    <row r="412" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN411" s="11"/>
+      <c r="BQ411" s="11"/>
+    </row>
+    <row r="412" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D412" s="9"/>
       <c r="E412" s="10"/>
     </row>
-    <row r="413" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="413" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D413" s="9"/>
       <c r="E413" s="10"/>
     </row>
-    <row r="414" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="414" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D414" s="9"/>
       <c r="E414" s="10"/>
     </row>
-    <row r="415" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="415" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D415" s="9"/>
       <c r="E415" s="10"/>
     </row>
-    <row r="416" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="416" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D416" s="9"/>
       <c r="E416" s="10"/>
     </row>
@@ -6010,334 +6011,334 @@
   <sheetData>
     <row r="1" spans="1:113" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
+        <v>137</v>
+      </c>
+      <c r="D1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E1" t="s">
+        <v>139</v>
+      </c>
+      <c r="F1" t="s">
+        <v>140</v>
+      </c>
+      <c r="G1" t="s">
         <v>141</v>
       </c>
-      <c r="D1" t="s">
+      <c r="H1" t="s">
         <v>142</v>
       </c>
-      <c r="E1" t="s">
+      <c r="I1" t="s">
         <v>143</v>
       </c>
-      <c r="F1" t="s">
+      <c r="J1" t="s">
         <v>144</v>
       </c>
-      <c r="G1" t="s">
+      <c r="K1" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="H1" t="s">
+      <c r="L1" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="I1" t="s">
+      <c r="M1" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="J1" t="s">
+      <c r="N1" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="O1" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="P1" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="Q1" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="R1" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="S1" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="T1" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="U1" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="V1" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="R1" s="4" t="s">
+      <c r="W1" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="S1" s="4" t="s">
+      <c r="X1" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="T1" s="4" t="s">
+      <c r="Y1" t="s">
         <v>158</v>
       </c>
-      <c r="U1" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="V1" s="4" t="s">
+      <c r="Z1" t="s">
         <v>159</v>
       </c>
-      <c r="W1" s="4" t="s">
+      <c r="AA1" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="X1" s="4" t="s">
+      <c r="AB1" t="s">
         <v>161</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="AC1" t="s">
         <v>162</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AD1" t="s">
         <v>163</v>
       </c>
-      <c r="AA1" s="4" t="s">
+      <c r="AE1" t="s">
         <v>164</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AF1" t="s">
         <v>165</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AG1" t="s">
         <v>166</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AH1" t="s">
         <v>167</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AI1" t="s">
         <v>168</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AJ1" t="s">
         <v>169</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AK1" t="s">
         <v>170</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AL1" t="s">
         <v>171</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AM1" t="s">
         <v>172</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AN1" t="s">
         <v>173</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AO1" t="s">
         <v>174</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AP1" t="s">
         <v>175</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AQ1" t="s">
         <v>176</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AR1" s="13" t="s">
+        <v>531</v>
+      </c>
+      <c r="AS1" s="13" t="s">
+        <v>532</v>
+      </c>
+      <c r="AT1" t="s">
         <v>177</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AU1" t="s">
         <v>178</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AV1" t="s">
         <v>179</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AW1" t="s">
         <v>180</v>
       </c>
-      <c r="AR1" s="13" t="s">
-        <v>535</v>
-      </c>
-      <c r="AS1" s="13" t="s">
-        <v>536</v>
-      </c>
-      <c r="AT1" t="s">
+      <c r="AX1" t="s">
         <v>181</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AY1" t="s">
         <v>182</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AZ1" t="s">
         <v>183</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="BA1" t="s">
         <v>184</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="BB1" t="s">
         <v>185</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="BC1" t="s">
         <v>186</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="BD1" t="s">
         <v>187</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BE1" t="s">
         <v>188</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="BF1" t="s">
         <v>189</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BG1" t="s">
         <v>190</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BH1" t="s">
         <v>191</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BJ1" t="s">
+        <v>191</v>
+      </c>
+      <c r="BK1" t="s">
         <v>192</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BL1" t="s">
         <v>193</v>
       </c>
-      <c r="BG1" t="s">
+      <c r="BM1" t="s">
         <v>194</v>
       </c>
-      <c r="BH1" t="s">
+      <c r="BN1" t="s">
         <v>195</v>
       </c>
-      <c r="BJ1" t="s">
-        <v>195</v>
-      </c>
-      <c r="BK1" t="s">
+      <c r="BO1" t="s">
         <v>196</v>
       </c>
-      <c r="BL1" t="s">
+      <c r="BP1" t="s">
         <v>197</v>
       </c>
-      <c r="BM1" t="s">
+      <c r="BQ1" t="s">
         <v>198</v>
       </c>
-      <c r="BN1" t="s">
+      <c r="BR1" t="s">
         <v>199</v>
       </c>
-      <c r="BO1" t="s">
+      <c r="BS1" t="s">
         <v>200</v>
       </c>
-      <c r="BP1" t="s">
+      <c r="BT1" t="s">
         <v>201</v>
       </c>
-      <c r="BQ1" t="s">
+      <c r="BU1" t="s">
         <v>202</v>
       </c>
-      <c r="BR1" t="s">
+      <c r="BV1" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="BS1" t="s">
+      <c r="BW1" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="BT1" t="s">
+      <c r="BX1" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="BU1" t="s">
+      <c r="BY1" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="BV1" s="5" t="s">
+      <c r="BZ1" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="BW1" s="5" t="s">
+      <c r="CA1" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="BX1" s="5" t="s">
+      <c r="CB1" t="s">
         <v>209</v>
       </c>
-      <c r="BY1" s="5" t="s">
+      <c r="CC1" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="BZ1" s="5" t="s">
+      <c r="CD1" t="s">
         <v>211</v>
       </c>
-      <c r="CA1" s="5" t="s">
+      <c r="CE1" t="s">
         <v>212</v>
       </c>
-      <c r="CB1" t="s">
+      <c r="CF1" t="s">
         <v>213</v>
       </c>
-      <c r="CC1" s="5" t="s">
+      <c r="CG1" t="s">
         <v>214</v>
       </c>
-      <c r="CD1" t="s">
+      <c r="CH1" t="s">
         <v>215</v>
       </c>
-      <c r="CE1" t="s">
+      <c r="CI1" t="s">
         <v>216</v>
       </c>
-      <c r="CF1" t="s">
+      <c r="CJ1" t="s">
         <v>217</v>
       </c>
-      <c r="CG1" t="s">
+      <c r="CK1" t="s">
         <v>218</v>
       </c>
-      <c r="CH1" t="s">
+      <c r="CL1" t="s">
         <v>219</v>
       </c>
-      <c r="CI1" t="s">
+      <c r="CM1" t="s">
         <v>220</v>
       </c>
-      <c r="CJ1" t="s">
+      <c r="CN1" t="s">
         <v>221</v>
       </c>
-      <c r="CK1" t="s">
+      <c r="CO1" t="s">
         <v>222</v>
       </c>
-      <c r="CL1" t="s">
+      <c r="CP1" t="s">
         <v>223</v>
       </c>
-      <c r="CM1" t="s">
+      <c r="CQ1" t="s">
         <v>224</v>
       </c>
-      <c r="CN1" t="s">
+      <c r="CR1" t="s">
+        <v>201</v>
+      </c>
+      <c r="CS1" t="s">
         <v>225</v>
       </c>
-      <c r="CO1" t="s">
+      <c r="CT1" t="s">
         <v>226</v>
       </c>
-      <c r="CP1" t="s">
+      <c r="CU1" t="s">
         <v>227</v>
       </c>
-      <c r="CQ1" t="s">
+      <c r="CV1" t="s">
         <v>228</v>
       </c>
-      <c r="CR1" t="s">
-        <v>205</v>
-      </c>
-      <c r="CS1" t="s">
+      <c r="CW1" t="s">
         <v>229</v>
       </c>
-      <c r="CT1" t="s">
+      <c r="CX1" t="s">
         <v>230</v>
       </c>
-      <c r="CU1" t="s">
+      <c r="CY1" t="s">
         <v>231</v>
       </c>
-      <c r="CV1" t="s">
+      <c r="CZ1" t="s">
+        <v>230</v>
+      </c>
+      <c r="DA1" t="s">
         <v>232</v>
       </c>
-      <c r="CW1" t="s">
+      <c r="DB1" t="s">
         <v>233</v>
       </c>
-      <c r="CX1" t="s">
+      <c r="DC1" t="s">
         <v>234</v>
       </c>
-      <c r="CY1" t="s">
+      <c r="DD1" t="s">
         <v>235</v>
       </c>
-      <c r="CZ1" t="s">
-        <v>234</v>
-      </c>
-      <c r="DA1" t="s">
+      <c r="DE1" t="s">
         <v>236</v>
       </c>
-      <c r="DB1" t="s">
+      <c r="DF1" t="s">
         <v>237</v>
       </c>
-      <c r="DC1" t="s">
+      <c r="DG1" t="s">
         <v>238</v>
       </c>
-      <c r="DD1" t="s">
+      <c r="DH1" t="s">
         <v>239</v>
       </c>
-      <c r="DE1" t="s">
+      <c r="DI1" t="s">
         <v>240</v>
-      </c>
-      <c r="DF1" t="s">
-        <v>241</v>
-      </c>
-      <c r="DG1" t="s">
-        <v>242</v>
-      </c>
-      <c r="DH1" t="s">
-        <v>243</v>
-      </c>
-      <c r="DI1" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="2" spans="1:113" x14ac:dyDescent="0.25">
@@ -6345,337 +6346,337 @@
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E2" t="s">
+        <v>241</v>
+      </c>
+      <c r="F2" t="s">
+        <v>242</v>
+      </c>
+      <c r="G2" t="s">
+        <v>51</v>
+      </c>
+      <c r="H2" t="s">
+        <v>243</v>
+      </c>
+      <c r="I2" t="s">
+        <v>244</v>
+      </c>
+      <c r="J2" t="s">
+        <v>245</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="R2" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="S2" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="T2" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="U2" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="V2" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="W2" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="X2" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>260</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>261</v>
+      </c>
+      <c r="AA2" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>263</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>264</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>265</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>266</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>267</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>268</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>269</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>270</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>271</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>272</v>
+      </c>
+      <c r="AL2" t="s">
+        <v>273</v>
+      </c>
+      <c r="AM2" t="s">
+        <v>274</v>
+      </c>
+      <c r="AN2" t="s">
+        <v>275</v>
+      </c>
+      <c r="AO2" t="s">
+        <v>276</v>
+      </c>
+      <c r="AP2" t="s">
+        <v>277</v>
+      </c>
+      <c r="AQ2" t="s">
+        <v>278</v>
+      </c>
+      <c r="AR2" s="13" t="s">
+        <v>533</v>
+      </c>
+      <c r="AS2" s="13" t="s">
+        <v>534</v>
+      </c>
+      <c r="AT2" t="s">
+        <v>279</v>
+      </c>
+      <c r="AU2" t="s">
+        <v>280</v>
+      </c>
+      <c r="AV2" t="s">
+        <v>281</v>
+      </c>
+      <c r="AW2" t="s">
+        <v>282</v>
+      </c>
+      <c r="AX2" t="s">
+        <v>283</v>
+      </c>
+      <c r="AY2" t="s">
+        <v>284</v>
+      </c>
+      <c r="AZ2" t="s">
+        <v>285</v>
+      </c>
+      <c r="BA2" t="s">
+        <v>286</v>
+      </c>
+      <c r="BB2" t="s">
+        <v>287</v>
+      </c>
+      <c r="BC2" t="s">
+        <v>288</v>
+      </c>
+      <c r="BD2" t="s">
+        <v>289</v>
+      </c>
+      <c r="BE2" t="s">
+        <v>290</v>
+      </c>
+      <c r="BF2" t="s">
+        <v>291</v>
+      </c>
+      <c r="BG2" t="s">
+        <v>292</v>
+      </c>
+      <c r="BH2" t="s">
+        <v>293</v>
+      </c>
+      <c r="BI2" t="s">
+        <v>294</v>
+      </c>
+      <c r="BJ2" t="s">
+        <v>295</v>
+      </c>
+      <c r="BK2" t="s">
+        <v>296</v>
+      </c>
+      <c r="BL2" t="s">
+        <v>297</v>
+      </c>
+      <c r="BM2" t="s">
+        <v>298</v>
+      </c>
+      <c r="BN2" t="s">
+        <v>299</v>
+      </c>
+      <c r="BO2" t="s">
         <v>77</v>
       </c>
-      <c r="E2" t="s">
-        <v>245</v>
-      </c>
-      <c r="F2" t="s">
-        <v>246</v>
-      </c>
-      <c r="G2" t="s">
-        <v>53</v>
-      </c>
-      <c r="H2" t="s">
-        <v>247</v>
-      </c>
-      <c r="I2" t="s">
-        <v>248</v>
-      </c>
-      <c r="J2" t="s">
-        <v>249</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>254</v>
-      </c>
-      <c r="P2" s="4" t="s">
-        <v>255</v>
-      </c>
-      <c r="Q2" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="R2" s="4" t="s">
-        <v>257</v>
-      </c>
-      <c r="S2" s="4" t="s">
-        <v>258</v>
-      </c>
-      <c r="T2" s="4" t="s">
-        <v>259</v>
-      </c>
-      <c r="U2" s="4" t="s">
-        <v>260</v>
-      </c>
-      <c r="V2" s="4" t="s">
-        <v>261</v>
-      </c>
-      <c r="W2" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="X2" s="4" t="s">
-        <v>263</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>264</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>265</v>
-      </c>
-      <c r="AA2" s="4" t="s">
-        <v>266</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>267</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>268</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>269</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>270</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>271</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>272</v>
-      </c>
-      <c r="AH2" t="s">
-        <v>273</v>
-      </c>
-      <c r="AI2" t="s">
-        <v>274</v>
-      </c>
-      <c r="AJ2" t="s">
-        <v>275</v>
-      </c>
-      <c r="AK2" t="s">
-        <v>276</v>
-      </c>
-      <c r="AL2" t="s">
-        <v>277</v>
-      </c>
-      <c r="AM2" t="s">
-        <v>278</v>
-      </c>
-      <c r="AN2" t="s">
-        <v>279</v>
-      </c>
-      <c r="AO2" t="s">
-        <v>280</v>
-      </c>
-      <c r="AP2" t="s">
-        <v>281</v>
-      </c>
-      <c r="AQ2" t="s">
-        <v>282</v>
-      </c>
-      <c r="AR2" s="13" t="s">
-        <v>537</v>
-      </c>
-      <c r="AS2" s="13" t="s">
-        <v>538</v>
-      </c>
-      <c r="AT2" t="s">
-        <v>283</v>
-      </c>
-      <c r="AU2" t="s">
-        <v>284</v>
-      </c>
-      <c r="AV2" t="s">
-        <v>285</v>
-      </c>
-      <c r="AW2" t="s">
-        <v>286</v>
-      </c>
-      <c r="AX2" t="s">
-        <v>287</v>
-      </c>
-      <c r="AY2" t="s">
-        <v>288</v>
-      </c>
-      <c r="AZ2" t="s">
-        <v>289</v>
-      </c>
-      <c r="BA2" t="s">
-        <v>290</v>
-      </c>
-      <c r="BB2" t="s">
-        <v>291</v>
-      </c>
-      <c r="BC2" t="s">
-        <v>292</v>
-      </c>
-      <c r="BD2" t="s">
-        <v>293</v>
-      </c>
-      <c r="BE2" t="s">
-        <v>294</v>
-      </c>
-      <c r="BF2" t="s">
-        <v>295</v>
-      </c>
-      <c r="BG2" t="s">
-        <v>296</v>
-      </c>
-      <c r="BH2" t="s">
-        <v>297</v>
-      </c>
-      <c r="BI2" t="s">
-        <v>298</v>
-      </c>
-      <c r="BJ2" t="s">
-        <v>299</v>
-      </c>
-      <c r="BK2" t="s">
+      <c r="BP2" t="s">
         <v>300</v>
       </c>
-      <c r="BL2" t="s">
+      <c r="BQ2" t="s">
         <v>301</v>
       </c>
-      <c r="BM2" t="s">
+      <c r="BR2" t="s">
         <v>302</v>
       </c>
-      <c r="BN2" t="s">
+      <c r="BS2" t="s">
         <v>303</v>
       </c>
-      <c r="BO2" t="s">
-        <v>79</v>
-      </c>
-      <c r="BP2" t="s">
+      <c r="BT2" t="s">
         <v>304</v>
       </c>
-      <c r="BQ2" t="s">
+      <c r="BU2" t="s">
+        <v>91</v>
+      </c>
+      <c r="BV2" s="5" t="s">
         <v>305</v>
       </c>
-      <c r="BR2" t="s">
+      <c r="BW2" s="5" t="s">
         <v>306</v>
       </c>
-      <c r="BS2" t="s">
+      <c r="BX2" s="5" t="s">
         <v>307</v>
       </c>
-      <c r="BT2" t="s">
+      <c r="BY2" s="5" t="s">
         <v>308</v>
       </c>
-      <c r="BU2" t="s">
-        <v>95</v>
-      </c>
-      <c r="BV2" s="5" t="s">
+      <c r="BZ2" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="BW2" s="5" t="s">
+      <c r="CA2" s="5" t="s">
         <v>310</v>
       </c>
-      <c r="BX2" s="5" t="s">
+      <c r="CB2" t="s">
         <v>311</v>
       </c>
-      <c r="BY2" s="5" t="s">
+      <c r="CC2" t="s">
         <v>312</v>
       </c>
-      <c r="BZ2" s="5" t="s">
+      <c r="CD2" t="s">
         <v>313</v>
       </c>
-      <c r="CA2" s="5" t="s">
+      <c r="CE2" t="s">
         <v>314</v>
       </c>
-      <c r="CB2" t="s">
+      <c r="CF2" t="s">
         <v>315</v>
       </c>
-      <c r="CC2" t="s">
+      <c r="CG2" t="s">
         <v>316</v>
       </c>
-      <c r="CD2" t="s">
+      <c r="CH2" t="s">
         <v>317</v>
       </c>
-      <c r="CE2" t="s">
+      <c r="CI2" t="s">
         <v>318</v>
       </c>
-      <c r="CF2" t="s">
+      <c r="CJ2" t="s">
         <v>319</v>
       </c>
-      <c r="CG2" t="s">
+      <c r="CK2" t="s">
         <v>320</v>
       </c>
-      <c r="CH2" t="s">
+      <c r="CL2" t="s">
         <v>321</v>
       </c>
-      <c r="CI2" t="s">
+      <c r="CM2" t="s">
         <v>322</v>
       </c>
-      <c r="CJ2" t="s">
+      <c r="CN2" t="s">
         <v>323</v>
       </c>
-      <c r="CK2" t="s">
+      <c r="CO2" t="s">
         <v>324</v>
       </c>
-      <c r="CL2" t="s">
+      <c r="CP2" t="s">
         <v>325</v>
       </c>
-      <c r="CM2" t="s">
+      <c r="CQ2" t="s">
         <v>326</v>
       </c>
-      <c r="CN2" t="s">
+      <c r="CR2" t="s">
         <v>327</v>
       </c>
-      <c r="CO2" t="s">
+      <c r="CS2" t="s">
         <v>328</v>
       </c>
-      <c r="CP2" t="s">
+      <c r="CT2" t="s">
         <v>329</v>
       </c>
-      <c r="CQ2" t="s">
+      <c r="CU2" t="s">
         <v>330</v>
       </c>
-      <c r="CR2" t="s">
+      <c r="CV2" t="s">
         <v>331</v>
       </c>
-      <c r="CS2" t="s">
+      <c r="CW2" t="s">
         <v>332</v>
       </c>
-      <c r="CT2" t="s">
+      <c r="CX2" t="s">
         <v>333</v>
       </c>
-      <c r="CU2" t="s">
+      <c r="CY2" t="s">
         <v>334</v>
       </c>
-      <c r="CV2" t="s">
+      <c r="CZ2" t="s">
         <v>335</v>
       </c>
-      <c r="CW2" t="s">
+      <c r="DA2" t="s">
         <v>336</v>
       </c>
-      <c r="CX2" t="s">
+      <c r="DB2" t="s">
         <v>337</v>
       </c>
-      <c r="CY2" t="s">
+      <c r="DC2" t="s">
         <v>338</v>
       </c>
-      <c r="CZ2" t="s">
+      <c r="DD2" t="s">
         <v>339</v>
       </c>
-      <c r="DA2" t="s">
+      <c r="DE2" t="s">
         <v>340</v>
       </c>
-      <c r="DB2" t="s">
+      <c r="DF2" t="s">
         <v>341</v>
       </c>
-      <c r="DC2" t="s">
+      <c r="DG2" t="s">
         <v>342</v>
       </c>
-      <c r="DD2" t="s">
+      <c r="DH2" t="s">
         <v>343</v>
       </c>
-      <c r="DE2" t="s">
+      <c r="DI2" t="s">
         <v>344</v>
-      </c>
-      <c r="DF2" t="s">
-        <v>345</v>
-      </c>
-      <c r="DG2" t="s">
-        <v>346</v>
-      </c>
-      <c r="DH2" t="s">
-        <v>347</v>
-      </c>
-      <c r="DI2" t="s">
-        <v>348</v>
       </c>
     </row>
     <row r="3" spans="1:113" x14ac:dyDescent="0.25">
@@ -6695,338 +6696,338 @@
         <v>2</v>
       </c>
       <c r="G3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H3" t="s">
         <v>2</v>
       </c>
       <c r="I3" t="s">
+        <v>112</v>
+      </c>
+      <c r="J3" t="s">
+        <v>345</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="N3" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="O3" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="J3" t="s">
-        <v>349</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>350</v>
-      </c>
-      <c r="L3" s="4" t="s">
-        <v>351</v>
-      </c>
-      <c r="M3" s="4" t="s">
+      <c r="P3" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q3" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="R3" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="S3" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="T3" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="U3" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="V3" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="W3" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="X3" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>112</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AA3" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>114</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>348</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AI3" t="s">
         <v>118</v>
-      </c>
-      <c r="N3" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="O3" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="P3" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="Q3" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="R3" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="S3" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="T3" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="U3" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="V3" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="W3" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="X3" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>116</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AA3" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>118</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>352</v>
-      </c>
-      <c r="AH3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AI3" t="s">
-        <v>122</v>
       </c>
       <c r="AJ3" t="s">
         <v>3</v>
       </c>
       <c r="AK3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="AL3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="AM3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="AN3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="AO3" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="AP3" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="AQ3" t="s">
         <v>2</v>
       </c>
       <c r="AR3" s="13" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="AS3" s="13" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="AT3" t="s">
+        <v>351</v>
+      </c>
+      <c r="AU3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AV3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AW3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AX3" t="s">
+        <v>352</v>
+      </c>
+      <c r="AY3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AZ3" t="s">
+        <v>113</v>
+      </c>
+      <c r="BA3" t="s">
+        <v>112</v>
+      </c>
+      <c r="BB3" t="s">
+        <v>114</v>
+      </c>
+      <c r="BC3" t="s">
+        <v>113</v>
+      </c>
+      <c r="BD3" t="s">
+        <v>114</v>
+      </c>
+      <c r="BE3" t="s">
+        <v>114</v>
+      </c>
+      <c r="BF3" t="s">
+        <v>113</v>
+      </c>
+      <c r="BG3" t="s">
+        <v>112</v>
+      </c>
+      <c r="BH3" t="s">
+        <v>351</v>
+      </c>
+      <c r="BI3" t="s">
+        <v>112</v>
+      </c>
+      <c r="BJ3" t="s">
+        <v>113</v>
+      </c>
+      <c r="BK3" t="s">
+        <v>113</v>
+      </c>
+      <c r="BL3" t="s">
+        <v>113</v>
+      </c>
+      <c r="BM3" t="s">
+        <v>114</v>
+      </c>
+      <c r="BN3" t="s">
+        <v>114</v>
+      </c>
+      <c r="BO3" t="s">
+        <v>115</v>
+      </c>
+      <c r="BP3" t="s">
+        <v>115</v>
+      </c>
+      <c r="BQ3" t="s">
+        <v>353</v>
+      </c>
+      <c r="BR3" t="s">
+        <v>354</v>
+      </c>
+      <c r="BS3" t="s">
+        <v>113</v>
+      </c>
+      <c r="BT3" t="s">
+        <v>113</v>
+      </c>
+      <c r="BU3" t="s">
+        <v>112</v>
+      </c>
+      <c r="BV3" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="BW3" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="BX3" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="BY3" s="5" t="s">
         <v>355</v>
       </c>
-      <c r="AU3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AV3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AW3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AX3" t="s">
+      <c r="BZ3" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="CA3" s="5" t="s">
+        <v>355</v>
+      </c>
+      <c r="CB3" t="s">
+        <v>120</v>
+      </c>
+      <c r="CC3" t="s">
         <v>356</v>
       </c>
-      <c r="AY3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AZ3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BA3" t="s">
-        <v>116</v>
-      </c>
-      <c r="BB3" t="s">
-        <v>118</v>
-      </c>
-      <c r="BC3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BD3" t="s">
-        <v>118</v>
-      </c>
-      <c r="BE3" t="s">
-        <v>118</v>
-      </c>
-      <c r="BF3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BG3" t="s">
-        <v>116</v>
-      </c>
-      <c r="BH3" t="s">
-        <v>355</v>
-      </c>
-      <c r="BI3" t="s">
-        <v>116</v>
-      </c>
-      <c r="BJ3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BK3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BL3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BM3" t="s">
-        <v>118</v>
-      </c>
-      <c r="BN3" t="s">
-        <v>118</v>
-      </c>
-      <c r="BO3" t="s">
-        <v>119</v>
-      </c>
-      <c r="BP3" t="s">
-        <v>119</v>
-      </c>
-      <c r="BQ3" t="s">
+      <c r="CD3" t="s">
+        <v>120</v>
+      </c>
+      <c r="CE3" t="s">
+        <v>120</v>
+      </c>
+      <c r="CF3" t="s">
+        <v>120</v>
+      </c>
+      <c r="CG3" t="s">
         <v>357</v>
       </c>
-      <c r="BR3" t="s">
+      <c r="CH3" t="s">
         <v>358</v>
-      </c>
-      <c r="BS3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BT3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BU3" t="s">
-        <v>116</v>
-      </c>
-      <c r="BV3" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="BW3" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="BX3" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="BY3" s="5" t="s">
-        <v>359</v>
-      </c>
-      <c r="BZ3" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="CA3" s="5" t="s">
-        <v>359</v>
-      </c>
-      <c r="CB3" t="s">
-        <v>124</v>
-      </c>
-      <c r="CC3" t="s">
-        <v>360</v>
-      </c>
-      <c r="CD3" t="s">
-        <v>124</v>
-      </c>
-      <c r="CE3" t="s">
-        <v>124</v>
-      </c>
-      <c r="CF3" t="s">
-        <v>124</v>
-      </c>
-      <c r="CG3" t="s">
-        <v>361</v>
-      </c>
-      <c r="CH3" t="s">
-        <v>362</v>
       </c>
       <c r="CI3" t="s">
         <v>2</v>
       </c>
       <c r="CJ3" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="CK3" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="CL3" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="CM3" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="CN3" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="CO3" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="CP3" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="CQ3" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="CR3" t="s">
+        <v>356</v>
+      </c>
+      <c r="CS3" t="s">
+        <v>119</v>
+      </c>
+      <c r="CT3" t="s">
+        <v>112</v>
+      </c>
+      <c r="CU3" t="s">
+        <v>121</v>
+      </c>
+      <c r="CV3" t="s">
         <v>360</v>
       </c>
-      <c r="CS3" t="s">
-        <v>123</v>
-      </c>
-      <c r="CT3" t="s">
-        <v>116</v>
-      </c>
-      <c r="CU3" t="s">
-        <v>125</v>
-      </c>
-      <c r="CV3" t="s">
-        <v>364</v>
-      </c>
       <c r="CW3" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="CX3" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="CY3" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="CZ3" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="DA3" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="DB3" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="DC3" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="DD3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="DE3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="DF3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="DG3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="DH3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="DI3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="4" spans="1:113" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
     </row>
     <row r="5" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="C5" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="M5"/>
       <c r="N5"/>
@@ -7040,36 +7041,36 @@
         <v>2</v>
       </c>
       <c r="AO5" t="s">
+        <v>364</v>
+      </c>
+      <c r="AT5" t="s">
+        <v>365</v>
+      </c>
+      <c r="AX5" t="s">
+        <v>366</v>
+      </c>
+      <c r="AZ5">
+        <v>1</v>
+      </c>
+      <c r="BD5">
+        <v>1</v>
+      </c>
+      <c r="CB5" t="s">
+        <v>55</v>
+      </c>
+      <c r="CG5" t="s">
+        <v>367</v>
+      </c>
+      <c r="CY5" t="s">
         <v>368</v>
-      </c>
-      <c r="AT5" t="s">
-        <v>369</v>
-      </c>
-      <c r="AX5" t="s">
-        <v>370</v>
-      </c>
-      <c r="AZ5">
-        <v>1</v>
-      </c>
-      <c r="BD5">
-        <v>1</v>
-      </c>
-      <c r="CB5" t="s">
-        <v>57</v>
-      </c>
-      <c r="CG5" t="s">
-        <v>371</v>
-      </c>
-      <c r="CY5" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="6" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="C6" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="I6">
         <v>1</v>
@@ -7085,19 +7086,19 @@
         <v>1</v>
       </c>
       <c r="AG6" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="BD6">
         <v>1</v>
       </c>
       <c r="BO6" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="BS6">
         <v>0.1</v>
       </c>
       <c r="CN6" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="CR6">
         <v>0.2</v>
@@ -7105,19 +7106,19 @@
     </row>
     <row r="7" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="C7" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="I7">
         <v>1</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="M7"/>
       <c r="N7"/>
@@ -7130,13 +7131,13 @@
         <v>1</v>
       </c>
       <c r="AG7" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="BD7">
         <v>1</v>
       </c>
       <c r="CN7" s="2" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="CR7">
         <v>4</v>
@@ -7144,21 +7145,21 @@
     </row>
     <row r="8" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="C8" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="I8">
         <v>1</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="M8"/>
       <c r="N8"/>
       <c r="P8" s="2" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="U8" s="4">
         <v>0.66666700000000001</v>
@@ -7169,10 +7170,10 @@
         <v>1</v>
       </c>
       <c r="AG8" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="AX8" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="AY8" s="4">
         <v>1</v>
@@ -7193,7 +7194,7 @@
         <v>0.1</v>
       </c>
       <c r="CN8" s="2" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="CR8">
         <v>0.2</v>
@@ -7201,10 +7202,10 @@
     </row>
     <row r="9" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="C9" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="I9">
         <v>1</v>
@@ -7220,22 +7221,22 @@
         <v>1</v>
       </c>
       <c r="AG9" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="BD9">
         <v>1</v>
       </c>
       <c r="BO9" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="BS9">
         <v>0.1</v>
       </c>
       <c r="CN9" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="CO9" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="CR9">
         <v>0.2</v>
@@ -7243,10 +7244,10 @@
     </row>
     <row r="10" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="C10" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="I10">
         <v>1</v>
@@ -7262,7 +7263,7 @@
         <v>1</v>
       </c>
       <c r="AG10" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="BD10">
         <v>1</v>
@@ -7271,10 +7272,10 @@
         <v>0.1</v>
       </c>
       <c r="CN10" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="CO10" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="CR10">
         <v>0.2</v>
@@ -7282,10 +7283,10 @@
     </row>
     <row r="11" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="C11" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="I11">
         <v>1</v>
@@ -7301,7 +7302,7 @@
         <v>1</v>
       </c>
       <c r="AG11" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="BD11">
         <v>1</v>
@@ -7310,10 +7311,10 @@
         <v>0.1</v>
       </c>
       <c r="CN11" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="CO11" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="CR11">
         <v>0.2</v>
@@ -7321,10 +7322,10 @@
     </row>
     <row r="12" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="C12" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="I12">
         <v>1</v>
@@ -7340,7 +7341,7 @@
         <v>1</v>
       </c>
       <c r="AG12" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="BD12">
         <v>1</v>
@@ -7349,10 +7350,10 @@
         <v>0.1</v>
       </c>
       <c r="CN12" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="CO12" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="CR12">
         <v>0.2</v>
@@ -7360,10 +7361,10 @@
     </row>
     <row r="13" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="C13" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="I13">
         <v>1</v>
@@ -7379,7 +7380,7 @@
         <v>1</v>
       </c>
       <c r="AG13" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="BD13">
         <v>1</v>
@@ -7388,10 +7389,10 @@
         <v>0.1</v>
       </c>
       <c r="CN13" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="CO13" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="CR13">
         <v>0.2</v>
@@ -7405,19 +7406,19 @@
     </row>
     <row r="15" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="C15" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="D15" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="E15" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="F15" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="G15">
         <v>3</v>
@@ -7426,10 +7427,10 @@
         <v>1</v>
       </c>
       <c r="J15" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="K15" s="4" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="M15"/>
       <c r="N15"/>
@@ -7439,13 +7440,13 @@
         <v>1</v>
       </c>
       <c r="AG15" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="BD15">
         <v>1</v>
       </c>
       <c r="BO15" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="BT15">
         <v>9999</v>
@@ -7460,7 +7461,7 @@
         <v>1</v>
       </c>
       <c r="BY15" s="5" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="CB15" s="4"/>
       <c r="CC15" s="4"/>
@@ -7473,10 +7474,10 @@
       <c r="CK15" s="4"/>
       <c r="CM15" s="4"/>
       <c r="CN15" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="CO15" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="CR15">
         <v>9999</v>
@@ -7484,10 +7485,10 @@
     </row>
     <row r="16" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="C16" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="I16">
         <v>1</v>
@@ -7495,7 +7496,7 @@
       <c r="M16"/>
       <c r="N16"/>
       <c r="O16" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="Y16" s="4"/>
       <c r="Z16" s="4"/>
@@ -7503,13 +7504,13 @@
         <v>2</v>
       </c>
       <c r="AO16" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="AT16" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="AX16" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="AZ16">
         <v>1</v>
@@ -7518,35 +7519,35 @@
         <v>1</v>
       </c>
       <c r="CB16" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="CG16" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="CY16" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
     </row>
     <row r="17" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C17" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="I17">
         <v>1</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="M17"/>
       <c r="N17"/>
       <c r="O17" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="Y17" s="4"/>
       <c r="Z17" s="4"/>
@@ -7560,7 +7561,7 @@
         <v>1</v>
       </c>
       <c r="AX17" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="AZ17">
         <v>1.75</v>
@@ -7569,7 +7570,7 @@
         <v>1</v>
       </c>
       <c r="CY17" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="DD17">
         <v>1</v>
@@ -7596,19 +7597,19 @@
     </row>
     <row r="19" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="C19" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="D19" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="E19" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="F19" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G19">
         <v>3</v>
@@ -7617,10 +7618,10 @@
         <v>1</v>
       </c>
       <c r="J19" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="K19" s="4" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="M19"/>
       <c r="N19"/>
@@ -7630,19 +7631,19 @@
         <v>1</v>
       </c>
       <c r="AG19" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="AT19" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="BD19">
         <v>1</v>
       </c>
       <c r="BO19" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="BP19" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="BT19">
         <v>32</v>
@@ -7660,7 +7661,7 @@
         <v>1</v>
       </c>
       <c r="BY19" s="5" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="CB19" s="4"/>
       <c r="CC19" s="4"/>
@@ -7673,24 +7674,24 @@
       <c r="CK19" s="4"/>
       <c r="CM19" s="4"/>
       <c r="CN19" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="CO19" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="CR19">
         <v>32</v>
       </c>
       <c r="CU19" s="12" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
     </row>
     <row r="20" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="C20" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="I20">
         <v>1</v>
@@ -7698,7 +7699,7 @@
       <c r="M20"/>
       <c r="N20"/>
       <c r="O20" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="Y20" s="4"/>
       <c r="Z20" s="4"/>
@@ -7709,13 +7710,13 @@
         <v>1</v>
       </c>
       <c r="AO20" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="AT20" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="AX20" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="AZ20">
         <v>1</v>
@@ -7730,30 +7731,30 @@
         <v>0.1</v>
       </c>
       <c r="CB20" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="CG20" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="CY20" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
     </row>
     <row r="21" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="C21" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="I21">
         <v>1</v>
       </c>
       <c r="K21" s="4" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="M21"/>
       <c r="N21"/>
@@ -7764,7 +7765,7 @@
         <v>1</v>
       </c>
       <c r="AG21" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="BD21">
         <v>1</v>
@@ -7773,7 +7774,7 @@
         <v>0.4</v>
       </c>
       <c r="CM21" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="DD21">
         <v>1</v>
@@ -7787,10 +7788,10 @@
     </row>
     <row r="22" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="C22" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="I22">
         <v>1</v>
@@ -7798,10 +7799,10 @@
       <c r="M22"/>
       <c r="N22"/>
       <c r="O22" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="P22" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="Y22" s="4"/>
       <c r="Z22" s="4"/>
@@ -7809,16 +7810,16 @@
         <v>1</v>
       </c>
       <c r="AG22" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="AT22" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="BD22">
         <v>1</v>
       </c>
       <c r="BO22" s="12" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="CB22" s="4"/>
       <c r="CC22" s="4"/>
@@ -7831,10 +7832,10 @@
       <c r="CK22" s="4"/>
       <c r="CM22" s="4"/>
       <c r="CN22" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="CO22" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="CP22">
         <v>-1</v>
@@ -7843,15 +7844,15 @@
         <v>11</v>
       </c>
       <c r="CU22" s="12" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
     </row>
     <row r="23" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="C23" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="I23">
         <v>1</v>
@@ -7859,7 +7860,7 @@
       <c r="M23"/>
       <c r="N23"/>
       <c r="O23" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="Y23" s="4"/>
       <c r="Z23" s="4"/>
@@ -7870,13 +7871,13 @@
         <v>1</v>
       </c>
       <c r="AO23" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="AT23" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="AX23" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="AZ23">
         <v>1</v>
@@ -7891,24 +7892,24 @@
         <v>0.1</v>
       </c>
       <c r="CB23" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="CG23" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="CY23" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="CZ23" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
     </row>
     <row r="24" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="C24" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="I24">
         <v>1</v>
@@ -7916,7 +7917,7 @@
       <c r="M24"/>
       <c r="N24"/>
       <c r="O24" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="R24" s="2"/>
       <c r="Y24" s="4"/>
@@ -7925,7 +7926,7 @@
         <v>1</v>
       </c>
       <c r="AT24" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="AW24">
         <v>1</v>
@@ -7937,7 +7938,7 @@
         <v>0.1</v>
       </c>
       <c r="CN24" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="CR24">
         <v>0.2</v>
@@ -7954,10 +7955,10 @@
     </row>
     <row r="25" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="C25" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="I25">
         <v>1</v>
@@ -7965,7 +7966,7 @@
       <c r="M25"/>
       <c r="N25"/>
       <c r="O25" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="R25"/>
       <c r="Y25" s="4"/>
@@ -7974,10 +7975,10 @@
         <v>1</v>
       </c>
       <c r="AG25" s="12" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="AT25" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="AW25">
         <v>1</v>
@@ -7989,7 +7990,7 @@
         <v>0.1</v>
       </c>
       <c r="CN25" s="12" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="CR25">
         <v>0.2</v>
@@ -8006,10 +8007,10 @@
     </row>
     <row r="26" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A26" s="12" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="C26" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="I26">
         <v>1</v>
@@ -8017,7 +8018,7 @@
       <c r="M26"/>
       <c r="N26"/>
       <c r="O26" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="R26"/>
       <c r="Y26" s="4"/>
@@ -8026,7 +8027,7 @@
         <v>1</v>
       </c>
       <c r="AG26" s="12" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="AW26">
         <v>1</v>
@@ -8038,7 +8039,7 @@
         <v>0.1</v>
       </c>
       <c r="CN26" s="12" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="CR26">
         <v>0.2</v>
@@ -8055,10 +8056,10 @@
     </row>
     <row r="27" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="C27" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="I27">
         <v>1</v>
@@ -8066,7 +8067,7 @@
       <c r="M27"/>
       <c r="N27"/>
       <c r="O27" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="Y27" s="4"/>
       <c r="Z27" s="4"/>
@@ -8074,27 +8075,27 @@
         <v>1</v>
       </c>
       <c r="AG27" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="BD27">
         <v>1</v>
       </c>
       <c r="CU27" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="28" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="C28" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="I28">
         <v>1</v>
       </c>
       <c r="K28" s="4" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="M28"/>
       <c r="N28"/>
@@ -8103,7 +8104,7 @@
         <v>1</v>
       </c>
       <c r="AG28" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="BD28">
         <v>1</v>
@@ -8112,10 +8113,10 @@
         <v>0.33300000000000002</v>
       </c>
       <c r="CB28" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="CG28" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="DD28">
         <v>1</v>
@@ -8129,19 +8130,19 @@
     </row>
     <row r="29" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="C29" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="I29">
         <v>1</v>
       </c>
       <c r="K29" s="4" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="L29" s="4" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="M29"/>
       <c r="N29"/>
@@ -8150,7 +8151,7 @@
         <v>1</v>
       </c>
       <c r="AG29" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="BD29">
         <v>1</v>
@@ -8159,10 +8160,10 @@
         <v>0.33300000000000002</v>
       </c>
       <c r="CB29" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="CG29" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="DD29">
         <v>1</v>
@@ -9427,34 +9428,34 @@
         <v>5</v>
       </c>
       <c r="E1" t="s">
+        <v>432</v>
+      </c>
+      <c r="F1" t="s">
+        <v>433</v>
+      </c>
+      <c r="G1" t="s">
+        <v>434</v>
+      </c>
+      <c r="H1" t="s">
+        <v>435</v>
+      </c>
+      <c r="I1" t="s">
         <v>436</v>
       </c>
-      <c r="F1" t="s">
+      <c r="J1" t="s">
         <v>437</v>
       </c>
-      <c r="G1" t="s">
+      <c r="L1" t="s">
         <v>438</v>
       </c>
-      <c r="H1" t="s">
+      <c r="M1" t="s">
         <v>439</v>
       </c>
-      <c r="I1" t="s">
+      <c r="N1" t="s">
         <v>440</v>
       </c>
-      <c r="J1" t="s">
+      <c r="O1" t="s">
         <v>441</v>
-      </c>
-      <c r="L1" t="s">
-        <v>442</v>
-      </c>
-      <c r="M1" t="s">
-        <v>443</v>
-      </c>
-      <c r="N1" t="s">
-        <v>444</v>
-      </c>
-      <c r="O1" t="s">
-        <v>445</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
@@ -9462,46 +9463,46 @@
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E2" t="s">
+        <v>442</v>
+      </c>
+      <c r="F2" t="s">
+        <v>443</v>
+      </c>
+      <c r="G2" t="s">
+        <v>444</v>
+      </c>
+      <c r="H2" t="s">
+        <v>445</v>
+      </c>
+      <c r="I2" t="s">
         <v>446</v>
       </c>
-      <c r="F2" t="s">
+      <c r="J2" t="s">
         <v>447</v>
       </c>
-      <c r="G2" t="s">
+      <c r="K2" t="s">
         <v>448</v>
       </c>
-      <c r="H2" t="s">
+      <c r="L2" t="s">
+        <v>51</v>
+      </c>
+      <c r="M2" t="s">
         <v>449</v>
       </c>
-      <c r="I2" t="s">
+      <c r="N2" t="s">
         <v>450</v>
       </c>
-      <c r="J2" t="s">
+      <c r="O2" t="s">
         <v>451</v>
       </c>
-      <c r="K2" t="s">
-        <v>452</v>
-      </c>
-      <c r="L2" t="s">
-        <v>53</v>
-      </c>
-      <c r="M2" t="s">
-        <v>453</v>
-      </c>
-      <c r="N2" t="s">
-        <v>454</v>
-      </c>
-      <c r="O2" t="s">
-        <v>455</v>
-      </c>
       <c r="P2" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
@@ -9515,48 +9516,48 @@
         <v>2</v>
       </c>
       <c r="E3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="G3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="I3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="J3" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="K3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="L3" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="M3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="N3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="O3" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="P3" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="C4" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="H4">
         <v>1</v>
@@ -9565,21 +9566,21 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="C5" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="H5">
         <v>1</v>
       </c>
       <c r="J5" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="N5">
         <v>1</v>
@@ -9588,10 +9589,10 @@
     </row>
     <row r="6" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="H6" s="2">
         <v>1</v>
@@ -9600,94 +9601,94 @@
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="C7" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="P7" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="C8" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="C9" t="s">
+        <v>456</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="J9" t="s">
+        <v>459</v>
+      </c>
+      <c r="P9" t="s">
         <v>460</v>
-      </c>
-      <c r="H9">
-        <v>1</v>
-      </c>
-      <c r="J9" t="s">
-        <v>463</v>
-      </c>
-      <c r="P9" t="s">
-        <v>464</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="C10" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="H10">
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="C11" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="H11">
         <v>1</v>
       </c>
       <c r="J11" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="P11" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="C12" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="H12">
         <v>1</v>
       </c>
       <c r="J12" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="P12" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
     </row>
     <row r="13" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="H13" s="2">
         <v>1</v>
@@ -9695,52 +9696,52 @@
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="C14" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="H14">
         <v>1</v>
       </c>
       <c r="J14" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="P15" s="12" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="C16" s="12" t="s">
+        <v>523</v>
+      </c>
+      <c r="P16" s="12" t="s">
         <v>527</v>
-      </c>
-      <c r="P16" s="12" t="s">
-        <v>531</v>
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="H17">
         <v>1</v>
       </c>
       <c r="P17" s="12" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
     </row>
   </sheetData>
@@ -9765,7 +9766,7 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -9773,13 +9774,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C2" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="D2" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -9790,10 +9791,10 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="D3" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -9816,7 +9817,7 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="I1" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -9824,31 +9825,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" t="s">
         <v>48</v>
       </c>
-      <c r="C2" t="s">
-        <v>50</v>
-      </c>
       <c r="D2" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="E2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F2" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="G2" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="H2" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="I2" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="J2" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -9865,22 +9866,22 @@
         <v>2</v>
       </c>
       <c r="E3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="F3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="G3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="I3" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="J3" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -9907,34 +9908,34 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>472</v>
+      </c>
+      <c r="C1" t="s">
+        <v>473</v>
+      </c>
+      <c r="D1" t="s">
+        <v>474</v>
+      </c>
+      <c r="E1" t="s">
+        <v>475</v>
+      </c>
+      <c r="F1" t="s">
         <v>476</v>
       </c>
-      <c r="C1" t="s">
+      <c r="H1" t="s">
         <v>477</v>
       </c>
-      <c r="D1" t="s">
+      <c r="I1" t="s">
         <v>478</v>
       </c>
-      <c r="E1" t="s">
+      <c r="J1" t="s">
         <v>479</v>
       </c>
-      <c r="F1" t="s">
+      <c r="K1" t="s">
         <v>480</v>
       </c>
-      <c r="H1" t="s">
+      <c r="L1" t="s">
         <v>481</v>
-      </c>
-      <c r="I1" t="s">
-        <v>482</v>
-      </c>
-      <c r="J1" t="s">
-        <v>483</v>
-      </c>
-      <c r="K1" t="s">
-        <v>484</v>
-      </c>
-      <c r="L1" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -9942,37 +9943,37 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>482</v>
+      </c>
+      <c r="C2" t="s">
+        <v>483</v>
+      </c>
+      <c r="D2" t="s">
+        <v>484</v>
+      </c>
+      <c r="E2" t="s">
+        <v>485</v>
+      </c>
+      <c r="F2" t="s">
         <v>486</v>
       </c>
-      <c r="C2" t="s">
+      <c r="G2" t="s">
         <v>487</v>
       </c>
-      <c r="D2" t="s">
+      <c r="H2" t="s">
         <v>488</v>
       </c>
-      <c r="E2" t="s">
+      <c r="I2" t="s">
         <v>489</v>
       </c>
-      <c r="F2" t="s">
+      <c r="J2" t="s">
         <v>490</v>
       </c>
-      <c r="G2" t="s">
-        <v>491</v>
-      </c>
-      <c r="H2" t="s">
-        <v>492</v>
-      </c>
-      <c r="I2" t="s">
-        <v>493</v>
-      </c>
-      <c r="J2" t="s">
-        <v>494</v>
-      </c>
       <c r="K2" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="L2" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -9983,34 +9984,34 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D3" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="E3" t="s">
         <v>2</v>
       </c>
       <c r="F3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="G3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="H3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="I3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="J3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="K3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="L3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>
@@ -10040,31 +10041,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="C2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D2" t="s">
+        <v>492</v>
+      </c>
+      <c r="E2" t="s">
+        <v>493</v>
+      </c>
+      <c r="F2" t="s">
         <v>77</v>
       </c>
-      <c r="D2" t="s">
-        <v>496</v>
-      </c>
-      <c r="E2" t="s">
-        <v>497</v>
-      </c>
-      <c r="F2" t="s">
-        <v>79</v>
-      </c>
       <c r="G2" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="H2" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="I2" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="J2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -10081,22 +10082,22 @@
         <v>2</v>
       </c>
       <c r="E3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F3" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="G3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H3" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="I3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="J3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -10125,28 +10126,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>502</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>503</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>504</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>505</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>506</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>507</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>508</v>
       </c>
     </row>
     <row r="2" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -10154,28 +10155,28 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>510</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>511</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>512</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>513</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>514</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>515</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>516</v>
       </c>
     </row>
     <row r="3" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -10183,10 +10184,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>2</v>
@@ -10215,22 +10216,22 @@
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>517</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>518</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>519</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>520</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>521</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>522</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/一方通行/斩业星熊.xlsx
+++ b/Excel/一方通行/斩业星熊.xlsx
@@ -323,7 +323,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="550">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="552">
   <si>
     <t>Id</t>
   </si>
@@ -670,6 +670,9 @@
     <t>Ablititys</t>
   </si>
   <si>
+    <t>StartAnimation</t>
+  </si>
+  <si>
     <t>DefaultAnimation</t>
   </si>
   <si>
@@ -686,6 +689,9 @@
   </si>
   <si>
     <t>ForwardAnimation</t>
+  </si>
+  <si>
+    <t>DieAnimation</t>
   </si>
   <si>
     <t>MaxAnimationScale</t>
@@ -2020,11 +2026,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
@@ -2338,30 +2347,30 @@
   <dimension ref="A2:B4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="9" customWidth="1" style="2"/>
+    <col min="1" max="2" width="9" customWidth="1" style="3"/>
   </cols>
   <sheetData>
     <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2374,7 +2383,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:BV4"/>
+  <dimension ref="A1:BX4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.58203125" customWidth="1" style="2"/>
@@ -2444,13 +2453,15 @@
     <col min="65" max="65" width="9" customWidth="1" style="2"/>
     <col min="66" max="66" width="9" customWidth="1" style="2"/>
     <col min="67" max="67" width="39.58203125" customWidth="1" style="2"/>
-    <col min="68" max="68" width="14" customWidth="1" style="2"/>
-    <col min="69" max="69" width="14.83203125" customWidth="1" style="2"/>
-    <col min="70" max="70" width="14" customWidth="1" style="2"/>
+    <col min="68" max="68" width="9" customWidth="1" style="2"/>
+    <col min="69" max="69" width="14" customWidth="1" style="2"/>
+    <col min="70" max="70" width="14.83203125" customWidth="1" style="2"/>
     <col min="71" max="71" width="14" customWidth="1" style="2"/>
     <col min="72" max="72" width="14" customWidth="1" style="2"/>
     <col min="73" max="73" width="14" customWidth="1" style="2"/>
-    <col min="74" max="74" width="19.1640625" customWidth="1" style="2"/>
+    <col min="74" max="74" width="14" customWidth="1" style="2"/>
+    <col min="75" max="75" width="9" customWidth="1" style="2"/>
+    <col min="76" max="76" width="19.1640625" customWidth="1" style="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2622,6 +2633,8 @@
       <c r="BT1" s="2"/>
       <c r="BU1" s="2"/>
       <c r="BV1" s="2"/>
+      <c r="BW1" s="2"/>
+      <c r="BX1" s="2"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
@@ -2842,6 +2855,12 @@
       <c r="BV2" s="2" t="s">
         <v>121</v>
       </c>
+      <c r="BW2" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="BX2" s="2" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
@@ -2851,7 +2870,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -2859,91 +2878,91 @@
         <v>2</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>2</v>
       </c>
       <c r="J3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="U3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="V3" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="W3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="X3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="Y3" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="Z3" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="AA3" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="AB3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="AC3" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="O3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="S3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="T3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="U3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="V3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="W3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="X3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="Y3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="Z3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="AA3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="AB3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="AC3" s="2" t="s">
-        <v>123</v>
-      </c>
       <c r="AD3" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="AE3" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="AF3" s="2" t="s">
         <v>2</v>
       </c>
       <c r="AG3" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="AH3" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="AI3" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="AJ3" s="2" t="s">
         <v>2</v>
@@ -2952,10 +2971,10 @@
         <v>2</v>
       </c>
       <c r="AL3" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="AM3" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="AN3" s="2" t="s">
         <v>2</v>
@@ -2964,50 +2983,50 @@
         <v>2</v>
       </c>
       <c r="AP3" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="AQ3" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="AR3" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="AR3" s="2" t="s">
+      <c r="AS3" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="AS3" s="2" t="s">
-        <v>123</v>
-      </c>
       <c r="AT3" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="AU3" s="2"/>
       <c r="AV3" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="AW3" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="AX3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="AY3" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="AZ3" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="AY3" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="AZ3" s="2" t="s">
-        <v>123</v>
-      </c>
       <c r="BA3" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="BB3" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="BC3" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="BD3" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="BE3" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="BF3" s="2" t="s">
         <v>2</v>
@@ -3022,43 +3041,49 @@
         <v>2</v>
       </c>
       <c r="BJ3" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="BK3" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="BL3" s="2" t="s">
         <v>2</v>
       </c>
       <c r="BM3" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="BN3" s="2" t="s">
         <v>2</v>
       </c>
       <c r="BO3" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="BP3" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="BQ3" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="BR3" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="BS3" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="BT3" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="BU3" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="BV3" s="2" t="s">
-        <v>123</v>
+        <v>129</v>
+      </c>
+      <c r="BW3" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="BX3" s="2" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="4">
@@ -3066,13 +3091,13 @@
         <v>4</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
       <c r="F4" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="G4" s="2">
         <v>1</v>
@@ -3133,23 +3158,23 @@
         <v>4</v>
       </c>
       <c r="AK4" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AL4" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="AM4" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AN4" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AO4" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="AP4" s="2"/>
       <c r="AQ4" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AR4" s="2">
         <v>3</v>
@@ -3171,49 +3196,51 @@
       <c r="BC4" s="2"/>
       <c r="BD4" s="2"/>
       <c r="BE4" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="BF4" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="BG4" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="BH4" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="BI4" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="BJ4" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="BK4" s="2">
         <v>6</v>
       </c>
       <c r="BL4" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="BM4" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="BN4" s="2"/>
       <c r="BO4" s="2"/>
-      <c r="BP4" s="2" t="s">
-        <v>149</v>
-      </c>
+      <c r="BP4" s="2"/>
       <c r="BQ4" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="BR4" s="2"/>
-      <c r="BS4" s="2" t="s">
         <v>151</v>
       </c>
+      <c r="BR4" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="BS4" s="2"/>
       <c r="BT4" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="BU4" s="2"/>
-      <c r="BV4" s="2">
+        <v>153</v>
+      </c>
+      <c r="BU4" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="BV4" s="2"/>
+      <c r="BW4" s="2"/>
+      <c r="BX4" s="2">
         <v>1</v>
       </c>
     </row>
@@ -3231,2161 +3258,2161 @@
   <dimension ref="A1:DI599"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.08203125" customWidth="1" style="2"/>
-    <col min="2" max="2" width="15.58203125" customWidth="1" style="2"/>
-    <col min="3" max="3" width="7.75" customWidth="1" style="2"/>
-    <col min="4" max="4" width="16.58203125" customWidth="1" style="2"/>
-    <col min="5" max="5" width="16.83203125" customWidth="1" style="2"/>
-    <col min="6" max="6" width="31.33203125" customWidth="1" style="2"/>
-    <col min="7" max="7" width="7.33203125" customWidth="1" style="2"/>
-    <col min="8" max="8" width="17.83203125" customWidth="1" style="2"/>
-    <col min="9" max="9" width="7.33203125" customWidth="1" style="2"/>
-    <col min="10" max="10" width="15.75" customWidth="1" style="2"/>
-    <col min="11" max="13" width="8.33203125" customWidth="1" style="2"/>
-    <col min="14" max="14" width="11.75" customWidth="1" style="2"/>
-    <col min="15" max="15" width="13.08203125" customWidth="1" style="2"/>
-    <col min="16" max="16" width="11.58203125" customWidth="1" style="2"/>
-    <col min="17" max="17" width="21.5" customWidth="1" style="2"/>
-    <col min="18" max="18" width="19.83203125" customWidth="1" style="2"/>
-    <col min="19" max="19" width="16.58203125" customWidth="1" style="2"/>
-    <col min="20" max="20" width="19.08203125" customWidth="1" style="2"/>
-    <col min="21" max="21" width="18.33203125" customWidth="1" style="2"/>
-    <col min="22" max="22" width="17.75" customWidth="1" style="2"/>
-    <col min="23" max="23" width="8.33203125" customWidth="1" style="2"/>
-    <col min="24" max="24" width="18.5" customWidth="1" style="2"/>
-    <col min="25" max="25" width="16.58203125" customWidth="1" style="2"/>
-    <col min="26" max="26" width="10.6640625" customWidth="1" style="2"/>
-    <col min="27" max="27" width="8.33203125" customWidth="1" style="2"/>
-    <col min="28" max="28" width="15.1640625" customWidth="1" style="2"/>
-    <col min="29" max="30" width="8.58203125" customWidth="1" style="2"/>
-    <col min="31" max="31" width="13.4140625" customWidth="1" style="2"/>
-    <col min="32" max="32" width="13.75" customWidth="1" style="2"/>
-    <col min="33" max="33" width="14.58203125" customWidth="1" style="2"/>
-    <col min="34" max="34" width="17.4140625" customWidth="1" style="2"/>
-    <col min="35" max="35" width="8.58203125" customWidth="1" style="2"/>
-    <col min="36" max="36" width="12.5" customWidth="1" style="2"/>
-    <col min="37" max="37" width="8.58203125" customWidth="1" style="2"/>
-    <col min="38" max="39" width="8.33203125" customWidth="1" style="2"/>
-    <col min="40" max="40" width="15" customWidth="1" style="2"/>
-    <col min="41" max="41" width="13.25" customWidth="1" style="2"/>
-    <col min="42" max="45" width="11.83203125" customWidth="1" style="2"/>
-    <col min="46" max="46" width="18.4140625" customWidth="1" style="2"/>
-    <col min="47" max="47" width="12.25" customWidth="1" style="2"/>
-    <col min="48" max="48" width="11.9140625" customWidth="1" style="2"/>
-    <col min="49" max="49" width="19.58203125" customWidth="1" style="2"/>
-    <col min="50" max="50" width="12.6640625" customWidth="1" style="2"/>
-    <col min="51" max="51" width="9" customWidth="1" style="2"/>
-    <col min="52" max="52" width="7" customWidth="1" style="2"/>
-    <col min="53" max="53" width="11.75" customWidth="1" style="2"/>
-    <col min="54" max="54" width="19.75" customWidth="1" style="2"/>
-    <col min="55" max="55" width="5.08203125" customWidth="1" style="2"/>
-    <col min="56" max="56" width="8.5" customWidth="1" style="2"/>
-    <col min="57" max="57" width="13.5" customWidth="1" style="2"/>
-    <col min="58" max="58" width="14.6640625" customWidth="1" style="2"/>
-    <col min="59" max="59" width="10.1640625" customWidth="1" style="2"/>
-    <col min="60" max="60" width="8.25" customWidth="1" style="2"/>
-    <col min="61" max="67" width="8.33203125" customWidth="1" style="2"/>
-    <col min="68" max="70" width="11.25" customWidth="1" style="2"/>
-    <col min="71" max="71" width="6.58203125" customWidth="1" style="2"/>
-    <col min="72" max="73" width="8" customWidth="1" style="2"/>
-    <col min="74" max="74" width="7.33203125" customWidth="1" style="2"/>
-    <col min="75" max="76" width="8.5" customWidth="1" style="2"/>
-    <col min="77" max="78" width="7.83203125" customWidth="1" style="2"/>
-    <col min="79" max="79" width="22.1640625" customWidth="1" style="2"/>
-    <col min="80" max="80" width="13.5" customWidth="1" style="2"/>
-    <col min="81" max="81" width="21.1640625" customWidth="1" style="2"/>
-    <col min="82" max="82" width="15.75" customWidth="1" style="2"/>
-    <col min="83" max="83" width="15.58203125" customWidth="1" style="2"/>
-    <col min="84" max="84" width="12.83203125" customWidth="1" style="2"/>
-    <col min="85" max="85" width="16.1640625" customWidth="1" style="2"/>
-    <col min="86" max="86" width="9" customWidth="1" style="2"/>
-    <col min="87" max="87" width="16" customWidth="1" style="2"/>
-    <col min="88" max="89" width="12.83203125" customWidth="1" style="2"/>
-    <col min="90" max="90" width="23.58203125" customWidth="1" style="2"/>
-    <col min="91" max="91" width="12.83203125" customWidth="1" style="2"/>
-    <col min="92" max="92" width="17.08203125" customWidth="1" style="2"/>
-    <col min="93" max="93" width="9.5" customWidth="1" style="2"/>
-    <col min="94" max="98" width="9" customWidth="1" style="2"/>
-    <col min="99" max="99" width="14" customWidth="1" style="2"/>
-    <col min="100" max="100" width="8" customWidth="1" style="2"/>
-    <col min="101" max="101" width="9" customWidth="1" style="2"/>
-    <col min="102" max="102" width="11.08203125" customWidth="1" style="2"/>
-    <col min="103" max="103" width="13.75" customWidth="1" style="2"/>
-    <col min="104" max="104" width="9.5" customWidth="1" style="2"/>
-    <col min="105" max="106" width="9" customWidth="1" style="2"/>
-    <col min="107" max="108" width="9.5" customWidth="1" style="2"/>
-    <col min="109" max="109" width="9" customWidth="1" style="2"/>
-    <col min="110" max="110" width="15.5" customWidth="1" style="2"/>
-    <col min="111" max="111" width="9" customWidth="1" style="2"/>
-    <col min="112" max="113" width="9.5" customWidth="1" style="2"/>
+    <col min="1" max="1" width="21.08203125" customWidth="1" style="3"/>
+    <col min="2" max="2" width="15.58203125" customWidth="1" style="3"/>
+    <col min="3" max="3" width="7.75" customWidth="1" style="3"/>
+    <col min="4" max="4" width="16.58203125" customWidth="1" style="3"/>
+    <col min="5" max="5" width="16.83203125" customWidth="1" style="3"/>
+    <col min="6" max="6" width="31.33203125" customWidth="1" style="3"/>
+    <col min="7" max="7" width="7.33203125" customWidth="1" style="3"/>
+    <col min="8" max="8" width="17.83203125" customWidth="1" style="3"/>
+    <col min="9" max="9" width="7.33203125" customWidth="1" style="3"/>
+    <col min="10" max="10" width="15.75" customWidth="1" style="3"/>
+    <col min="11" max="13" width="8.33203125" customWidth="1" style="3"/>
+    <col min="14" max="14" width="11.75" customWidth="1" style="3"/>
+    <col min="15" max="15" width="13.08203125" customWidth="1" style="3"/>
+    <col min="16" max="16" width="11.58203125" customWidth="1" style="3"/>
+    <col min="17" max="17" width="21.5" customWidth="1" style="3"/>
+    <col min="18" max="18" width="19.83203125" customWidth="1" style="3"/>
+    <col min="19" max="19" width="16.58203125" customWidth="1" style="3"/>
+    <col min="20" max="20" width="19.08203125" customWidth="1" style="3"/>
+    <col min="21" max="21" width="18.33203125" customWidth="1" style="3"/>
+    <col min="22" max="22" width="17.75" customWidth="1" style="3"/>
+    <col min="23" max="23" width="8.33203125" customWidth="1" style="3"/>
+    <col min="24" max="24" width="18.5" customWidth="1" style="3"/>
+    <col min="25" max="25" width="16.58203125" customWidth="1" style="3"/>
+    <col min="26" max="26" width="10.6640625" customWidth="1" style="3"/>
+    <col min="27" max="27" width="8.33203125" customWidth="1" style="3"/>
+    <col min="28" max="28" width="15.1640625" customWidth="1" style="3"/>
+    <col min="29" max="30" width="8.58203125" customWidth="1" style="3"/>
+    <col min="31" max="31" width="13.4140625" customWidth="1" style="3"/>
+    <col min="32" max="32" width="13.75" customWidth="1" style="3"/>
+    <col min="33" max="33" width="14.58203125" customWidth="1" style="3"/>
+    <col min="34" max="34" width="17.4140625" customWidth="1" style="3"/>
+    <col min="35" max="35" width="8.58203125" customWidth="1" style="3"/>
+    <col min="36" max="36" width="12.5" customWidth="1" style="3"/>
+    <col min="37" max="37" width="8.58203125" customWidth="1" style="3"/>
+    <col min="38" max="39" width="8.33203125" customWidth="1" style="3"/>
+    <col min="40" max="40" width="15" customWidth="1" style="3"/>
+    <col min="41" max="41" width="13.25" customWidth="1" style="3"/>
+    <col min="42" max="45" width="11.83203125" customWidth="1" style="3"/>
+    <col min="46" max="46" width="18.4140625" customWidth="1" style="3"/>
+    <col min="47" max="47" width="12.25" customWidth="1" style="3"/>
+    <col min="48" max="48" width="11.9140625" customWidth="1" style="3"/>
+    <col min="49" max="49" width="19.58203125" customWidth="1" style="3"/>
+    <col min="50" max="50" width="12.6640625" customWidth="1" style="3"/>
+    <col min="51" max="51" width="9" customWidth="1" style="3"/>
+    <col min="52" max="52" width="7" customWidth="1" style="3"/>
+    <col min="53" max="53" width="11.75" customWidth="1" style="3"/>
+    <col min="54" max="54" width="19.75" customWidth="1" style="3"/>
+    <col min="55" max="55" width="5.08203125" customWidth="1" style="3"/>
+    <col min="56" max="56" width="8.5" customWidth="1" style="3"/>
+    <col min="57" max="57" width="13.5" customWidth="1" style="3"/>
+    <col min="58" max="58" width="14.6640625" customWidth="1" style="3"/>
+    <col min="59" max="59" width="10.1640625" customWidth="1" style="3"/>
+    <col min="60" max="60" width="8.25" customWidth="1" style="3"/>
+    <col min="61" max="67" width="8.33203125" customWidth="1" style="3"/>
+    <col min="68" max="70" width="11.25" customWidth="1" style="3"/>
+    <col min="71" max="71" width="6.58203125" customWidth="1" style="3"/>
+    <col min="72" max="73" width="8" customWidth="1" style="3"/>
+    <col min="74" max="74" width="7.33203125" customWidth="1" style="3"/>
+    <col min="75" max="76" width="8.5" customWidth="1" style="3"/>
+    <col min="77" max="78" width="7.83203125" customWidth="1" style="3"/>
+    <col min="79" max="79" width="22.1640625" customWidth="1" style="3"/>
+    <col min="80" max="80" width="13.5" customWidth="1" style="3"/>
+    <col min="81" max="81" width="21.1640625" customWidth="1" style="3"/>
+    <col min="82" max="82" width="15.75" customWidth="1" style="3"/>
+    <col min="83" max="83" width="15.58203125" customWidth="1" style="3"/>
+    <col min="84" max="84" width="12.83203125" customWidth="1" style="3"/>
+    <col min="85" max="85" width="16.1640625" customWidth="1" style="3"/>
+    <col min="86" max="86" width="9" customWidth="1" style="3"/>
+    <col min="87" max="87" width="16" customWidth="1" style="3"/>
+    <col min="88" max="89" width="12.83203125" customWidth="1" style="3"/>
+    <col min="90" max="90" width="23.58203125" customWidth="1" style="3"/>
+    <col min="91" max="91" width="12.83203125" customWidth="1" style="3"/>
+    <col min="92" max="92" width="17.08203125" customWidth="1" style="3"/>
+    <col min="93" max="93" width="9.5" customWidth="1" style="3"/>
+    <col min="94" max="98" width="9" customWidth="1" style="3"/>
+    <col min="99" max="99" width="14" customWidth="1" style="3"/>
+    <col min="100" max="100" width="8" customWidth="1" style="3"/>
+    <col min="101" max="101" width="9" customWidth="1" style="3"/>
+    <col min="102" max="102" width="11.08203125" customWidth="1" style="3"/>
+    <col min="103" max="103" width="13.75" customWidth="1" style="3"/>
+    <col min="104" max="104" width="9.5" customWidth="1" style="3"/>
+    <col min="105" max="106" width="9" customWidth="1" style="3"/>
+    <col min="107" max="108" width="9.5" customWidth="1" style="3"/>
+    <col min="109" max="109" width="9" customWidth="1" style="3"/>
+    <col min="110" max="110" width="15.5" customWidth="1" style="3"/>
+    <col min="111" max="111" width="9" customWidth="1" style="3"/>
+    <col min="112" max="113" width="9.5" customWidth="1" style="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="B1" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="E1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="K1" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="L1" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="M1" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="N1" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="O1" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="P1" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="Q1" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="R1" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="U1" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="V1" s="2" t="s">
+      <c r="S1" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="T1" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="X1" s="2" t="s">
+      <c r="U1" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="V1" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="W1" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="X1" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="Y1" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="AB1" s="2" t="s">
+      <c r="Z1" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="AC1" s="2" t="s">
+      <c r="AA1" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="AD1" s="2" t="s">
+      <c r="AB1" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="AE1" s="2" t="s">
+      <c r="AC1" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="AF1" s="2" t="s">
+      <c r="AD1" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="AG1" s="2" t="s">
+      <c r="AE1" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="AH1" s="2" t="s">
+      <c r="AF1" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="AI1" s="2" t="s">
+      <c r="AG1" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="AJ1" s="2" t="s">
+      <c r="AH1" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="AK1" s="2" t="s">
+      <c r="AI1" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="AL1" s="2" t="s">
+      <c r="AJ1" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="AM1" s="2" t="s">
+      <c r="AK1" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="AN1" s="2" t="s">
+      <c r="AL1" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="AO1" s="2" t="s">
+      <c r="AM1" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="AP1" s="2" t="s">
+      <c r="AN1" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="AQ1" s="2" t="s">
+      <c r="AO1" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="AR1" s="2" t="s">
+      <c r="AP1" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="AS1" s="2" t="s">
+      <c r="AQ1" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="AT1" s="2" t="s">
+      <c r="AR1" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="AU1" s="2" t="s">
+      <c r="AS1" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="AV1" s="2" t="s">
+      <c r="AT1" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="AW1" s="2" t="s">
+      <c r="AU1" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="AX1" s="2" t="s">
+      <c r="AV1" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="AY1" s="2" t="s">
+      <c r="AW1" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="AZ1" s="2" t="s">
+      <c r="AX1" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="BA1" s="2" t="s">
+      <c r="AY1" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="BB1" s="2" t="s">
+      <c r="AZ1" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="BC1" s="2" t="s">
+      <c r="BA1" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="BD1" s="2" t="s">
+      <c r="BB1" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="BE1" s="2" t="s">
+      <c r="BC1" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="BF1" s="2" t="s">
+      <c r="BD1" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="BG1" s="2" t="s">
+      <c r="BE1" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="BH1" s="2" t="s">
+      <c r="BF1" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="BJ1" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="BK1" s="2" t="s">
+      <c r="BG1" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="BL1" s="2" t="s">
+      <c r="BH1" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="BM1" s="2" t="s">
+      <c r="BJ1" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="BK1" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="BN1" s="2" t="s">
+      <c r="BL1" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="BO1" s="2" t="s">
+      <c r="BM1" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="BP1" s="2" t="s">
+      <c r="BN1" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="BQ1" s="2" t="s">
+      <c r="BO1" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="BR1" s="2" t="s">
+      <c r="BP1" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="BS1" s="2" t="s">
+      <c r="BQ1" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="BT1" s="2" t="s">
+      <c r="BR1" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="BU1" s="2" t="s">
+      <c r="BS1" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="BV1" s="2" t="s">
+      <c r="BT1" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="BW1" s="2" t="s">
+      <c r="BU1" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="BX1" s="2" t="s">
+      <c r="BV1" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="BY1" s="2" t="s">
+      <c r="BW1" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="BZ1" s="2" t="s">
+      <c r="BX1" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="CA1" s="2" t="s">
+      <c r="BY1" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="CB1" s="2" t="s">
+      <c r="BZ1" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="CC1" s="2" t="s">
+      <c r="CA1" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="CD1" s="2" t="s">
+      <c r="CB1" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="CE1" s="2" t="s">
+      <c r="CC1" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="CF1" s="2" t="s">
+      <c r="CD1" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="CG1" s="2" t="s">
+      <c r="CE1" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="CH1" s="2" t="s">
+      <c r="CF1" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="CI1" s="2" t="s">
+      <c r="CG1" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="CJ1" s="2" t="s">
+      <c r="CH1" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="CK1" s="2" t="s">
+      <c r="CI1" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="CL1" s="2" t="s">
+      <c r="CJ1" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="CM1" s="2" t="s">
+      <c r="CK1" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="CN1" s="2" t="s">
+      <c r="CL1" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="CO1" s="2" t="s">
+      <c r="CM1" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="CP1" s="2" t="s">
+      <c r="CN1" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="CQ1" s="2" t="s">
+      <c r="CO1" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="CR1" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="CS1" s="2" t="s">
+      <c r="CP1" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="CT1" s="2" t="s">
+      <c r="CQ1" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="CU1" s="2" t="s">
+      <c r="CR1" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="CS1" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="CV1" s="2" t="s">
+      <c r="CT1" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="CW1" s="2" t="s">
+      <c r="CU1" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="CX1" s="2" t="s">
+      <c r="CV1" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="CY1" s="2" t="s">
+      <c r="CW1" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="CZ1" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="DA1" s="2" t="s">
+      <c r="CX1" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="DB1" s="2" t="s">
+      <c r="CY1" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="DC1" s="2" t="s">
+      <c r="CZ1" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="DA1" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="DD1" s="2" t="s">
+      <c r="DB1" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="DE1" s="2" t="s">
+      <c r="DC1" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="DF1" s="2" t="s">
+      <c r="DD1" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="DG1" s="2" t="s">
+      <c r="DE1" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="DH1" s="2" t="s">
+      <c r="DF1" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="DI1" s="2" t="s">
+      <c r="DG1" s="3" t="s">
         <v>257</v>
       </c>
+      <c r="DH1" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="DI1" s="3" t="s">
+        <v>259</v>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="G2" s="2" t="s">
+      <c r="E2" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="G2" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="J2" s="2" t="s">
+      <c r="H2" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="I2" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="J2" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="K2" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="L2" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="M2" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="N2" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="O2" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="R2" s="2" t="s">
+      <c r="P2" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="S2" s="2" t="s">
+      <c r="Q2" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="T2" s="2" t="s">
+      <c r="R2" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="U2" s="2" t="s">
+      <c r="S2" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="V2" s="2" t="s">
+      <c r="T2" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="W2" s="2" t="s">
+      <c r="U2" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="X2" s="2" t="s">
+      <c r="V2" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="Y2" s="2" t="s">
+      <c r="W2" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="Z2" s="2" t="s">
+      <c r="X2" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="AA2" s="2" t="s">
+      <c r="Y2" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="AB2" s="2" t="s">
+      <c r="Z2" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="AC2" s="2" t="s">
+      <c r="AA2" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="AD2" s="2" t="s">
+      <c r="AB2" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="AE2" s="2" t="s">
+      <c r="AC2" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="AF2" s="2" t="s">
+      <c r="AD2" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="AG2" s="2" t="s">
+      <c r="AE2" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="AH2" s="2" t="s">
+      <c r="AF2" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="AI2" s="2" t="s">
+      <c r="AG2" s="3" t="s">
         <v>287</v>
       </c>
-      <c r="AJ2" s="2" t="s">
+      <c r="AH2" s="3" t="s">
         <v>288</v>
       </c>
-      <c r="AK2" s="2" t="s">
+      <c r="AI2" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="AL2" s="2" t="s">
+      <c r="AJ2" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="AM2" s="2" t="s">
+      <c r="AK2" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="AN2" s="2" t="s">
+      <c r="AL2" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="AO2" s="2" t="s">
+      <c r="AM2" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="AP2" s="2" t="s">
+      <c r="AN2" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="AQ2" s="2" t="s">
+      <c r="AO2" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="AR2" s="2" t="s">
+      <c r="AP2" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="AS2" s="2" t="s">
+      <c r="AQ2" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="AT2" s="2" t="s">
+      <c r="AR2" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="AU2" s="2" t="s">
+      <c r="AS2" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="AV2" s="2" t="s">
+      <c r="AT2" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="AW2" s="2" t="s">
+      <c r="AU2" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="AX2" s="2" t="s">
+      <c r="AV2" s="3" t="s">
         <v>302</v>
       </c>
-      <c r="AY2" s="2" t="s">
+      <c r="AW2" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="AZ2" s="2" t="s">
+      <c r="AX2" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="BA2" s="2" t="s">
+      <c r="AY2" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="BB2" s="2" t="s">
+      <c r="AZ2" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="BC2" s="2" t="s">
+      <c r="BA2" s="3" t="s">
         <v>307</v>
       </c>
-      <c r="BD2" s="2" t="s">
+      <c r="BB2" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="BE2" s="2" t="s">
+      <c r="BC2" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="BF2" s="2" t="s">
+      <c r="BD2" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="BG2" s="2" t="s">
+      <c r="BE2" s="3" t="s">
         <v>311</v>
       </c>
-      <c r="BH2" s="2" t="s">
+      <c r="BF2" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="BI2" s="2" t="s">
+      <c r="BG2" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="BJ2" s="2" t="s">
+      <c r="BH2" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="BK2" s="2" t="s">
+      <c r="BI2" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="BL2" s="2" t="s">
+      <c r="BJ2" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="BM2" s="2" t="s">
+      <c r="BK2" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="BN2" s="2" t="s">
+      <c r="BL2" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="BO2" s="2" t="s">
+      <c r="BM2" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="BN2" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="BO2" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="BP2" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="BQ2" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="BR2" s="2" t="s">
+      <c r="BP2" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="BS2" s="2" t="s">
+      <c r="BQ2" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="BT2" s="2" t="s">
+      <c r="BR2" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="BU2" s="2" t="s">
+      <c r="BS2" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="BT2" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="BU2" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="BV2" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="BW2" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="BX2" s="2" t="s">
+      <c r="BV2" s="3" t="s">
         <v>326</v>
       </c>
-      <c r="BY2" s="2" t="s">
+      <c r="BW2" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="BZ2" s="2" t="s">
+      <c r="BX2" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="CA2" s="2" t="s">
+      <c r="BY2" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="CB2" s="2" t="s">
+      <c r="BZ2" s="3" t="s">
         <v>330</v>
       </c>
-      <c r="CC2" s="2" t="s">
+      <c r="CA2" s="3" t="s">
         <v>331</v>
       </c>
-      <c r="CD2" s="2" t="s">
+      <c r="CB2" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="CE2" s="2" t="s">
+      <c r="CC2" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="CF2" s="2" t="s">
+      <c r="CD2" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="CG2" s="2" t="s">
+      <c r="CE2" s="3" t="s">
         <v>335</v>
       </c>
-      <c r="CH2" s="2" t="s">
+      <c r="CF2" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="CI2" s="2" t="s">
+      <c r="CG2" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="CJ2" s="2" t="s">
+      <c r="CH2" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="CK2" s="2" t="s">
+      <c r="CI2" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="CL2" s="2" t="s">
+      <c r="CJ2" s="3" t="s">
         <v>340</v>
       </c>
-      <c r="CM2" s="2" t="s">
+      <c r="CK2" s="3" t="s">
         <v>341</v>
       </c>
-      <c r="CN2" s="2" t="s">
+      <c r="CL2" s="3" t="s">
         <v>342</v>
       </c>
-      <c r="CO2" s="2" t="s">
+      <c r="CM2" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="CP2" s="2" t="s">
+      <c r="CN2" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="CQ2" s="2" t="s">
+      <c r="CO2" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="CR2" s="2" t="s">
+      <c r="CP2" s="3" t="s">
         <v>346</v>
       </c>
-      <c r="CS2" s="2" t="s">
+      <c r="CQ2" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="CT2" s="2" t="s">
+      <c r="CR2" s="3" t="s">
         <v>348</v>
       </c>
-      <c r="CU2" s="2" t="s">
+      <c r="CS2" s="3" t="s">
         <v>349</v>
       </c>
-      <c r="CV2" s="2" t="s">
+      <c r="CT2" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="CW2" s="2" t="s">
+      <c r="CU2" s="3" t="s">
         <v>351</v>
       </c>
-      <c r="CX2" s="2" t="s">
+      <c r="CV2" s="3" t="s">
         <v>352</v>
       </c>
-      <c r="CY2" s="2" t="s">
+      <c r="CW2" s="3" t="s">
         <v>353</v>
       </c>
-      <c r="CZ2" s="2" t="s">
+      <c r="CX2" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="DA2" s="2" t="s">
+      <c r="CY2" s="3" t="s">
         <v>355</v>
       </c>
-      <c r="DB2" s="2" t="s">
+      <c r="CZ2" s="3" t="s">
         <v>356</v>
       </c>
-      <c r="DC2" s="2" t="s">
+      <c r="DA2" s="3" t="s">
         <v>357</v>
       </c>
-      <c r="DD2" s="2" t="s">
+      <c r="DB2" s="3" t="s">
         <v>358</v>
       </c>
-      <c r="DE2" s="2" t="s">
+      <c r="DC2" s="3" t="s">
         <v>359</v>
       </c>
-      <c r="DF2" s="2" t="s">
+      <c r="DD2" s="3" t="s">
         <v>360</v>
       </c>
-      <c r="DG2" s="2" t="s">
+      <c r="DE2" s="3" t="s">
         <v>361</v>
       </c>
-      <c r="DH2" s="2" t="s">
+      <c r="DF2" s="3" t="s">
         <v>362</v>
       </c>
-      <c r="DI2" s="2" t="s">
+      <c r="DG2" s="3" t="s">
         <v>363</v>
       </c>
+      <c r="DH2" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="DI2" s="3" t="s">
+        <v>365</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="R3" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="S3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="T3" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="U3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="V3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="W3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="X3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="Y3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="Z3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="AA3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="AB3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="AC3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="AD3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="AE3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="AF3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="AG3" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="AH3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="AI3" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="AJ3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="AL3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="AM3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="AN3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="AO3" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="AP3" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="AQ3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="I3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="M3" s="2" t="s">
+      <c r="AR3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AS3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AT3" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="AU3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="AV3" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="AW3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="AX3" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="AY3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="AZ3" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="O3" s="2" t="s">
+      <c r="BA3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="BB3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="BC3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="BD3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="BE3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="BF3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="BG3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="BH3" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="BI3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="BJ3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="BK3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="BL3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="BM3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="BN3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="BO3" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="P3" s="2" t="s">
+      <c r="BP3" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="Q3" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="S3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="T3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="U3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="V3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="W3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="X3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="Y3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="Z3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="AA3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="AB3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="AC3" s="2" t="s">
+      <c r="BQ3" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="BR3" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="BS3" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="AD3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="AE3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="AF3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="AG3" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="AH3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="AI3" s="2" t="s">
+      <c r="BT3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="BU3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="BV3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="BW3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="BX3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="BY3" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="BZ3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="CA3" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="CB3" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="CC3" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="CD3" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="CE3" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="CF3" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="CG3" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="CH3" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="CI3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="CJ3" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="CK3" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="CL3" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="CM3" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="AJ3" s="2" t="s">
+      <c r="CN3" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="CO3" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="CP3" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="CQ3" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="CR3" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="CS3" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="CT3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="CU3" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="CV3" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="CW3" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="CX3" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="CY3" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="CZ3" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="DA3" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="DB3" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="DC3" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="DD3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="DE3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="DF3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="DG3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="DH3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="DI3" s="3" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="S5" s="3">
+        <v>1</v>
+      </c>
+      <c r="AC5" s="3">
+        <v>2</v>
+      </c>
+      <c r="AO5" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="AT5" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="AX5" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="AZ5" s="3">
+        <v>1</v>
+      </c>
+      <c r="BD5" s="3">
+        <v>1</v>
+      </c>
+      <c r="CB5" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="CG5" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="CY5" s="3" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="I6" s="3">
+        <v>1</v>
+      </c>
+      <c r="U6" s="3">
+        <v>0.666667</v>
+      </c>
+      <c r="AC6" s="3">
+        <v>1</v>
+      </c>
+      <c r="AG6" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="BD6" s="3">
+        <v>1</v>
+      </c>
+      <c r="BO6" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="BS6" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="CN6" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="CR6" s="3">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="I7" s="3">
+        <v>1</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="U7" s="3">
+        <v>0.666667</v>
+      </c>
+      <c r="AC7" s="3">
+        <v>1</v>
+      </c>
+      <c r="AG7" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="BD7" s="3">
+        <v>1</v>
+      </c>
+      <c r="CN7" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="CR7" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="I8" s="3">
+        <v>1</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="U8" s="3">
+        <v>0.666667</v>
+      </c>
+      <c r="AC8" s="3">
+        <v>1</v>
+      </c>
+      <c r="AG8" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="AX8" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="AY8" s="3">
+        <v>1</v>
+      </c>
+      <c r="AZ8" s="3">
+        <v>0.0167</v>
+      </c>
+      <c r="BA8" s="3">
+        <v>1</v>
+      </c>
+      <c r="BB8" s="3">
+        <v>1</v>
+      </c>
+      <c r="BD8" s="3">
+        <v>1</v>
+      </c>
+      <c r="BS8" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="CN8" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="CR8" s="3">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="I9" s="3">
+        <v>1</v>
+      </c>
+      <c r="U9" s="3">
+        <v>0.953333</v>
+      </c>
+      <c r="AC9" s="3">
+        <v>1</v>
+      </c>
+      <c r="AG9" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="BD9" s="3">
+        <v>1</v>
+      </c>
+      <c r="BO9" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="BS9" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="CN9" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="CO9" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="CR9" s="3">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="I10" s="3">
+        <v>1</v>
+      </c>
+      <c r="U10" s="3">
+        <v>0.906667</v>
+      </c>
+      <c r="AC10" s="3">
+        <v>1</v>
+      </c>
+      <c r="AG10" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="BD10" s="3">
+        <v>1</v>
+      </c>
+      <c r="BS10" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="CN10" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="CO10" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="CR10" s="3">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="I11" s="3">
+        <v>1</v>
+      </c>
+      <c r="U11" s="3">
+        <v>0.86</v>
+      </c>
+      <c r="AC11" s="3">
+        <v>1</v>
+      </c>
+      <c r="AG11" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="BD11" s="3">
+        <v>1</v>
+      </c>
+      <c r="BS11" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="CN11" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="CO11" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="CR11" s="3">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="I12" s="3">
+        <v>1</v>
+      </c>
+      <c r="U12" s="3">
+        <v>0.813333</v>
+      </c>
+      <c r="AC12" s="3">
+        <v>1</v>
+      </c>
+      <c r="AG12" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="BD12" s="3">
+        <v>1</v>
+      </c>
+      <c r="BS12" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="CN12" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="CO12" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="CR12" s="3">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="I13" s="3">
+        <v>1</v>
+      </c>
+      <c r="U13" s="3">
+        <v>0.766667</v>
+      </c>
+      <c r="AC13" s="3">
+        <v>1</v>
+      </c>
+      <c r="AG13" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="BD13" s="3">
+        <v>1</v>
+      </c>
+      <c r="BS13" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="CN13" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="CO13" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="CR13" s="3">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="G15" s="3">
         <v>3</v>
       </c>
-      <c r="AK3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="AL3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="AM3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="AN3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="AO3" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="AP3" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="AQ3" s="2" t="s">
+      <c r="I15" s="3">
+        <v>1</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="AC15" s="3">
+        <v>1</v>
+      </c>
+      <c r="AG15" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="BD15" s="3">
+        <v>1</v>
+      </c>
+      <c r="BO15" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="BT15" s="3">
+        <v>9999</v>
+      </c>
+      <c r="BV15" s="3">
+        <v>0</v>
+      </c>
+      <c r="BW15" s="3">
+        <v>15</v>
+      </c>
+      <c r="BX15" s="3">
+        <v>1</v>
+      </c>
+      <c r="BY15" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="CN15" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="CO15" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="CR15" s="3">
+        <v>9999</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="I16" s="3">
+        <v>1</v>
+      </c>
+      <c r="O16" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="AC16" s="3">
         <v>2</v>
       </c>
-      <c r="AR3" s="2" t="s">
+      <c r="AO16" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="AT16" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="AX16" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="AZ16" s="3">
+        <v>1</v>
+      </c>
+      <c r="BD16" s="3">
+        <v>1</v>
+      </c>
+      <c r="CB16" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="CG16" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="CY16" s="3" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="I17" s="3">
+        <v>1</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="O17" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="AC17" s="3">
         <v>2</v>
       </c>
-      <c r="AS3" s="2" t="s">
+      <c r="AD17" s="3">
+        <v>1</v>
+      </c>
+      <c r="AE17" s="3">
+        <v>1</v>
+      </c>
+      <c r="AX17" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="AZ17" s="3">
+        <v>1.75</v>
+      </c>
+      <c r="BD17" s="3">
+        <v>1</v>
+      </c>
+      <c r="CY17" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="DD17" s="3">
+        <v>1</v>
+      </c>
+      <c r="DH17" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="G19" s="3">
+        <v>3</v>
+      </c>
+      <c r="I19" s="3">
+        <v>1</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="AC19" s="3">
+        <v>1</v>
+      </c>
+      <c r="AG19" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="AT19" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="BD19" s="3">
+        <v>1</v>
+      </c>
+      <c r="BO19" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="BP19" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="BT19" s="3">
+        <v>32</v>
+      </c>
+      <c r="BU19" s="3">
+        <v>1</v>
+      </c>
+      <c r="BV19" s="3">
+        <v>37</v>
+      </c>
+      <c r="BW19" s="3">
+        <v>45</v>
+      </c>
+      <c r="BX19" s="3">
+        <v>1</v>
+      </c>
+      <c r="BY19" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="CN19" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="CO19" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="CR19" s="3">
+        <v>32</v>
+      </c>
+      <c r="CU19" s="3" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="I20" s="3">
+        <v>1</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="AC20" s="3">
         <v>2</v>
       </c>
-      <c r="AT3" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="AU3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="AV3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="AW3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="AX3" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="AY3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="AZ3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="BA3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="BB3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="BC3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="BD3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="BE3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="BF3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="BG3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="BH3" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="BI3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="BJ3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="BK3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="BL3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="BM3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="BN3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="BO3" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="BP3" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="BQ3" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="BR3" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="BS3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="BT3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="BU3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="BV3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="BW3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="BX3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="BY3" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="BZ3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="CA3" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="CB3" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="CC3" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="CD3" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="CE3" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="CF3" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="CG3" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="CH3" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="CI3" s="2" t="s">
+      <c r="AD20" s="3">
+        <v>1</v>
+      </c>
+      <c r="AO20" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="AT20" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="AX20" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="AZ20" s="3">
+        <v>1</v>
+      </c>
+      <c r="BD20" s="3">
+        <v>3</v>
+      </c>
+      <c r="BE20" s="3">
+        <v>1</v>
+      </c>
+      <c r="BF20" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="CB20" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="CG20" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="CY20" s="3" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="I21" s="3">
+        <v>1</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="AC21" s="3">
+        <v>1</v>
+      </c>
+      <c r="AG21" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="BD21" s="3">
+        <v>1</v>
+      </c>
+      <c r="BS21" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="CM21" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="DD21" s="3">
+        <v>1</v>
+      </c>
+      <c r="DG21" s="3">
+        <v>1</v>
+      </c>
+      <c r="DH21" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="I22" s="3">
+        <v>1</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="AC22" s="3">
+        <v>1</v>
+      </c>
+      <c r="AG22" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="AT22" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="BD22" s="3">
+        <v>1</v>
+      </c>
+      <c r="BO22" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="CN22" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="CO22" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="CP22" s="3">
+        <v>-1</v>
+      </c>
+      <c r="CR22" s="3">
+        <v>11</v>
+      </c>
+      <c r="CU22" s="3" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="I23" s="3">
+        <v>1</v>
+      </c>
+      <c r="O23" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="AC23" s="3">
         <v>2</v>
       </c>
-      <c r="CJ3" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="CK3" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="CL3" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="CM3" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="CN3" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="CO3" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="CP3" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="CQ3" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="CR3" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="CS3" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="CT3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="CU3" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="CV3" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="CW3" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="CX3" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="CY3" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="CZ3" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="DA3" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="DB3" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="DC3" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="DD3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="DE3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="DF3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="DG3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="DH3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="DI3" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="S5" s="2">
-        <v>1</v>
-      </c>
-      <c r="AC5" s="2">
-        <v>2</v>
-      </c>
-      <c r="AO5" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="AT5" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="AX5" s="2" t="s">
+      <c r="AD23" s="3">
+        <v>1</v>
+      </c>
+      <c r="AO23" s="3" t="s">
         <v>385</v>
       </c>
-      <c r="AZ5" s="2">
-        <v>1</v>
-      </c>
-      <c r="BD5" s="2">
-        <v>1</v>
-      </c>
-      <c r="CB5" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="CG5" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="CY5" s="2" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="s">
+      <c r="AT23" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="AX23" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="AZ23" s="3">
+        <v>1</v>
+      </c>
+      <c r="BD23" s="3">
+        <v>3</v>
+      </c>
+      <c r="BE23" s="3">
+        <v>3</v>
+      </c>
+      <c r="BF23" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="CB23" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="CG23" s="3" t="s">
         <v>388</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="I6" s="2">
-        <v>1</v>
-      </c>
-      <c r="U6" s="2">
-        <v>0.666667</v>
-      </c>
-      <c r="AC6" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG6" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="BD6" s="2">
-        <v>1</v>
-      </c>
-      <c r="BO6" s="2" t="s">
+      <c r="CY23" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="CZ23" s="3" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>391</v>
       </c>
-      <c r="BS6" s="2">
+      <c r="I24" s="3">
+        <v>1</v>
+      </c>
+      <c r="O24" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="AC24" s="3">
+        <v>1</v>
+      </c>
+      <c r="AT24" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="AW24" s="3">
+        <v>1</v>
+      </c>
+      <c r="BD24" s="3">
+        <v>99</v>
+      </c>
+      <c r="BS24" s="3">
         <v>0.1</v>
       </c>
-      <c r="CN6" s="2" t="s">
+      <c r="CN24" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="CR24" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="DD24" s="3">
+        <v>1</v>
+      </c>
+      <c r="DG24" s="3">
+        <v>1</v>
+      </c>
+      <c r="DH24" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="I25" s="3">
+        <v>1</v>
+      </c>
+      <c r="O25" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="AC25" s="3">
+        <v>1</v>
+      </c>
+      <c r="AG25" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="AT25" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="AW25" s="3">
+        <v>1</v>
+      </c>
+      <c r="BD25" s="3">
+        <v>99</v>
+      </c>
+      <c r="BS25" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="CN25" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="CR25" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="DD25" s="3">
+        <v>1</v>
+      </c>
+      <c r="DG25" s="3">
+        <v>1</v>
+      </c>
+      <c r="DH25" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="I26" s="3">
+        <v>1</v>
+      </c>
+      <c r="O26" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="AC26" s="3">
+        <v>1</v>
+      </c>
+      <c r="AG26" s="3" t="s">
         <v>392</v>
       </c>
-      <c r="CR6" s="2">
+      <c r="AW26" s="3">
+        <v>1</v>
+      </c>
+      <c r="BD26" s="3">
+        <v>99</v>
+      </c>
+      <c r="BS26" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="CN26" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="CR26" s="3">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="I7" s="2">
-        <v>1</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="U7" s="2">
-        <v>0.666667</v>
-      </c>
-      <c r="AC7" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG7" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="BD7" s="2">
-        <v>1</v>
-      </c>
-      <c r="CN7" s="2" t="s">
+      <c r="DD26" s="3">
+        <v>1</v>
+      </c>
+      <c r="DG26" s="3">
+        <v>1</v>
+      </c>
+      <c r="DH26" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="I27" s="3">
+        <v>1</v>
+      </c>
+      <c r="O27" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="AC27" s="3">
+        <v>1</v>
+      </c>
+      <c r="AG27" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="BD27" s="3">
+        <v>1</v>
+      </c>
+      <c r="CU27" s="3" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="I28" s="3">
+        <v>1</v>
+      </c>
+      <c r="K28" s="3" t="s">
         <v>396</v>
       </c>
-      <c r="CR7" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="s">
-        <v>397</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="I8" s="2">
-        <v>1</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="P8" s="2" t="s">
+      <c r="AC28" s="3">
+        <v>1</v>
+      </c>
+      <c r="AG28" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="BD28" s="3">
+        <v>1</v>
+      </c>
+      <c r="BS28" s="3">
+        <v>0.333</v>
+      </c>
+      <c r="CB28" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="CG28" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="DD28" s="3">
+        <v>1</v>
+      </c>
+      <c r="DG28" s="3">
+        <v>1</v>
+      </c>
+      <c r="DH28" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="I29" s="3">
+        <v>1</v>
+      </c>
+      <c r="K29" s="3" t="s">
         <v>396</v>
       </c>
-      <c r="U8" s="2">
-        <v>0.666667</v>
-      </c>
-      <c r="AC8" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG8" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="AX8" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="AY8" s="2">
-        <v>1</v>
-      </c>
-      <c r="AZ8" s="2">
-        <v>0.0167</v>
-      </c>
-      <c r="BA8" s="2">
-        <v>1</v>
-      </c>
-      <c r="BB8" s="2">
-        <v>1</v>
-      </c>
-      <c r="BD8" s="2">
-        <v>1</v>
-      </c>
-      <c r="BS8" s="2">
+      <c r="L29" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="AC29" s="3">
+        <v>1</v>
+      </c>
+      <c r="AG29" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="BD29" s="3">
+        <v>1</v>
+      </c>
+      <c r="BS29" s="3">
+        <v>0.333</v>
+      </c>
+      <c r="CB29" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="CG29" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="DD29" s="3">
+        <v>1</v>
+      </c>
+      <c r="DG29" s="3">
+        <v>1</v>
+      </c>
+      <c r="DH29" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="CL579" s="3">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="CL581" s="3">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="CL582" s="3">
         <v>0.1</v>
       </c>
-      <c r="CN8" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="CR8" s="2">
+    </row>
+    <row r="584">
+      <c r="CL584" s="3">
         <v>0.2</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="I9" s="2">
-        <v>1</v>
-      </c>
-      <c r="U9" s="2">
-        <v>0.953333</v>
-      </c>
-      <c r="AC9" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG9" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="BD9" s="2">
-        <v>1</v>
-      </c>
-      <c r="BO9" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="BS9" s="2">
-        <v>0.1</v>
-      </c>
-      <c r="CN9" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="CO9" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="CR9" s="2">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="I10" s="2">
-        <v>1</v>
-      </c>
-      <c r="U10" s="2">
-        <v>0.906667</v>
-      </c>
-      <c r="AC10" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG10" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="BD10" s="2">
-        <v>1</v>
-      </c>
-      <c r="BS10" s="2">
-        <v>0.1</v>
-      </c>
-      <c r="CN10" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="CO10" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="CR10" s="2">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="I11" s="2">
-        <v>1</v>
-      </c>
-      <c r="U11" s="2">
-        <v>0.86</v>
-      </c>
-      <c r="AC11" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG11" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="BD11" s="2">
-        <v>1</v>
-      </c>
-      <c r="BS11" s="2">
-        <v>0.1</v>
-      </c>
-      <c r="CN11" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="CO11" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="CR11" s="2">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="I12" s="2">
-        <v>1</v>
-      </c>
-      <c r="U12" s="2">
-        <v>0.813333</v>
-      </c>
-      <c r="AC12" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG12" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="BD12" s="2">
-        <v>1</v>
-      </c>
-      <c r="BS12" s="2">
-        <v>0.1</v>
-      </c>
-      <c r="CN12" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="CO12" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="CR12" s="2">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="I13" s="2">
-        <v>1</v>
-      </c>
-      <c r="U13" s="2">
-        <v>0.766667</v>
-      </c>
-      <c r="AC13" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG13" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="BD13" s="2">
-        <v>1</v>
-      </c>
-      <c r="BS13" s="2">
-        <v>0.1</v>
-      </c>
-      <c r="CN13" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="CO13" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="CR13" s="2">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>412</v>
-      </c>
-      <c r="G15" s="2">
-        <v>3</v>
-      </c>
-      <c r="I15" s="2">
-        <v>1</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="AC15" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG15" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="BD15" s="2">
-        <v>1</v>
-      </c>
-      <c r="BO15" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="BT15" s="2">
-        <v>9999</v>
-      </c>
-      <c r="BV15" s="2">
-        <v>0</v>
-      </c>
-      <c r="BW15" s="2">
-        <v>15</v>
-      </c>
-      <c r="BX15" s="2">
-        <v>1</v>
-      </c>
-      <c r="BY15" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="CN15" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="CO15" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="CR15" s="2">
-        <v>9999</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="I16" s="2">
-        <v>1</v>
-      </c>
-      <c r="O16" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="AC16" s="2">
-        <v>2</v>
-      </c>
-      <c r="AO16" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="AT16" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="AX16" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="AZ16" s="2">
-        <v>1</v>
-      </c>
-      <c r="BD16" s="2">
-        <v>1</v>
-      </c>
-      <c r="CB16" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="CG16" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="CY16" s="2" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="I17" s="2">
-        <v>1</v>
-      </c>
-      <c r="K17" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="L17" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="O17" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="AC17" s="2">
-        <v>2</v>
-      </c>
-      <c r="AD17" s="2">
-        <v>1</v>
-      </c>
-      <c r="AE17" s="2">
-        <v>1</v>
-      </c>
-      <c r="AX17" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="AZ17" s="2">
-        <v>1.75</v>
-      </c>
-      <c r="BD17" s="2">
-        <v>1</v>
-      </c>
-      <c r="CY17" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="DD17" s="2">
-        <v>1</v>
-      </c>
-      <c r="DH17" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="G19" s="2">
-        <v>3</v>
-      </c>
-      <c r="I19" s="2">
-        <v>1</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="K19" s="2" t="s">
-        <v>426</v>
-      </c>
-      <c r="AC19" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG19" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="AT19" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="BD19" s="2">
-        <v>1</v>
-      </c>
-      <c r="BO19" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="BP19" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="BT19" s="2">
-        <v>32</v>
-      </c>
-      <c r="BU19" s="2">
-        <v>1</v>
-      </c>
-      <c r="BV19" s="2">
-        <v>37</v>
-      </c>
-      <c r="BW19" s="2">
-        <v>45</v>
-      </c>
-      <c r="BX19" s="2">
-        <v>1</v>
-      </c>
-      <c r="BY19" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="CN19" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="CO19" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="CR19" s="2">
-        <v>32</v>
-      </c>
-      <c r="CU19" s="2" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="s">
-        <v>433</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="I20" s="2">
-        <v>1</v>
-      </c>
-      <c r="O20" s="2" t="s">
-        <v>434</v>
-      </c>
-      <c r="AC20" s="2">
-        <v>2</v>
-      </c>
-      <c r="AD20" s="2">
-        <v>1</v>
-      </c>
-      <c r="AO20" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="AT20" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="AX20" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="AZ20" s="2">
-        <v>1</v>
-      </c>
-      <c r="BD20" s="2">
-        <v>3</v>
-      </c>
-      <c r="BE20" s="2">
-        <v>1</v>
-      </c>
-      <c r="BF20" s="2">
-        <v>0.1</v>
-      </c>
-      <c r="CB20" s="2" t="s">
-        <v>435</v>
-      </c>
-      <c r="CG20" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="CY20" s="2" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="I21" s="2">
-        <v>1</v>
-      </c>
-      <c r="K21" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="L21" s="2" t="s">
-        <v>437</v>
-      </c>
-      <c r="AC21" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG21" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="BD21" s="2">
-        <v>1</v>
-      </c>
-      <c r="BS21" s="2">
+    <row r="591">
+      <c r="CL591" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="593">
+      <c r="CL593" s="3">
         <v>0.4</v>
       </c>
-      <c r="CM21" s="2" t="s">
-        <v>434</v>
-      </c>
-      <c r="DD21" s="2">
-        <v>1</v>
-      </c>
-      <c r="DG21" s="2">
-        <v>1</v>
-      </c>
-      <c r="DH21" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="s">
-        <v>438</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="I22" s="2">
-        <v>1</v>
-      </c>
-      <c r="O22" s="2" t="s">
-        <v>439</v>
-      </c>
-      <c r="P22" s="2" t="s">
-        <v>434</v>
-      </c>
-      <c r="AC22" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG22" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="AT22" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="BD22" s="2">
-        <v>1</v>
-      </c>
-      <c r="BO22" s="2" t="s">
-        <v>440</v>
-      </c>
-      <c r="CN22" s="2" t="s">
-        <v>441</v>
-      </c>
-      <c r="CO22" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="CP22" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CR22" s="2">
-        <v>11</v>
-      </c>
-      <c r="CU22" s="2" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="s">
-        <v>443</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="I23" s="2">
-        <v>1</v>
-      </c>
-      <c r="O23" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="AC23" s="2">
-        <v>2</v>
-      </c>
-      <c r="AD23" s="2">
-        <v>1</v>
-      </c>
-      <c r="AO23" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="AT23" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="AX23" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="AZ23" s="2">
-        <v>1</v>
-      </c>
-      <c r="BD23" s="2">
-        <v>3</v>
-      </c>
-      <c r="BE23" s="2">
-        <v>3</v>
-      </c>
-      <c r="BF23" s="2">
-        <v>0.1</v>
-      </c>
-      <c r="CB23" s="2" t="s">
-        <v>435</v>
-      </c>
-      <c r="CG23" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="CY23" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="CZ23" s="2" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="s">
-        <v>446</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="I24" s="2">
-        <v>1</v>
-      </c>
-      <c r="O24" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="AC24" s="2">
-        <v>1</v>
-      </c>
-      <c r="AT24" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="AW24" s="2">
-        <v>1</v>
-      </c>
-      <c r="BD24" s="2">
-        <v>99</v>
-      </c>
-      <c r="BS24" s="2">
-        <v>0.1</v>
-      </c>
-      <c r="CN24" s="2" t="s">
-        <v>447</v>
-      </c>
-      <c r="CR24" s="2">
-        <v>0.2</v>
-      </c>
-      <c r="DD24" s="2">
-        <v>1</v>
-      </c>
-      <c r="DG24" s="2">
-        <v>1</v>
-      </c>
-      <c r="DH24" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="I25" s="2">
-        <v>1</v>
-      </c>
-      <c r="O25" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="AC25" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG25" s="2" t="s">
-        <v>449</v>
-      </c>
-      <c r="AT25" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="AW25" s="2">
-        <v>1</v>
-      </c>
-      <c r="BD25" s="2">
-        <v>99</v>
-      </c>
-      <c r="BS25" s="2">
-        <v>0.1</v>
-      </c>
-      <c r="CN25" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="CR25" s="2">
-        <v>0.2</v>
-      </c>
-      <c r="DD25" s="2">
-        <v>1</v>
-      </c>
-      <c r="DG25" s="2">
-        <v>1</v>
-      </c>
-      <c r="DH25" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="s">
-        <v>450</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="I26" s="2">
-        <v>1</v>
-      </c>
-      <c r="O26" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="AC26" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG26" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="AW26" s="2">
-        <v>1</v>
-      </c>
-      <c r="BD26" s="2">
-        <v>99</v>
-      </c>
-      <c r="BS26" s="2">
-        <v>0.1</v>
-      </c>
-      <c r="CN26" s="2" t="s">
-        <v>450</v>
-      </c>
-      <c r="CR26" s="2">
-        <v>0.2</v>
-      </c>
-      <c r="DD26" s="2">
-        <v>1</v>
-      </c>
-      <c r="DG26" s="2">
-        <v>1</v>
-      </c>
-      <c r="DH26" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="s">
-        <v>451</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="I27" s="2">
-        <v>1</v>
-      </c>
-      <c r="O27" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="AC27" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG27" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="BD27" s="2">
-        <v>1</v>
-      </c>
-      <c r="CU27" s="2" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="I28" s="2">
-        <v>1</v>
-      </c>
-      <c r="K28" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="AC28" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG28" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="BD28" s="2">
-        <v>1</v>
-      </c>
-      <c r="BS28" s="2">
-        <v>0.333</v>
-      </c>
-      <c r="CB28" s="2" t="s">
-        <v>454</v>
-      </c>
-      <c r="CG28" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="DD28" s="2">
-        <v>1</v>
-      </c>
-      <c r="DG28" s="2">
-        <v>1</v>
-      </c>
-      <c r="DH28" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="I29" s="2">
-        <v>1</v>
-      </c>
-      <c r="K29" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="L29" s="2" t="s">
-        <v>437</v>
-      </c>
-      <c r="AC29" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG29" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="BD29" s="2">
-        <v>1</v>
-      </c>
-      <c r="BS29" s="2">
-        <v>0.333</v>
-      </c>
-      <c r="CB29" s="2" t="s">
-        <v>456</v>
-      </c>
-      <c r="CG29" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="DD29" s="2">
-        <v>1</v>
-      </c>
-      <c r="DG29" s="2">
-        <v>1</v>
-      </c>
-      <c r="DH29" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="579">
-      <c r="CL579" s="2">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="581">
-      <c r="CL581" s="2">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="582">
-      <c r="CL582" s="2">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="584">
-      <c r="CL584" s="2">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="591">
-      <c r="CL591" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="593">
-      <c r="CL593" s="2">
-        <v>0.4</v>
-      </c>
     </row>
     <row r="594">
-      <c r="CL594" s="2">
+      <c r="CL594" s="3">
         <v>0.6</v>
       </c>
     </row>
     <row r="597">
-      <c r="CL597" s="2">
+      <c r="CL597" s="3">
         <v>0.5</v>
       </c>
     </row>
     <row r="598">
-      <c r="CL598" s="2">
+      <c r="CL598" s="3">
         <v>0.667</v>
       </c>
     </row>
     <row r="599">
-      <c r="CL599" s="2">
+      <c r="CL599" s="3">
         <v>0.2</v>
       </c>
     </row>
@@ -5403,347 +5430,347 @@
   <dimension ref="A1:Q17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13" customWidth="1" style="2"/>
-    <col min="2" max="2" width="31.25" customWidth="1" style="2"/>
-    <col min="3" max="6" width="9" customWidth="1" style="2"/>
-    <col min="7" max="7" width="18.75" customWidth="1" style="2"/>
-    <col min="8" max="8" width="15" customWidth="1" style="2"/>
-    <col min="9" max="13" width="9" customWidth="1" style="2"/>
-    <col min="14" max="14" width="16.08203125" customWidth="1" style="2"/>
-    <col min="15" max="15" width="9.5" customWidth="1" style="2"/>
-    <col min="16" max="16" width="9" customWidth="1" style="2"/>
-    <col min="17" max="17" width="12.83203125" customWidth="1" style="2"/>
+    <col min="1" max="1" width="13" customWidth="1" style="3"/>
+    <col min="2" max="2" width="31.25" customWidth="1" style="3"/>
+    <col min="3" max="6" width="9" customWidth="1" style="3"/>
+    <col min="7" max="7" width="18.75" customWidth="1" style="3"/>
+    <col min="8" max="8" width="15" customWidth="1" style="3"/>
+    <col min="9" max="13" width="9" customWidth="1" style="3"/>
+    <col min="14" max="14" width="16.08203125" customWidth="1" style="3"/>
+    <col min="15" max="15" width="9.5" customWidth="1" style="3"/>
+    <col min="16" max="16" width="9" customWidth="1" style="3"/>
+    <col min="17" max="17" width="12.83203125" customWidth="1" style="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>457</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="G1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>459</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>460</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>461</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>462</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>463</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>464</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="L1" s="3" t="s">
         <v>465</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="M1" s="3" t="s">
         <v>466</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="N1" s="3" t="s">
         <v>467</v>
       </c>
+      <c r="O1" s="3" t="s">
+        <v>468</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>469</v>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>468</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="G2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>470</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>471</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="G2" s="3" t="s">
         <v>472</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="H2" s="3" t="s">
         <v>473</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="I2" s="3" t="s">
         <v>474</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="J2" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="L2" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="M2" s="2" t="s">
-        <v>475</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>476</v>
-      </c>
-      <c r="O2" s="2" t="s">
+      <c r="M2" s="3" t="s">
         <v>477</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="N2" s="3" t="s">
         <v>478</v>
       </c>
-      <c r="Q2" s="2" t="s">
-        <v>349</v>
+      <c r="O2" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>351</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="K3" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>132</v>
+      <c r="L3" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>479</v>
-      </c>
-      <c r="H4" s="2">
-        <v>1</v>
-      </c>
-      <c r="N4" s="2">
-        <v>1</v>
-      </c>
-      <c r="Q4" s="2" t="s">
-        <v>480</v>
+      <c r="A4" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="H4" s="3">
+        <v>1</v>
+      </c>
+      <c r="N4" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="3" t="s">
+        <v>482</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>481</v>
-      </c>
-      <c r="H5" s="2">
-        <v>1</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="N5" s="2">
+      <c r="A5" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="H5" s="3">
+        <v>1</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="N5" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>481</v>
-      </c>
-      <c r="H6" s="2">
+      <c r="A6" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="H6" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="C7" s="2" t="s">
+      <c r="A7" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="Q7" s="3" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>483</v>
       </c>
-      <c r="Q7" s="2" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="s">
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="C9" s="2" t="s">
+      <c r="H9" s="3">
+        <v>1</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="H10" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="H11" s="3">
+        <v>1</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>492</v>
+      </c>
+      <c r="Q11" s="3" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="H12" s="3">
+        <v>1</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>483</v>
       </c>
-      <c r="H9" s="2">
-        <v>1</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>486</v>
-      </c>
-      <c r="Q9" s="2" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="s">
-        <v>434</v>
-      </c>
-      <c r="C10" s="2" t="s">
+      <c r="H13" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>483</v>
       </c>
-      <c r="H10" s="2">
-        <v>1</v>
-      </c>
-      <c r="Q10" s="2" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="s">
-        <v>489</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="H11" s="2">
-        <v>1</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>490</v>
-      </c>
-      <c r="Q11" s="2" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>483</v>
-      </c>
-      <c r="H12" s="2">
-        <v>1</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>486</v>
-      </c>
-      <c r="Q12" s="2" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="s">
-        <v>439</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>481</v>
-      </c>
-      <c r="H13" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="s">
-        <v>492</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>481</v>
-      </c>
-      <c r="H14" s="2">
-        <v>1</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>439</v>
+      <c r="H14" s="3">
+        <v>1</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="Q15" s="2" t="s">
-        <v>494</v>
+      <c r="A15" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="Q15" s="3" t="s">
+        <v>496</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="s">
-        <v>450</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="Q16" s="2" t="s">
+      <c r="A16" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>495</v>
       </c>
+      <c r="Q16" s="3" t="s">
+        <v>497</v>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="s">
-        <v>447</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>496</v>
-      </c>
-      <c r="H17" s="2">
-        <v>1</v>
-      </c>
-      <c r="Q17" s="2" t="s">
-        <v>497</v>
+      <c r="A17" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="H17" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q17" s="3" t="s">
+        <v>499</v>
       </c>
     </row>
   </sheetData>
@@ -5759,46 +5786,46 @@
   <dimension ref="A1:D3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.33203125" customWidth="1" style="2"/>
-    <col min="2" max="2" width="11.25" customWidth="1" style="2"/>
-    <col min="3" max="3" width="9" customWidth="1" style="2"/>
-    <col min="4" max="4" width="27.5" customWidth="1" style="2"/>
+    <col min="1" max="1" width="11.33203125" customWidth="1" style="3"/>
+    <col min="2" max="2" width="11.25" customWidth="1" style="3"/>
+    <col min="3" max="3" width="9" customWidth="1" style="3"/>
+    <col min="4" max="4" width="27.5" customWidth="1" style="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>498</v>
+      <c r="C1" s="3" t="s">
+        <v>500</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>349</v>
+      <c r="C2" s="3" t="s">
+        <v>501</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>351</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>132</v>
+      <c r="C3" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -5814,80 +5841,80 @@
   <dimension ref="A1:J3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.25" customWidth="1" style="2"/>
-    <col min="2" max="2" width="9" customWidth="1" style="2"/>
-    <col min="3" max="3" width="27.25" customWidth="1" style="2"/>
-    <col min="4" max="4" width="10.83203125" customWidth="1" style="2"/>
-    <col min="5" max="10" width="9" customWidth="1" style="2"/>
+    <col min="1" max="1" width="15.25" customWidth="1" style="3"/>
+    <col min="2" max="2" width="9" customWidth="1" style="3"/>
+    <col min="3" max="3" width="27.25" customWidth="1" style="3"/>
+    <col min="4" max="4" width="10.83203125" customWidth="1" style="3"/>
+    <col min="5" max="10" width="9" customWidth="1" style="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="I1" s="2" t="s">
-        <v>234</v>
+      <c r="I1" s="3" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>500</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="D2" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>501</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>502</v>
-      </c>
-      <c r="H2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>503</v>
       </c>
-      <c r="I2" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>349</v>
+      <c r="G2" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>351</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="F3" s="2" t="s">
+      <c r="E3" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>132</v>
+      <c r="F3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -5903,123 +5930,123 @@
   <dimension ref="A1:L3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.25" customWidth="1" style="2"/>
-    <col min="2" max="2" width="28" customWidth="1" style="2"/>
-    <col min="3" max="4" width="10.08203125" customWidth="1" style="2"/>
-    <col min="5" max="10" width="11.25" customWidth="1" style="2"/>
-    <col min="11" max="11" width="6.33203125" customWidth="1" style="2"/>
-    <col min="12" max="12" width="9" customWidth="1" style="2"/>
+    <col min="1" max="1" width="15.25" customWidth="1" style="3"/>
+    <col min="2" max="2" width="28" customWidth="1" style="3"/>
+    <col min="3" max="4" width="10.08203125" customWidth="1" style="3"/>
+    <col min="5" max="10" width="11.25" customWidth="1" style="3"/>
+    <col min="11" max="11" width="6.33203125" customWidth="1" style="3"/>
+    <col min="12" max="12" width="9" customWidth="1" style="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>504</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>505</v>
-      </c>
-      <c r="D1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>506</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>507</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>508</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>509</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>510</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>511</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>512</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>513</v>
       </c>
+      <c r="K1" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>515</v>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>514</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="D2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>516</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>517</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>518</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>519</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>520</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="G2" s="3" t="s">
         <v>521</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="H2" s="3" t="s">
         <v>522</v>
       </c>
-      <c r="K2" s="2" t="s">
-        <v>501</v>
-      </c>
-      <c r="L2" s="2" t="s">
+      <c r="I2" s="3" t="s">
+        <v>523</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>503</v>
+      </c>
+      <c r="L2" s="3" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="K3" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="H3" s="2" t="s">
+      <c r="L3" s="3" t="s">
         <v>125</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>123</v>
       </c>
     </row>
   </sheetData>
@@ -6036,45 +6063,45 @@
   <dimension ref="A2:J3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.08203125" customWidth="1" style="2"/>
-    <col min="2" max="2" width="16.25" customWidth="1" style="2"/>
-    <col min="3" max="3" width="16.33203125" customWidth="1" style="2"/>
-    <col min="4" max="4" width="47.83203125" customWidth="1" style="2"/>
-    <col min="5" max="5" width="10.25" customWidth="1" style="2"/>
-    <col min="6" max="6" width="12.83203125" customWidth="1" style="2"/>
-    <col min="7" max="9" width="9" customWidth="1" style="2"/>
-    <col min="10" max="10" width="11.83203125" customWidth="1" style="2"/>
+    <col min="1" max="1" width="19.08203125" customWidth="1" style="3"/>
+    <col min="2" max="2" width="16.25" customWidth="1" style="3"/>
+    <col min="3" max="3" width="16.33203125" customWidth="1" style="3"/>
+    <col min="4" max="4" width="47.83203125" customWidth="1" style="3"/>
+    <col min="5" max="5" width="10.25" customWidth="1" style="3"/>
+    <col min="6" max="6" width="12.83203125" customWidth="1" style="3"/>
+    <col min="7" max="9" width="9" customWidth="1" style="3"/>
+    <col min="10" max="10" width="11.83203125" customWidth="1" style="3"/>
   </cols>
   <sheetData>
     <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="C2" s="2" t="s">
+      <c r="B2" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>524</v>
-      </c>
-      <c r="F2" s="2" t="s">
+      <c r="D2" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>526</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>525</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>526</v>
-      </c>
-      <c r="J2" s="2" t="s">
+      <c r="G2" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>528</v>
+      </c>
+      <c r="J2" s="3" t="s">
         <v>58</v>
       </c>
     </row>
@@ -6092,22 +6119,22 @@
         <v>2</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
   </sheetData>
@@ -6122,127 +6149,127 @@
   <dimension ref="A1:I4"/>
   <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.5" customWidth="1" style="2"/>
-    <col min="2" max="2" width="10.6640625" customWidth="1" style="2"/>
-    <col min="3" max="3" width="21.9140625" customWidth="1" style="2"/>
-    <col min="4" max="4" width="16.25" customWidth="1" style="2"/>
-    <col min="5" max="5" width="14" customWidth="1" style="2"/>
-    <col min="6" max="7" width="15.1640625" customWidth="1" style="2"/>
-    <col min="8" max="8" width="12.9140625" customWidth="1" style="2"/>
-    <col min="9" max="9" width="14" customWidth="1" style="2"/>
+    <col min="1" max="1" width="7.5" customWidth="1" style="3"/>
+    <col min="2" max="2" width="10.6640625" customWidth="1" style="3"/>
+    <col min="3" max="3" width="21.9140625" customWidth="1" style="3"/>
+    <col min="4" max="4" width="16.25" customWidth="1" style="3"/>
+    <col min="5" max="5" width="14" customWidth="1" style="3"/>
+    <col min="6" max="7" width="15.1640625" customWidth="1" style="3"/>
+    <col min="8" max="8" width="12.9140625" customWidth="1" style="3"/>
+    <col min="9" max="9" width="14" customWidth="1" style="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>528</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>529</v>
-      </c>
-      <c r="D1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>530</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>531</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>532</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>533</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>534</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>535</v>
       </c>
+      <c r="H1" s="3" t="s">
+        <v>536</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>537</v>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>537</v>
-      </c>
-      <c r="D2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>539</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>540</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>541</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>542</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="G2" s="3" t="s">
         <v>543</v>
       </c>
+      <c r="H2" s="3" t="s">
+        <v>544</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>545</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="D3" s="2" t="s">
+      <c r="B3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="2">
-        <v>1</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>544</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>545</v>
-      </c>
-      <c r="F4" s="2" t="s">
+      <c r="C4" s="3">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>546</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="E4" s="3" t="s">
         <v>547</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="F4" s="3" t="s">
         <v>548</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="G4" s="3" t="s">
         <v>549</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>550</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>551</v>
       </c>
     </row>
   </sheetData>
